--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -218,10 +218,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -243,10 +243,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -268,10 +268,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -293,10 +293,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59" customWidth="1" min="1" max="1"/>
@@ -642,448 +642,224 @@
     <col width="8" customWidth="1" min="31" max="31"/>
     <col width="8" customWidth="1" min="32" max="32"/>
     <col width="8" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="42" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
+          <t>INFORME DE CONTROL TÉCNICO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>COORDINACIÓN ZONAL 6</t>
+          <t>No. IT-CZ06-R-2025-00XX</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:MACAS</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:MACAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FRECUENCIA (MHz)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Frecuencia (MHz)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T10" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W10" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X10" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y10" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA8" s="3" t="n">
+      <c r="AA10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB8" s="3" t="n">
+      <c r="AB10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC10" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD8" s="3" t="n">
+      <c r="AD10" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE8" s="3" t="n">
+      <c r="AE10" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF8" s="3" t="n">
+      <c r="AF10" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG8" s="3" t="n">
+      <c r="AG10" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
+      <c r="AH10" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI8" s="3" t="inlineStr">
+      <c r="AI10" s="3" t="inlineStr">
         <is>
           <t>Ancho de Banda
 (KHz)</t>
         </is>
       </c>
-      <c r="AJ8" s="3" t="inlineStr">
+      <c r="AJ10" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AK8" s="4" t="inlineStr">
+      <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>PUBLICA FM</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>66.56999999999999</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>80.47</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>80.86</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>80.84</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>74.51000000000001</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>72.01000000000001</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>81.16</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>80.72</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>80.48</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>80.53</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="U9" s="6" t="n">
-        <v>63.59</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>76.68000000000001</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>82.92</v>
-      </c>
-      <c r="X9" s="6" t="n">
-        <v>82.81999999999999</v>
-      </c>
-      <c r="Y9" s="6" t="n">
-        <v>75.56</v>
-      </c>
-      <c r="Z9" s="6" t="n">
-        <v>73.47</v>
-      </c>
-      <c r="AA9" s="6" t="n">
-        <v>83.01000000000001</v>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>82.97</v>
-      </c>
-      <c r="AC9" s="6" t="n">
-        <v>75.53</v>
-      </c>
-      <c r="AD9" s="6" t="n">
-        <v>82.34999999999999</v>
-      </c>
-      <c r="AE9" s="6" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="AF9" s="6" t="n">
-        <v>72.95</v>
-      </c>
-      <c r="AG9" s="6" t="n">
-        <v>79.95</v>
-      </c>
-      <c r="AH9" s="6" t="n">
-        <v>76.17</v>
-      </c>
-      <c r="AI9" s="6" t="n">
-        <v>172.46</v>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>RADIO MORONA NO autorizada</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>61.59</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>62.58</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>61.98</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>64.01000000000001</v>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>63.42</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>62.89</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>62.57</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="U10" s="6" t="n">
-        <v>62.14</v>
-      </c>
-      <c r="V10" s="6" t="n">
-        <v>62.39</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="Y10" s="6" t="n">
-        <v>62.69</v>
-      </c>
-      <c r="Z10" s="6" t="n">
-        <v>63.32</v>
-      </c>
-      <c r="AA10" s="6" t="n">
-        <v>63.82</v>
-      </c>
-      <c r="AB10" s="6" t="n">
-        <v>63.92</v>
-      </c>
-      <c r="AC10" s="6" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="AD10" s="6" t="n">
-        <v>62.72</v>
-      </c>
-      <c r="AE10" s="6" t="n">
-        <v>62.31</v>
-      </c>
-      <c r="AF10" s="6" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="AG10" s="6" t="n">
-        <v>77.42</v>
-      </c>
-      <c r="AH10" s="6" t="n">
-        <v>62.84</v>
-      </c>
-      <c r="AI10" s="6" t="n">
-        <v>205.41</v>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>LA VOZ DE LA NAE</t>
+          <t>PUBLICA FM</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>89.7</v>
+        <v>88.5</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>45.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>41.8</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>50.04</v>
+        <v>80.47</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>52.02</v>
+        <v>80.86</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -1096,19 +872,19 @@
         </is>
       </c>
       <c r="I11" s="6" t="n">
-        <v>51.87</v>
+        <v>80.84</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>43.55</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>42.94</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>52.16</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>52.39</v>
+        <v>60.2</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
@@ -1121,64 +897,64 @@
         </is>
       </c>
       <c r="P11" s="6" t="n">
-        <v>51.88</v>
+        <v>81.16</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>53.01</v>
+        <v>80.72</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>53.68</v>
+        <v>80.48</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>53.23</v>
+        <v>80.53</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>53.03</v>
+        <v>66.73</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>52.08</v>
+        <v>63.59</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>53.32</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>56.62</v>
+        <v>82.92</v>
       </c>
       <c r="X11" s="6" t="n">
-        <v>54.02</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>51.79</v>
+        <v>75.56</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>51.92</v>
+        <v>73.47</v>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>55.86</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="AB11" s="6" t="n">
-        <v>57.24</v>
+        <v>82.97</v>
       </c>
       <c r="AC11" s="6" t="n">
-        <v>53.42</v>
+        <v>75.53</v>
       </c>
       <c r="AD11" s="6" t="n">
-        <v>55.09</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="AE11" s="6" t="n">
-        <v>52.02</v>
+        <v>75.8</v>
       </c>
       <c r="AF11" s="6" t="n">
-        <v>52.26</v>
+        <v>72.95</v>
       </c>
       <c r="AG11" s="6" t="n">
-        <v>69.26000000000001</v>
+        <v>79.95</v>
       </c>
       <c r="AH11" s="6" t="n">
-        <v>52.3</v>
+        <v>76.17</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>237.33</v>
+        <v>172.46</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
       <c r="AK11" s="7" t="inlineStr"/>
@@ -1186,23 +962,23 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RADIO LA VOZ DEL UPANO</t>
+          <t>RADIO MORONA NO autorizada</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>90.5</v>
+        <v>89.3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>109.78</v>
+        <v>61.59</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>106.81</v>
+        <v>60.48</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>108.96</v>
+        <v>61.1</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>109.08</v>
+        <v>62.58</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1215,19 +991,19 @@
         </is>
       </c>
       <c r="I12" s="6" t="n">
-        <v>109.52</v>
+        <v>61.98</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>104.66</v>
+        <v>60</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>108.14</v>
+        <v>57.81</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>106.88</v>
+        <v>62.01</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>105.61</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -1240,64 +1016,64 @@
         </is>
       </c>
       <c r="P12" s="6" t="n">
-        <v>109.61</v>
+        <v>63.4</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>109.38</v>
+        <v>63.42</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>108.96</v>
+        <v>62.89</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>109.92</v>
+        <v>62.57</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>105.51</v>
+        <v>60.43</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>105.63</v>
+        <v>62.14</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>107.74</v>
+        <v>62.39</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>109.52</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="X12" s="6" t="n">
-        <v>109.3</v>
+        <v>62.5</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>107.91</v>
+        <v>62.69</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>107.72</v>
+        <v>63.32</v>
       </c>
       <c r="AA12" s="6" t="n">
-        <v>110.12</v>
+        <v>63.82</v>
       </c>
       <c r="AB12" s="6" t="n">
-        <v>109.82</v>
+        <v>63.92</v>
       </c>
       <c r="AC12" s="6" t="n">
-        <v>107.43</v>
+        <v>62.53</v>
       </c>
       <c r="AD12" s="6" t="n">
-        <v>109.26</v>
+        <v>62.72</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>107.44</v>
+        <v>62.31</v>
       </c>
       <c r="AF12" s="6" t="n">
-        <v>106.69</v>
+        <v>62.48</v>
       </c>
       <c r="AG12" s="6" t="n">
-        <v>109.6</v>
+        <v>77.42</v>
       </c>
       <c r="AH12" s="6" t="n">
-        <v>108.19</v>
+        <v>62.84</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>137.83</v>
+        <v>205.41</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
       <c r="AK12" s="7" t="inlineStr"/>
@@ -1305,23 +1081,23 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>LA RADIO DE LA ASAMBLEA NACIONAL</t>
+          <t>LA VOZ DE LA NAE</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>90.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>45.29</v>
+        <v>45.5</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>42.04</v>
+        <v>41.8</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>50.12</v>
+        <v>50.04</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>51.98</v>
+        <v>52.02</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1334,19 +1110,19 @@
         </is>
       </c>
       <c r="I13" s="6" t="n">
-        <v>50.55</v>
+        <v>51.87</v>
       </c>
       <c r="J13" s="6" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="K13" s="6" t="n">
         <v>42.94</v>
       </c>
-      <c r="K13" s="6" t="n">
-        <v>43.26</v>
-      </c>
       <c r="L13" s="6" t="n">
-        <v>48.76</v>
+        <v>52.16</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>48.99</v>
+        <v>52.39</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -1359,64 +1135,64 @@
         </is>
       </c>
       <c r="P13" s="6" t="n">
-        <v>56.08</v>
+        <v>51.88</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>56.57</v>
+        <v>53.01</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>56.91</v>
+        <v>53.68</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>76.69</v>
+        <v>53.23</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>95.5</v>
+        <v>53.03</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>93.18000000000001</v>
+        <v>52.08</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>95.66</v>
+        <v>53.32</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>97.03</v>
+        <v>56.62</v>
       </c>
       <c r="X13" s="6" t="n">
-        <v>96.73999999999999</v>
+        <v>54.02</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>91.09</v>
+        <v>51.79</v>
       </c>
       <c r="Z13" s="6" t="n">
-        <v>90.98999999999999</v>
+        <v>51.92</v>
       </c>
       <c r="AA13" s="6" t="n">
-        <v>96.06</v>
+        <v>55.86</v>
       </c>
       <c r="AB13" s="6" t="n">
-        <v>96.89</v>
+        <v>57.24</v>
       </c>
       <c r="AC13" s="6" t="n">
-        <v>91.52</v>
+        <v>53.42</v>
       </c>
       <c r="AD13" s="6" t="n">
-        <v>96.27</v>
+        <v>55.09</v>
       </c>
       <c r="AE13" s="6" t="n">
-        <v>90.23999999999999</v>
+        <v>52.02</v>
       </c>
       <c r="AF13" s="6" t="n">
-        <v>90.91</v>
+        <v>52.26</v>
       </c>
       <c r="AG13" s="6" t="n">
-        <v>93.54000000000001</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="AH13" s="6" t="n">
-        <v>73.55</v>
+        <v>52.3</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>299.96</v>
+        <v>237.33</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
       <c r="AK13" s="7" t="inlineStr"/>
@@ -1424,23 +1200,23 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>BONITA FM</t>
+          <t>RADIO LA VOZ DEL UPANO</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>91.7</v>
+        <v>90.5</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>107.59</v>
+        <v>109.78</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>93.81</v>
+        <v>106.81</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>108.35</v>
+        <v>108.96</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>108.56</v>
+        <v>109.08</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1453,19 +1229,19 @@
         </is>
       </c>
       <c r="I14" s="6" t="n">
-        <v>108.44</v>
+        <v>109.52</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>89.39</v>
+        <v>104.66</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>101.09</v>
+        <v>108.14</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>99.14</v>
+        <v>106.88</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>86.36</v>
+        <v>105.61</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -1478,64 +1254,64 @@
         </is>
       </c>
       <c r="P14" s="6" t="n">
-        <v>108.01</v>
+        <v>109.61</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>107.68</v>
+        <v>109.38</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>108.93</v>
+        <v>108.96</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>104.02</v>
+        <v>109.92</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>94.18000000000001</v>
+        <v>105.51</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>89.81</v>
+        <v>105.63</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>101.15</v>
+        <v>107.74</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>108.49</v>
+        <v>109.52</v>
       </c>
       <c r="X14" s="6" t="n">
-        <v>107.51</v>
+        <v>109.3</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>96.81999999999999</v>
+        <v>107.91</v>
       </c>
       <c r="Z14" s="6" t="n">
-        <v>98.70999999999999</v>
+        <v>107.72</v>
       </c>
       <c r="AA14" s="6" t="n">
-        <v>107.18</v>
+        <v>110.12</v>
       </c>
       <c r="AB14" s="6" t="n">
-        <v>107.91</v>
+        <v>109.82</v>
       </c>
       <c r="AC14" s="6" t="n">
-        <v>99.31</v>
+        <v>107.43</v>
       </c>
       <c r="AD14" s="6" t="n">
-        <v>107.21</v>
+        <v>109.26</v>
       </c>
       <c r="AE14" s="6" t="n">
-        <v>97.72</v>
+        <v>107.44</v>
       </c>
       <c r="AF14" s="6" t="n">
-        <v>99.06999999999999</v>
+        <v>106.69</v>
       </c>
       <c r="AG14" s="6" t="n">
-        <v>104.34</v>
+        <v>109.6</v>
       </c>
       <c r="AH14" s="6" t="n">
-        <v>101.88</v>
+        <v>108.19</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>149.91</v>
+        <v>137.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
       <c r="AK14" s="7" t="inlineStr"/>
@@ -1543,23 +1319,23 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>RADIO MIA FM (MAGNIFICA INTEGRACION AMAZÓNICA)</t>
+          <t>LA RADIO DE LA ASAMBLEA NACIONAL</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>92.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>105.74</v>
+        <v>45.29</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>100.15</v>
+        <v>42.04</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>105.96</v>
+        <v>50.12</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>106.57</v>
+        <v>51.98</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1572,19 +1348,19 @@
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>106.49</v>
+        <v>50.55</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>99.04000000000001</v>
+        <v>42.94</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>101.86</v>
+        <v>43.26</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>101.58</v>
+        <v>48.76</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>98.15000000000001</v>
+        <v>48.99</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
@@ -1597,64 +1373,64 @@
         </is>
       </c>
       <c r="P15" s="6" t="n">
-        <v>106.69</v>
+        <v>56.08</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>106.43</v>
+        <v>56.57</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>107.08</v>
+        <v>56.91</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>102.64</v>
+        <v>76.69</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>99.98999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>98.48</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="V15" s="6" t="n">
-        <v>103.04</v>
+        <v>95.66</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>107.46</v>
+        <v>97.03</v>
       </c>
       <c r="X15" s="6" t="n">
-        <v>106.45</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>102.93</v>
+        <v>91.09</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>102.51</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="AA15" s="6" t="n">
-        <v>106.14</v>
+        <v>96.06</v>
       </c>
       <c r="AB15" s="6" t="n">
-        <v>107.07</v>
+        <v>96.89</v>
       </c>
       <c r="AC15" s="6" t="n">
-        <v>103.14</v>
+        <v>91.52</v>
       </c>
       <c r="AD15" s="6" t="n">
-        <v>106.84</v>
+        <v>96.27</v>
       </c>
       <c r="AE15" s="6" t="n">
-        <v>101.76</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="AF15" s="6" t="n">
-        <v>102.42</v>
+        <v>90.91</v>
       </c>
       <c r="AG15" s="6" t="n">
-        <v>104.2</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="AH15" s="6" t="n">
-        <v>103.73</v>
+        <v>73.55</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>187.17</v>
+        <v>299.96</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
       <c r="AK15" s="7" t="inlineStr"/>
@@ -1662,23 +1438,23 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CANAL JUVENIL FM</t>
+          <t>BONITA FM</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>94.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>63.02</v>
+        <v>107.59</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>58.38</v>
+        <v>93.81</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>64.98999999999999</v>
+        <v>108.35</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>67.68000000000001</v>
+        <v>108.56</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
@@ -1691,19 +1467,19 @@
         </is>
       </c>
       <c r="I16" s="6" t="n">
-        <v>67.52</v>
+        <v>108.44</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>58.28</v>
+        <v>89.39</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>65.03</v>
+        <v>101.09</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>62.27</v>
+        <v>99.14</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>58.3</v>
+        <v>86.36</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
@@ -1716,64 +1492,64 @@
         </is>
       </c>
       <c r="P16" s="6" t="n">
-        <v>65.92</v>
+        <v>108.01</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>66.34999999999999</v>
+        <v>107.68</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>62.22</v>
+        <v>108.93</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>59.86</v>
+        <v>104.02</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>64.81</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>55.07</v>
+        <v>89.81</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>65.63</v>
+        <v>101.15</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>61.1</v>
+        <v>108.49</v>
       </c>
       <c r="X16" s="6" t="n">
-        <v>66.61</v>
+        <v>107.51</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>66.45999999999999</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="Z16" s="6" t="n">
-        <v>60.84</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="AA16" s="6" t="n">
-        <v>65.91</v>
+        <v>107.18</v>
       </c>
       <c r="AB16" s="6" t="n">
-        <v>63.78</v>
+        <v>107.91</v>
       </c>
       <c r="AC16" s="6" t="n">
-        <v>62.94</v>
+        <v>99.31</v>
       </c>
       <c r="AD16" s="6" t="n">
-        <v>66.7</v>
+        <v>107.21</v>
       </c>
       <c r="AE16" s="6" t="n">
-        <v>59.84</v>
+        <v>97.72</v>
       </c>
       <c r="AF16" s="6" t="n">
-        <v>63.09</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="AG16" s="6" t="n">
-        <v>64.59</v>
+        <v>104.34</v>
       </c>
       <c r="AH16" s="6" t="n">
-        <v>63.23</v>
+        <v>101.88</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>174.55</v>
+        <v>149.91</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
       <c r="AK16" s="7" t="inlineStr"/>
@@ -1781,23 +1557,23 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>RADIO INTEROCEANICA</t>
+          <t>RADIO MIA FM (MAGNIFICA INTEGRACION AMAZÓNICA)</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>96.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>45.01</v>
+        <v>105.74</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>42.51</v>
+        <v>100.15</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>47.62</v>
+        <v>105.96</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>48.7</v>
+        <v>106.57</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -1810,19 +1586,19 @@
         </is>
       </c>
       <c r="I17" s="6" t="n">
-        <v>50.16</v>
+        <v>106.49</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>43.32</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>45.82</v>
+        <v>101.86</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>45.42</v>
+        <v>101.58</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>42.99</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
@@ -1835,64 +1611,64 @@
         </is>
       </c>
       <c r="P17" s="6" t="n">
-        <v>46.38</v>
+        <v>106.69</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>47.96</v>
+        <v>106.43</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>49.18</v>
+        <v>107.08</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>44.67</v>
+        <v>102.64</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>47.12</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>46.34</v>
+        <v>98.48</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>48.12</v>
+        <v>103.04</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>49.51</v>
+        <v>107.46</v>
       </c>
       <c r="X17" s="6" t="n">
-        <v>47.52</v>
+        <v>106.45</v>
       </c>
       <c r="Y17" s="6" t="n">
-        <v>44.94</v>
+        <v>102.93</v>
       </c>
       <c r="Z17" s="6" t="n">
-        <v>42.99</v>
+        <v>102.51</v>
       </c>
       <c r="AA17" s="6" t="n">
-        <v>49.02</v>
+        <v>106.14</v>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>49.04</v>
+        <v>107.07</v>
       </c>
       <c r="AC17" s="6" t="n">
-        <v>46.11</v>
+        <v>103.14</v>
       </c>
       <c r="AD17" s="6" t="n">
-        <v>47.42</v>
+        <v>106.84</v>
       </c>
       <c r="AE17" s="6" t="n">
-        <v>44.98</v>
+        <v>101.76</v>
       </c>
       <c r="AF17" s="6" t="n">
-        <v>47.28</v>
+        <v>102.42</v>
       </c>
       <c r="AG17" s="6" t="n">
-        <v>46.35</v>
+        <v>104.2</v>
       </c>
       <c r="AH17" s="6" t="n">
-        <v>46.54</v>
+        <v>103.73</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>499.13</v>
+        <v>187.17</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
       <c r="AK17" s="7" t="inlineStr"/>
@@ -1900,23 +1676,23 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>SISTEMA RADIAL OLIMPICA</t>
+          <t>CANAL JUVENIL FM</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>97.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>89.51000000000001</v>
+        <v>63.02</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>81.95999999999999</v>
+        <v>58.38</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>89.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>91.45</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -1929,19 +1705,19 @@
         </is>
       </c>
       <c r="I18" s="6" t="n">
-        <v>90.48</v>
+        <v>67.52</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>80.09999999999999</v>
+        <v>58.28</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>86.26000000000001</v>
+        <v>65.03</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>83.86</v>
+        <v>62.27</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>79.45</v>
+        <v>58.3</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
@@ -1954,64 +1730,64 @@
         </is>
       </c>
       <c r="P18" s="6" t="n">
-        <v>90.51000000000001</v>
+        <v>65.92</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>90.81</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>91.64</v>
+        <v>62.22</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>85.58</v>
+        <v>59.86</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>81.23999999999999</v>
+        <v>64.81</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>79.42</v>
+        <v>55.07</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>87.36</v>
+        <v>65.63</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>92.31999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="X18" s="6" t="n">
-        <v>91.98999999999999</v>
+        <v>66.61</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>85.3</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="Z18" s="6" t="n">
-        <v>82.70999999999999</v>
+        <v>60.84</v>
       </c>
       <c r="AA18" s="6" t="n">
-        <v>91.26000000000001</v>
+        <v>65.91</v>
       </c>
       <c r="AB18" s="6" t="n">
-        <v>92.29000000000001</v>
+        <v>63.78</v>
       </c>
       <c r="AC18" s="6" t="n">
-        <v>85.56999999999999</v>
+        <v>62.94</v>
       </c>
       <c r="AD18" s="6" t="n">
-        <v>91.02</v>
+        <v>66.7</v>
       </c>
       <c r="AE18" s="6" t="n">
-        <v>85.31999999999999</v>
+        <v>59.84</v>
       </c>
       <c r="AF18" s="6" t="n">
-        <v>82.48999999999999</v>
+        <v>63.09</v>
       </c>
       <c r="AG18" s="6" t="n">
-        <v>85.90000000000001</v>
+        <v>64.59</v>
       </c>
       <c r="AH18" s="6" t="n">
-        <v>86.86</v>
+        <v>63.23</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>112.27</v>
+        <v>174.55</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
       <c r="AK18" s="7" t="inlineStr"/>
@@ -2019,23 +1795,23 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TU PANA</t>
+          <t>RADIO INTEROCEANICA</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>98.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>98.34</v>
+        <v>45.01</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>99.76000000000001</v>
+        <v>42.51</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>101.26</v>
+        <v>47.62</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>101.47</v>
+        <v>48.7</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -2048,19 +1824,19 @@
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>103.69</v>
+        <v>50.16</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>100.86</v>
+        <v>43.32</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>103.41</v>
+        <v>45.82</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>102.35</v>
+        <v>45.42</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>100.96</v>
+        <v>42.99</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -2073,64 +1849,64 @@
         </is>
       </c>
       <c r="P19" s="6" t="n">
-        <v>99.04000000000001</v>
+        <v>46.38</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>103.47</v>
+        <v>47.96</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>104</v>
+        <v>49.18</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>104.37</v>
+        <v>44.67</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>100.84</v>
+        <v>47.12</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>101.53</v>
+        <v>46.34</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>99.76000000000001</v>
+        <v>48.12</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>101.29</v>
+        <v>49.51</v>
       </c>
       <c r="X19" s="6" t="n">
-        <v>103.64</v>
+        <v>47.52</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>100.18</v>
+        <v>44.94</v>
       </c>
       <c r="Z19" s="6" t="n">
-        <v>100.08</v>
+        <v>42.99</v>
       </c>
       <c r="AA19" s="6" t="n">
-        <v>100.99</v>
+        <v>49.02</v>
       </c>
       <c r="AB19" s="6" t="n">
-        <v>103.89</v>
+        <v>49.04</v>
       </c>
       <c r="AC19" s="6" t="n">
-        <v>105.16</v>
+        <v>46.11</v>
       </c>
       <c r="AD19" s="6" t="n">
-        <v>101.01</v>
+        <v>47.42</v>
       </c>
       <c r="AE19" s="6" t="n">
-        <v>102.46</v>
+        <v>44.98</v>
       </c>
       <c r="AF19" s="6" t="n">
-        <v>105.29</v>
+        <v>47.28</v>
       </c>
       <c r="AG19" s="6" t="n">
-        <v>99.95999999999999</v>
+        <v>46.35</v>
       </c>
       <c r="AH19" s="6" t="n">
-        <v>101.82</v>
+        <v>46.54</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>208.17</v>
+        <v>499.13</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
       <c r="AK19" s="7" t="inlineStr"/>
@@ -2138,23 +1914,23 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>RADIO MARIA</t>
+          <t>SISTEMA RADIAL OLIMPICA</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>99.5</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>95.20999999999999</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>99.42</v>
+        <v>89.38</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>101.61</v>
+        <v>91.45</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
@@ -2167,19 +1943,19 @@
         </is>
       </c>
       <c r="I20" s="6" t="n">
-        <v>101.38</v>
+        <v>90.48</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>92.95999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>96.08</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>95.78</v>
+        <v>83.86</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>93.04000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -2192,64 +1968,64 @@
         </is>
       </c>
       <c r="P20" s="6" t="n">
-        <v>100.32</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>100.12</v>
+        <v>90.81</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>101.44</v>
+        <v>91.64</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>96.90000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>94.20999999999999</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>92.56999999999999</v>
+        <v>79.42</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>97.48</v>
+        <v>87.36</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>101.01</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="X20" s="6" t="n">
-        <v>100.29</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>97.31999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="Z20" s="6" t="n">
-        <v>96.56</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="AA20" s="6" t="n">
-        <v>99.92</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="AB20" s="6" t="n">
-        <v>101.01</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="AC20" s="6" t="n">
-        <v>97.25</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="AD20" s="6" t="n">
-        <v>99.95999999999999</v>
+        <v>91.02</v>
       </c>
       <c r="AE20" s="6" t="n">
-        <v>96.06999999999999</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="AF20" s="6" t="n">
-        <v>97</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="AG20" s="6" t="n">
-        <v>97.05</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="AH20" s="6" t="n">
-        <v>97.83</v>
+        <v>86.86</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>131.9</v>
+        <v>112.27</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
       <c r="AK20" s="7" t="inlineStr"/>
@@ -2257,23 +2033,23 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>LA RADIO FM DIGITAL 100.1</t>
+          <t>TU PANA</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>100.1</v>
+        <v>98.5</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>47.7</v>
+        <v>98.34</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>43.78</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>49.55</v>
+        <v>101.26</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>51.52</v>
+        <v>101.47</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -2286,19 +2062,19 @@
         </is>
       </c>
       <c r="I21" s="6" t="n">
-        <v>51.51</v>
+        <v>103.69</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>46</v>
+        <v>100.86</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>44.19</v>
+        <v>103.41</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>78.01000000000001</v>
+        <v>102.35</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>107.6</v>
+        <v>100.96</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -2311,64 +2087,64 @@
         </is>
       </c>
       <c r="P21" s="6" t="n">
-        <v>109.66</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>109.71</v>
+        <v>103.47</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>110.36</v>
+        <v>104</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>108.43</v>
+        <v>104.37</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>108.78</v>
+        <v>100.84</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>107.36</v>
+        <v>101.53</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>109.56</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>110.01</v>
+        <v>101.29</v>
       </c>
       <c r="X21" s="6" t="n">
-        <v>109.64</v>
+        <v>103.64</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>109.68</v>
+        <v>100.18</v>
       </c>
       <c r="Z21" s="6" t="n">
-        <v>109.14</v>
+        <v>100.08</v>
       </c>
       <c r="AA21" s="6" t="n">
-        <v>109.69</v>
+        <v>100.99</v>
       </c>
       <c r="AB21" s="6" t="n">
-        <v>109.97</v>
+        <v>103.89</v>
       </c>
       <c r="AC21" s="6" t="n">
-        <v>109.84</v>
+        <v>105.16</v>
       </c>
       <c r="AD21" s="6" t="n">
-        <v>109.11</v>
+        <v>101.01</v>
       </c>
       <c r="AE21" s="6" t="n">
-        <v>109.33</v>
+        <v>102.46</v>
       </c>
       <c r="AF21" s="6" t="n">
-        <v>109.56</v>
+        <v>105.29</v>
       </c>
       <c r="AG21" s="6" t="n">
-        <v>109.65</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
-        <v>92.2</v>
+        <v>101.82</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>217.44</v>
+        <v>208.17</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
       <c r="AK21" s="7" t="inlineStr"/>
@@ -2376,23 +2152,23 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>RADIO RELOJ</t>
+          <t>RADIO MARIA</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>100.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>108.18</v>
+        <v>99.5</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>106.3</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>107.82</v>
+        <v>99.42</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>108.52</v>
+        <v>101.61</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -2405,19 +2181,19 @@
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>108.51</v>
+        <v>101.38</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>106.51</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>107.64</v>
+        <v>96.08</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>107.61</v>
+        <v>95.78</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>106</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
@@ -2430,64 +2206,64 @@
         </is>
       </c>
       <c r="P22" s="6" t="n">
-        <v>108.43</v>
+        <v>100.32</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>108.12</v>
+        <v>100.12</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>108.58</v>
+        <v>101.44</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>107.31</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>107.6</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>107.37</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>108.86</v>
+        <v>97.48</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>108.52</v>
+        <v>101.01</v>
       </c>
       <c r="X22" s="6" t="n">
-        <v>108</v>
+        <v>100.29</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>108.71</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="Z22" s="6" t="n">
-        <v>107.91</v>
+        <v>96.56</v>
       </c>
       <c r="AA22" s="6" t="n">
-        <v>108.32</v>
+        <v>99.92</v>
       </c>
       <c r="AB22" s="6" t="n">
-        <v>108.39</v>
+        <v>101.01</v>
       </c>
       <c r="AC22" s="6" t="n">
-        <v>109.13</v>
+        <v>97.25</v>
       </c>
       <c r="AD22" s="6" t="n">
-        <v>107.91</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="AE22" s="6" t="n">
-        <v>107.97</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="AF22" s="6" t="n">
-        <v>108.65</v>
+        <v>97</v>
       </c>
       <c r="AG22" s="6" t="n">
-        <v>107.92</v>
+        <v>97.05</v>
       </c>
       <c r="AH22" s="6" t="n">
-        <v>107.96</v>
+        <v>97.83</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>179.35</v>
+        <v>131.9</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
       <c r="AK22" s="7" t="inlineStr"/>
@@ -2495,23 +2271,23 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>RADIO UNIVERSITARIA PRIMICIAS DE LA CULTURA</t>
+          <t>LA RADIO FM DIGITAL 100.1</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>101.7</v>
+        <v>100.1</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>99.59</v>
+        <v>47.7</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>98.40000000000001</v>
+        <v>43.78</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>99.61</v>
+        <v>49.55</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>100.02</v>
+        <v>51.52</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -2524,19 +2300,19 @@
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>99.69</v>
+        <v>51.51</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>98.56</v>
+        <v>46</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>98.23999999999999</v>
+        <v>44.19</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>98.36</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>97.34</v>
+        <v>107.6</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -2549,64 +2325,64 @@
         </is>
       </c>
       <c r="P23" s="6" t="n">
-        <v>100.28</v>
+        <v>109.66</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>99.61</v>
+        <v>109.71</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>99.86</v>
+        <v>110.36</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>98.62</v>
+        <v>108.43</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>97.48</v>
+        <v>108.78</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>95.91</v>
+        <v>107.36</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>99.28</v>
+        <v>109.56</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>99.76000000000001</v>
+        <v>110.01</v>
       </c>
       <c r="X23" s="6" t="n">
-        <v>100.02</v>
+        <v>109.64</v>
       </c>
       <c r="Y23" s="6" t="n">
-        <v>99.62</v>
+        <v>109.68</v>
       </c>
       <c r="Z23" s="6" t="n">
-        <v>98.54000000000001</v>
+        <v>109.14</v>
       </c>
       <c r="AA23" s="6" t="n">
-        <v>99.52</v>
+        <v>109.69</v>
       </c>
       <c r="AB23" s="6" t="n">
-        <v>99.69</v>
+        <v>109.97</v>
       </c>
       <c r="AC23" s="6" t="n">
-        <v>98.75</v>
+        <v>109.84</v>
       </c>
       <c r="AD23" s="6" t="n">
-        <v>99.54000000000001</v>
+        <v>109.11</v>
       </c>
       <c r="AE23" s="6" t="n">
-        <v>99.41</v>
+        <v>109.33</v>
       </c>
       <c r="AF23" s="6" t="n">
-        <v>99.84</v>
+        <v>109.56</v>
       </c>
       <c r="AG23" s="6" t="n">
-        <v>99.05</v>
+        <v>109.65</v>
       </c>
       <c r="AH23" s="6" t="n">
-        <v>99.06</v>
+        <v>92.2</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>37.91</v>
+        <v>217.44</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
       <c r="AK23" s="7" t="inlineStr"/>
@@ -2614,23 +2390,23 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>RADIO KIRUBA 102.5 FM(NO AUTORIZADA)</t>
+          <t>RADIO RELOJ</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>102.5</v>
+        <v>100.5</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>92.06</v>
+        <v>108.18</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>86.98999999999999</v>
+        <v>106.3</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>91.81999999999999</v>
+        <v>107.82</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>92.64</v>
+        <v>108.52</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -2643,19 +2419,19 @@
         </is>
       </c>
       <c r="I24" s="6" t="n">
-        <v>92.51000000000001</v>
+        <v>108.51</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>86.19</v>
+        <v>106.51</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>90.39</v>
+        <v>107.64</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>87.59</v>
+        <v>107.61</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>80.54000000000001</v>
+        <v>106</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -2668,64 +2444,64 @@
         </is>
       </c>
       <c r="P24" s="6" t="n">
-        <v>92.56</v>
+        <v>108.43</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>91.94</v>
+        <v>108.12</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>92.38</v>
+        <v>108.58</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>89.69</v>
+        <v>107.31</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>85.63</v>
+        <v>107.6</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>79.22</v>
+        <v>107.37</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>90.13</v>
+        <v>108.86</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>92.39</v>
+        <v>108.52</v>
       </c>
       <c r="X24" s="6" t="n">
-        <v>92.28</v>
+        <v>108</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>87.91</v>
+        <v>108.71</v>
       </c>
       <c r="Z24" s="6" t="n">
-        <v>87.38</v>
+        <v>107.91</v>
       </c>
       <c r="AA24" s="6" t="n">
-        <v>92.01000000000001</v>
+        <v>108.32</v>
       </c>
       <c r="AB24" s="6" t="n">
-        <v>92.16</v>
+        <v>108.39</v>
       </c>
       <c r="AC24" s="6" t="n">
-        <v>88.69</v>
+        <v>109.13</v>
       </c>
       <c r="AD24" s="6" t="n">
-        <v>92.31</v>
+        <v>107.91</v>
       </c>
       <c r="AE24" s="6" t="n">
-        <v>89.11</v>
+        <v>107.97</v>
       </c>
       <c r="AF24" s="6" t="n">
-        <v>89.39</v>
+        <v>108.65</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>90.84999999999999</v>
+        <v>107.92</v>
       </c>
       <c r="AH24" s="6" t="n">
-        <v>89.51000000000001</v>
+        <v>107.96</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>162.72</v>
+        <v>179.35</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
       <c r="AK24" s="7" t="inlineStr"/>
@@ -2733,23 +2509,23 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>RADIO IKIAM NO AUTORIZADA</t>
+          <t>RADIO UNIVERSITARIA PRIMICIAS DE LA CULTURA</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>103.7</v>
+        <v>101.7</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>40.55</v>
+        <v>99.59</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>40.37</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>45.01</v>
+        <v>99.61</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>45.64</v>
+        <v>100.02</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -2762,19 +2538,19 @@
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>45.92</v>
+        <v>99.69</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>44.02</v>
+        <v>98.56</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>39.78</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>42.79</v>
+        <v>98.36</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>43.6</v>
+        <v>97.34</v>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -2787,64 +2563,64 @@
         </is>
       </c>
       <c r="P25" s="6" t="n">
-        <v>43.68</v>
+        <v>100.28</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>44.51</v>
+        <v>99.61</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>45.51</v>
+        <v>99.86</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>41.6</v>
+        <v>98.62</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>47.68</v>
+        <v>97.48</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>47.97</v>
+        <v>95.91</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>48.11</v>
+        <v>99.28</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>46.76</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>45.13</v>
+        <v>100.02</v>
       </c>
       <c r="Y25" s="6" t="n">
-        <v>43.96</v>
+        <v>99.62</v>
       </c>
       <c r="Z25" s="6" t="n">
-        <v>42.04</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="AA25" s="6" t="n">
-        <v>46.09</v>
+        <v>99.52</v>
       </c>
       <c r="AB25" s="6" t="n">
-        <v>44.94</v>
+        <v>99.69</v>
       </c>
       <c r="AC25" s="6" t="n">
-        <v>42.45</v>
+        <v>98.75</v>
       </c>
       <c r="AD25" s="6" t="n">
-        <v>45.12</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="AE25" s="6" t="n">
-        <v>42.72</v>
+        <v>99.41</v>
       </c>
       <c r="AF25" s="6" t="n">
-        <v>44.48</v>
+        <v>99.84</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>46.65</v>
+        <v>99.05</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>44.34</v>
+        <v>99.06</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>499.69</v>
+        <v>37.91</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
       <c r="AK25" s="7" t="inlineStr"/>
@@ -2852,23 +2628,23 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>SHALOM</t>
+          <t>RADIO KIRUBA 102.5 FM(NO AUTORIZADA)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>104.9</v>
+        <v>102.5</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>42.55</v>
+        <v>92.06</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>40.56</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>45.41</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>46</v>
+        <v>92.64</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
@@ -2881,19 +2657,19 @@
         </is>
       </c>
       <c r="I26" s="6" t="n">
-        <v>47.29</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>43.31</v>
+        <v>86.19</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>43.66</v>
+        <v>90.39</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>43.66</v>
+        <v>87.59</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>43.85</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
@@ -2906,64 +2682,64 @@
         </is>
       </c>
       <c r="P26" s="6" t="n">
-        <v>44.41</v>
+        <v>92.56</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>46.52</v>
+        <v>91.94</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>46.61</v>
+        <v>92.38</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>43.24</v>
+        <v>89.69</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>47.58</v>
+        <v>85.63</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>47.44</v>
+        <v>79.22</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>47.52</v>
+        <v>90.13</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>47.36</v>
+        <v>92.39</v>
       </c>
       <c r="X26" s="6" t="n">
-        <v>46.7</v>
+        <v>92.28</v>
       </c>
       <c r="Y26" s="6" t="n">
-        <v>43.12</v>
+        <v>87.91</v>
       </c>
       <c r="Z26" s="6" t="n">
-        <v>43.08</v>
+        <v>87.38</v>
       </c>
       <c r="AA26" s="6" t="n">
-        <v>46.76</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="AB26" s="6" t="n">
-        <v>46.58</v>
+        <v>92.16</v>
       </c>
       <c r="AC26" s="6" t="n">
-        <v>44.84</v>
+        <v>88.69</v>
       </c>
       <c r="AD26" s="6" t="n">
-        <v>46.04</v>
+        <v>92.31</v>
       </c>
       <c r="AE26" s="6" t="n">
-        <v>44.46</v>
+        <v>89.11</v>
       </c>
       <c r="AF26" s="6" t="n">
-        <v>46.29</v>
+        <v>89.39</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>47.22</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>45.26</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>499.61</v>
+        <v>162.72</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
       <c r="AK26" s="7" t="inlineStr"/>
@@ -2971,23 +2747,23 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>ESTELAR FM</t>
+          <t>RADIO IKIAM NO AUTORIZADA</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>106.5</v>
+        <v>103.7</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>75.36</v>
+        <v>40.55</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>75.08</v>
+        <v>40.37</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>74.23999999999999</v>
+        <v>45.01</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>74.31999999999999</v>
+        <v>45.64</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -3000,19 +2776,19 @@
         </is>
       </c>
       <c r="I27" s="6" t="n">
-        <v>74.01000000000001</v>
+        <v>45.92</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>74.62</v>
+        <v>44.02</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>75.54000000000001</v>
+        <v>39.78</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>74.73</v>
+        <v>42.79</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>75.15000000000001</v>
+        <v>43.6</v>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
@@ -3025,616 +2801,620 @@
         </is>
       </c>
       <c r="P27" s="6" t="n">
-        <v>74.02</v>
+        <v>43.68</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>73.97</v>
+        <v>44.51</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>74.06</v>
+        <v>45.51</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>74.39</v>
+        <v>41.6</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>74.88</v>
+        <v>47.68</v>
       </c>
       <c r="U27" s="6" t="n">
-        <v>74.45999999999999</v>
+        <v>47.97</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>75.29000000000001</v>
+        <v>48.11</v>
       </c>
       <c r="W27" s="6" t="n">
-        <v>74.34</v>
+        <v>46.76</v>
       </c>
       <c r="X27" s="6" t="n">
-        <v>74.42</v>
+        <v>45.13</v>
       </c>
       <c r="Y27" s="6" t="n">
-        <v>73.54000000000001</v>
+        <v>43.96</v>
       </c>
       <c r="Z27" s="6" t="n">
-        <v>74.66</v>
+        <v>42.04</v>
       </c>
       <c r="AA27" s="6" t="n">
-        <v>74.95</v>
+        <v>46.09</v>
       </c>
       <c r="AB27" s="6" t="n">
-        <v>74.91</v>
+        <v>44.94</v>
       </c>
       <c r="AC27" s="6" t="n">
-        <v>74.06</v>
+        <v>42.45</v>
       </c>
       <c r="AD27" s="6" t="n">
-        <v>74.48999999999999</v>
+        <v>45.12</v>
       </c>
       <c r="AE27" s="6" t="n">
-        <v>73.81999999999999</v>
+        <v>42.72</v>
       </c>
       <c r="AF27" s="6" t="n">
-        <v>73.91</v>
+        <v>44.48</v>
       </c>
       <c r="AG27" s="6" t="n">
-        <v>74.38</v>
+        <v>46.65</v>
       </c>
       <c r="AH27" s="6" t="n">
-        <v>74.5</v>
+        <v>44.34</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>273.47</v>
+        <v>499.69</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
       <c r="AK27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>SHALOM</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="T28" s="6" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="U28" s="6" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="W28" s="6" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="X28" s="6" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="Y28" s="6" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="Z28" s="6" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="AA28" s="6" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="AB28" s="6" t="n">
+        <v>46.58</v>
+      </c>
+      <c r="AC28" s="6" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="AD28" s="6" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="AE28" s="6" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="AF28" s="6" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="AG28" s="6" t="n">
+        <v>47.22</v>
+      </c>
+      <c r="AH28" s="6" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="AI28" s="6" t="n">
+        <v>499.61</v>
+      </c>
+      <c r="AJ28" s="6" t="inlineStr"/>
+      <c r="AK28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>ESTELAR FM</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>75.36</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>75.08</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>74.01000000000001</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>74.62</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>75.54000000000001</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>74.73</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>74.02</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>73.97</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>74.06</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="T29" s="6" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="U29" s="6" t="n">
+        <v>74.45999999999999</v>
+      </c>
+      <c r="V29" s="6" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="W29" s="6" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="X29" s="6" t="n">
+        <v>74.42</v>
+      </c>
+      <c r="Y29" s="6" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="Z29" s="6" t="n">
+        <v>74.66</v>
+      </c>
+      <c r="AA29" s="6" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="AB29" s="6" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="AC29" s="6" t="n">
+        <v>74.06</v>
+      </c>
+      <c r="AD29" s="6" t="n">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="AE29" s="6" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="AF29" s="6" t="n">
+        <v>73.91</v>
+      </c>
+      <c r="AG29" s="6" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="AH29" s="6" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AI29" s="6" t="n">
+        <v>273.47</v>
+      </c>
+      <c r="AJ29" s="6" t="inlineStr"/>
+      <c r="AK29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>LA VOZ DE ARUTAM (NO AUTORIZADA)</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B30" s="9" t="n">
         <v>107.3</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C30" s="9" t="n">
         <v>43.06</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D30" s="9" t="n">
         <v>41.51</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E30" s="9" t="n">
         <v>47.48</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F30" s="9" t="n">
         <v>48.84</v>
       </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="n">
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="n">
         <v>49.17</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J30" s="9" t="n">
         <v>40.76</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K30" s="9" t="n">
         <v>41.36</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L30" s="9" t="n">
         <v>46.16</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M30" s="9" t="n">
         <v>43.89</v>
       </c>
-      <c r="N28" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O28" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P28" s="9" t="n">
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="9" t="n">
         <v>53.46</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q30" s="9" t="n">
         <v>54.55</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R30" s="9" t="n">
         <v>56.15</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S30" s="9" t="n">
         <v>49.19</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T30" s="9" t="n">
         <v>47.4</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U30" s="9" t="n">
         <v>46.51</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V30" s="9" t="n">
         <v>50.82</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W30" s="9" t="n">
         <v>55.1</v>
       </c>
-      <c r="X28" s="9" t="n">
+      <c r="X30" s="9" t="n">
         <v>54.54</v>
       </c>
-      <c r="Y28" s="9" t="n">
+      <c r="Y30" s="9" t="n">
         <v>49.52</v>
       </c>
-      <c r="Z28" s="9" t="n">
+      <c r="Z30" s="9" t="n">
         <v>47.54</v>
       </c>
-      <c r="AA28" s="9" t="n">
+      <c r="AA30" s="9" t="n">
         <v>54.18</v>
       </c>
-      <c r="AB28" s="9" t="n">
+      <c r="AB30" s="9" t="n">
         <v>55.12</v>
       </c>
-      <c r="AC28" s="9" t="n">
+      <c r="AC30" s="9" t="n">
         <v>48.65</v>
       </c>
-      <c r="AD28" s="9" t="n">
+      <c r="AD30" s="9" t="n">
         <v>53.31</v>
       </c>
-      <c r="AE28" s="9" t="n">
+      <c r="AE30" s="9" t="n">
         <v>49.16</v>
       </c>
-      <c r="AF28" s="9" t="n">
+      <c r="AF30" s="9" t="n">
         <v>50.49</v>
       </c>
-      <c r="AG28" s="9" t="n">
+      <c r="AG30" s="9" t="n">
         <v>51.46</v>
       </c>
-      <c r="AH28" s="9" t="n">
+      <c r="AH30" s="9" t="n">
         <v>49.24</v>
       </c>
-      <c r="AI28" s="9" t="n">
+      <c r="AI30" s="9" t="n">
         <v>498.71</v>
       </c>
-      <c r="AJ28" s="9" t="inlineStr"/>
-      <c r="AK28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>COORDINACIÓN ZONAL 6</t>
-        </is>
-      </c>
-    </row>
+      <c r="AJ30" s="9" t="inlineStr"/>
+      <c r="AK30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:MACAS</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:MACAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="45" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Frecuencia (MHz)</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G40" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H40" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I40" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="J40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K40" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L40" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M40" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="O40" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="3" t="n">
+      <c r="P40" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q40" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S38" s="3" t="n">
+      <c r="S40" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T38" s="3" t="n">
+      <c r="T40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U38" s="3" t="n">
+      <c r="U40" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V40" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W40" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X38" s="3" t="n">
+      <c r="X40" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y38" s="3" t="n">
+      <c r="Y40" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z38" s="3" t="n">
+      <c r="Z40" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA38" s="3" t="n">
+      <c r="AA40" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB38" s="3" t="n">
+      <c r="AB40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC38" s="3" t="n">
+      <c r="AC40" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD38" s="3" t="n">
+      <c r="AD40" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE38" s="3" t="n">
+      <c r="AE40" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF38" s="3" t="n">
+      <c r="AF40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG38" s="3" t="n">
+      <c r="AG40" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH38" s="3" t="inlineStr">
+      <c r="AH40" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI38" s="3" t="inlineStr">
+      <c r="AI40" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AJ38" s="3" t="inlineStr">
+      <c r="AJ40" s="3" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>RED TELESISTEMA (R.T.S)</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>86.73</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>82.92</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>87.48</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>87.08</v>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>87.06999999999999</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>81.53</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="L39" s="6" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="M39" s="6" t="n">
-        <v>85.23</v>
-      </c>
-      <c r="N39" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O39" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v>87.17</v>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v>87.05</v>
-      </c>
-      <c r="S39" s="6" t="n">
-        <v>86.67</v>
-      </c>
-      <c r="T39" s="6" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="U39" s="6" t="n">
-        <v>84.83</v>
-      </c>
-      <c r="V39" s="6" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="W39" s="6" t="n">
-        <v>87.38</v>
-      </c>
-      <c r="X39" s="6" t="n">
-        <v>86.98</v>
-      </c>
-      <c r="Y39" s="6" t="n">
-        <v>87.37</v>
-      </c>
-      <c r="Z39" s="6" t="n">
-        <v>84.87</v>
-      </c>
-      <c r="AA39" s="6" t="n">
-        <v>86.98</v>
-      </c>
-      <c r="AB39" s="6" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="AC39" s="6" t="n">
-        <v>87.02</v>
-      </c>
-      <c r="AD39" s="6" t="n">
-        <v>86.87</v>
-      </c>
-      <c r="AE39" s="6" t="n">
-        <v>86.73</v>
-      </c>
-      <c r="AF39" s="6" t="n">
-        <v>86.87</v>
-      </c>
-      <c r="AG39" s="6" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="AH39" s="6" t="n">
-        <v>86.20999999999999</v>
-      </c>
-      <c r="AI39" s="6" t="inlineStr"/>
-      <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>ECUADOR TV</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>175.25</v>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>108.83</v>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>109.62</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>109.05</v>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>108.47</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>109.17</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="L40" s="6" t="n">
-        <v>108.75</v>
-      </c>
-      <c r="M40" s="6" t="n">
-        <v>108.4</v>
-      </c>
-      <c r="N40" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O40" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>109.07</v>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v>109.23</v>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v>109.03</v>
-      </c>
-      <c r="S40" s="6" t="n">
-        <v>110.05</v>
-      </c>
-      <c r="T40" s="6" t="n">
-        <v>109.6</v>
-      </c>
-      <c r="U40" s="6" t="n">
-        <v>109</v>
-      </c>
-      <c r="V40" s="6" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="W40" s="6" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="X40" s="6" t="n">
-        <v>109.07</v>
-      </c>
-      <c r="Y40" s="6" t="n">
-        <v>108.78</v>
-      </c>
-      <c r="Z40" s="6" t="n">
-        <v>108.83</v>
-      </c>
-      <c r="AA40" s="6" t="n">
-        <v>109.1</v>
-      </c>
-      <c r="AB40" s="6" t="n">
-        <v>109.03</v>
-      </c>
-      <c r="AC40" s="6" t="n">
-        <v>108.75</v>
-      </c>
-      <c r="AD40" s="6" t="n">
-        <v>108.88</v>
-      </c>
-      <c r="AE40" s="6" t="n">
-        <v>108.47</v>
-      </c>
-      <c r="AF40" s="6" t="n">
-        <v>108.88</v>
-      </c>
-      <c r="AG40" s="6" t="n">
-        <v>109.2</v>
-      </c>
-      <c r="AH40" s="6" t="n">
-        <v>109.02</v>
-      </c>
-      <c r="AI40" s="6" t="inlineStr"/>
-      <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="7" t="n"/>
+      <c r="AK40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>CADENA ECUATORIANA DE TELEVISIO</t>
+          <t>RED TELESISTEMA (R.T.S)</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>181.25</v>
+        <v>61.25</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>38.13</v>
+        <v>86.73</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>42</v>
+        <v>82.92</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>41.13</v>
+        <v>87.48</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>41.17</v>
+        <v>87.08</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
@@ -3647,19 +3427,19 @@
         </is>
       </c>
       <c r="I41" s="6" t="n">
-        <v>36.3</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>49.5</v>
+        <v>81.53</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>37.1</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>40.53</v>
+        <v>84.2</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>50.5</v>
+        <v>85.23</v>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
@@ -3672,61 +3452,61 @@
         </is>
       </c>
       <c r="P41" s="6" t="n">
-        <v>39.87</v>
+        <v>87.17</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>38.13</v>
+        <v>87.3</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>37.27</v>
+        <v>87.05</v>
       </c>
       <c r="S41" s="6" t="n">
-        <v>47.38</v>
+        <v>86.67</v>
       </c>
       <c r="T41" s="6" t="n">
-        <v>51.48</v>
+        <v>84.38</v>
       </c>
       <c r="U41" s="6" t="n">
-        <v>56.65</v>
+        <v>84.83</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>45.32</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="W41" s="6" t="n">
-        <v>41.1</v>
+        <v>87.38</v>
       </c>
       <c r="X41" s="6" t="n">
-        <v>39.07</v>
+        <v>86.98</v>
       </c>
       <c r="Y41" s="6" t="n">
-        <v>41.78</v>
+        <v>87.37</v>
       </c>
       <c r="Z41" s="6" t="n">
-        <v>44.7</v>
+        <v>84.87</v>
       </c>
       <c r="AA41" s="6" t="n">
-        <v>42.47</v>
+        <v>86.98</v>
       </c>
       <c r="AB41" s="6" t="n">
-        <v>37.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AC41" s="6" t="n">
-        <v>39.95</v>
+        <v>87.02</v>
       </c>
       <c r="AD41" s="6" t="n">
-        <v>38.4</v>
+        <v>86.87</v>
       </c>
       <c r="AE41" s="6" t="n">
-        <v>39.77</v>
+        <v>86.73</v>
       </c>
       <c r="AF41" s="6" t="n">
-        <v>41.9</v>
+        <v>86.87</v>
       </c>
       <c r="AG41" s="6" t="n">
-        <v>39.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AH41" s="6" t="n">
-        <v>42.16</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
@@ -3735,23 +3515,23 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>TELEVISION DEL PACIFICO</t>
+          <t>ECUADOR TV</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>187.25</v>
+        <v>175.25</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>36.4</v>
+        <v>108.83</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>37.47</v>
+        <v>109.62</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>39.78</v>
+        <v>109.3</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>41.35</v>
+        <v>109.05</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -3764,19 +3544,19 @@
         </is>
       </c>
       <c r="I42" s="6" t="n">
-        <v>36.1</v>
+        <v>108.47</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>39</v>
+        <v>109.17</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>37.07</v>
+        <v>108.9</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>37.3</v>
+        <v>108.75</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>39.17</v>
+        <v>108.4</v>
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
@@ -3789,61 +3569,61 @@
         </is>
       </c>
       <c r="P42" s="6" t="n">
-        <v>36.13</v>
+        <v>109.07</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>36.55</v>
+        <v>109.23</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>37.55</v>
+        <v>109.03</v>
       </c>
       <c r="S42" s="6" t="n">
-        <v>37.77</v>
+        <v>110.05</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>42.85</v>
+        <v>109.6</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>43.72</v>
+        <v>109</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>42.25</v>
+        <v>108.9</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>39.5</v>
+        <v>109.3</v>
       </c>
       <c r="X42" s="6" t="n">
-        <v>37.32</v>
+        <v>109.07</v>
       </c>
       <c r="Y42" s="6" t="n">
-        <v>38.07</v>
+        <v>108.78</v>
       </c>
       <c r="Z42" s="6" t="n">
-        <v>37.63</v>
+        <v>108.83</v>
       </c>
       <c r="AA42" s="6" t="n">
-        <v>40.42</v>
+        <v>109.1</v>
       </c>
       <c r="AB42" s="6" t="n">
-        <v>38.12</v>
+        <v>109.03</v>
       </c>
       <c r="AC42" s="6" t="n">
-        <v>36.5</v>
+        <v>108.75</v>
       </c>
       <c r="AD42" s="6" t="n">
-        <v>36.72</v>
+        <v>108.88</v>
       </c>
       <c r="AE42" s="6" t="n">
-        <v>36.95</v>
+        <v>108.47</v>
       </c>
       <c r="AF42" s="6" t="n">
-        <v>39.42</v>
+        <v>108.88</v>
       </c>
       <c r="AG42" s="6" t="n">
-        <v>37.27</v>
+        <v>109.2</v>
       </c>
       <c r="AH42" s="6" t="n">
-        <v>38.46</v>
+        <v>109.02</v>
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
@@ -3852,23 +3632,23 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TELEAMAZONAS</t>
+          <t>CADENA ECUATORIANA DE TELEVISIO</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>211.25</v>
+        <v>181.25</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>92.83</v>
+        <v>38.13</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>96.5</v>
+        <v>42</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>93.18000000000001</v>
+        <v>41.13</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>92.88</v>
+        <v>41.17</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
@@ -3881,19 +3661,19 @@
         </is>
       </c>
       <c r="I43" s="6" t="n">
-        <v>92.53</v>
+        <v>36.3</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>96.27</v>
+        <v>49.5</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>93.27</v>
+        <v>37.1</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>94.75</v>
+        <v>40.53</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>96.56999999999999</v>
+        <v>50.5</v>
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
@@ -3906,61 +3686,61 @@
         </is>
       </c>
       <c r="P43" s="6" t="n">
-        <v>92.67</v>
+        <v>39.87</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>93.09999999999999</v>
+        <v>38.13</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>92.52</v>
+        <v>37.27</v>
       </c>
       <c r="S43" s="6" t="n">
-        <v>95.59999999999999</v>
+        <v>47.38</v>
       </c>
       <c r="T43" s="6" t="n">
-        <v>94.47</v>
+        <v>51.48</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>96.7</v>
+        <v>56.65</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>92.53</v>
+        <v>45.32</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>92.92</v>
+        <v>41.1</v>
       </c>
       <c r="X43" s="6" t="n">
-        <v>93.13</v>
+        <v>39.07</v>
       </c>
       <c r="Y43" s="6" t="n">
-        <v>93.31999999999999</v>
+        <v>41.78</v>
       </c>
       <c r="Z43" s="6" t="n">
-        <v>94.62</v>
+        <v>44.7</v>
       </c>
       <c r="AA43" s="6" t="n">
-        <v>93.18000000000001</v>
+        <v>42.47</v>
       </c>
       <c r="AB43" s="6" t="n">
-        <v>93.09999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="AC43" s="6" t="n">
-        <v>93.2</v>
+        <v>39.95</v>
       </c>
       <c r="AD43" s="6" t="n">
-        <v>92.87</v>
+        <v>38.4</v>
       </c>
       <c r="AE43" s="6" t="n">
-        <v>92.92</v>
+        <v>39.77</v>
       </c>
       <c r="AF43" s="6" t="n">
-        <v>93.48</v>
+        <v>41.9</v>
       </c>
       <c r="AG43" s="6" t="n">
-        <v>93.43000000000001</v>
+        <v>39.3</v>
       </c>
       <c r="AH43" s="6" t="n">
-        <v>93.8</v>
+        <v>42.16</v>
       </c>
       <c r="AI43" s="6" t="inlineStr"/>
       <c r="AJ43" s="6" t="inlineStr"/>
@@ -3969,23 +3749,23 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>UCSG TELEVISION</t>
+          <t>TELEVISION DEL PACIFICO</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>519.25</v>
+        <v>187.25</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>27.47</v>
+        <v>36.4</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>26.83</v>
+        <v>37.47</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>28.47</v>
+        <v>39.78</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>27.65</v>
+        <v>41.35</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
@@ -3998,19 +3778,19 @@
         </is>
       </c>
       <c r="I44" s="6" t="n">
-        <v>26.77</v>
+        <v>36.1</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>27.47</v>
+        <v>39</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>26.73</v>
+        <v>37.07</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>26.62</v>
+        <v>37.3</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>26.77</v>
+        <v>39.17</v>
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
@@ -4023,61 +3803,61 @@
         </is>
       </c>
       <c r="P44" s="6" t="n">
-        <v>27.73</v>
+        <v>36.13</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>26.82</v>
+        <v>36.55</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>26.38</v>
+        <v>37.55</v>
       </c>
       <c r="S44" s="6" t="n">
-        <v>27.02</v>
+        <v>37.77</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>26.75</v>
+        <v>42.85</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>27.97</v>
+        <v>43.72</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>26.12</v>
+        <v>42.25</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>26.88</v>
+        <v>39.5</v>
       </c>
       <c r="X44" s="6" t="n">
-        <v>26.98</v>
+        <v>37.32</v>
       </c>
       <c r="Y44" s="6" t="n">
-        <v>26.9</v>
+        <v>38.07</v>
       </c>
       <c r="Z44" s="6" t="n">
-        <v>35.83</v>
+        <v>37.63</v>
       </c>
       <c r="AA44" s="6" t="n">
-        <v>27.43</v>
+        <v>40.42</v>
       </c>
       <c r="AB44" s="6" t="n">
-        <v>26.72</v>
+        <v>38.12</v>
       </c>
       <c r="AC44" s="6" t="n">
-        <v>26.77</v>
+        <v>36.5</v>
       </c>
       <c r="AD44" s="6" t="n">
-        <v>26.87</v>
+        <v>36.72</v>
       </c>
       <c r="AE44" s="6" t="n">
-        <v>28.92</v>
+        <v>36.95</v>
       </c>
       <c r="AF44" s="6" t="n">
-        <v>27.12</v>
+        <v>39.42</v>
       </c>
       <c r="AG44" s="6" t="n">
-        <v>26.6</v>
+        <v>37.27</v>
       </c>
       <c r="AH44" s="6" t="n">
-        <v>27.43</v>
+        <v>38.46</v>
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
@@ -4086,23 +3866,23 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>SONOVISIÓN TV</t>
+          <t>TELEAMAZONAS</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>543.25</v>
+        <v>211.25</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>28.37</v>
+        <v>92.83</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>27.92</v>
+        <v>96.5</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>27.95</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>27.78</v>
+        <v>92.88</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
@@ -4115,19 +3895,19 @@
         </is>
       </c>
       <c r="I45" s="6" t="n">
-        <v>27.37</v>
+        <v>92.53</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>27.83</v>
+        <v>96.27</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>27.77</v>
+        <v>93.27</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>28.52</v>
+        <v>94.75</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>28.13</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
@@ -4140,61 +3920,61 @@
         </is>
       </c>
       <c r="P45" s="6" t="n">
-        <v>27.4</v>
+        <v>92.67</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>27.75</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>27.68</v>
+        <v>92.52</v>
       </c>
       <c r="S45" s="6" t="n">
-        <v>27.72</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>28.08</v>
+        <v>94.47</v>
       </c>
       <c r="U45" s="6" t="n">
-        <v>27.73</v>
+        <v>96.7</v>
       </c>
       <c r="V45" s="6" t="n">
-        <v>28.07</v>
+        <v>92.53</v>
       </c>
       <c r="W45" s="6" t="n">
-        <v>28.58</v>
+        <v>92.92</v>
       </c>
       <c r="X45" s="6" t="n">
-        <v>28.65</v>
+        <v>93.13</v>
       </c>
       <c r="Y45" s="6" t="n">
-        <v>27.85</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="Z45" s="6" t="n">
-        <v>28.33</v>
+        <v>94.62</v>
       </c>
       <c r="AA45" s="6" t="n">
-        <v>28.08</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="AB45" s="6" t="n">
-        <v>29.27</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC45" s="6" t="n">
-        <v>28.18</v>
+        <v>93.2</v>
       </c>
       <c r="AD45" s="6" t="n">
-        <v>28.13</v>
+        <v>92.87</v>
       </c>
       <c r="AE45" s="6" t="n">
-        <v>27.93</v>
+        <v>92.92</v>
       </c>
       <c r="AF45" s="6" t="n">
-        <v>28.4</v>
+        <v>93.48</v>
       </c>
       <c r="AG45" s="6" t="n">
-        <v>27.67</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="AH45" s="6" t="n">
-        <v>28.04</v>
+        <v>93.8</v>
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
@@ -4203,23 +3983,23 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>DIGITAL TV</t>
+          <t>UCSG TELEVISION</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>555.25</v>
+        <v>519.25</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>30.87</v>
+        <v>27.47</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>35.67</v>
+        <v>26.83</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>31.3</v>
+        <v>28.47</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>30.95</v>
+        <v>27.65</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
@@ -4232,19 +4012,19 @@
         </is>
       </c>
       <c r="I46" s="6" t="n">
-        <v>29.83</v>
+        <v>26.77</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>37</v>
+        <v>27.47</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>30.7</v>
+        <v>26.73</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>32.82</v>
+        <v>26.62</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>36.93</v>
+        <v>26.77</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
@@ -4257,61 +4037,61 @@
         </is>
       </c>
       <c r="P46" s="6" t="n">
-        <v>30.17</v>
+        <v>27.73</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>30.43</v>
+        <v>26.82</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>30.48</v>
+        <v>26.38</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>35.07</v>
+        <v>27.02</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>35.13</v>
+        <v>26.75</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>38.18</v>
+        <v>27.97</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>30.97</v>
+        <v>26.12</v>
       </c>
       <c r="W46" s="6" t="n">
-        <v>29.7</v>
+        <v>26.88</v>
       </c>
       <c r="X46" s="6" t="n">
-        <v>30.2</v>
+        <v>26.98</v>
       </c>
       <c r="Y46" s="6" t="n">
-        <v>30.97</v>
+        <v>26.9</v>
       </c>
       <c r="Z46" s="6" t="n">
-        <v>34.18</v>
+        <v>35.83</v>
       </c>
       <c r="AA46" s="6" t="n">
-        <v>30.1</v>
+        <v>27.43</v>
       </c>
       <c r="AB46" s="6" t="n">
-        <v>29.78</v>
+        <v>26.72</v>
       </c>
       <c r="AC46" s="6" t="n">
-        <v>31.43</v>
+        <v>26.77</v>
       </c>
       <c r="AD46" s="6" t="n">
-        <v>30.87</v>
+        <v>26.87</v>
       </c>
       <c r="AE46" s="6" t="n">
-        <v>29.88</v>
+        <v>28.92</v>
       </c>
       <c r="AF46" s="6" t="n">
-        <v>31.67</v>
+        <v>27.12</v>
       </c>
       <c r="AG46" s="6" t="n">
-        <v>29.67</v>
+        <v>26.6</v>
       </c>
       <c r="AH46" s="6" t="n">
-        <v>32.04</v>
+        <v>27.43</v>
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
@@ -4320,23 +4100,23 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TV LEGISLATIVA NO AUTORIZADA</t>
+          <t>SONOVISIÓN TV</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>567.25</v>
+        <v>543.25</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>29.83</v>
+        <v>28.37</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>34.67</v>
+        <v>27.92</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>30.1</v>
+        <v>27.95</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>30.13</v>
+        <v>27.78</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -4349,19 +4129,19 @@
         </is>
       </c>
       <c r="I47" s="6" t="n">
-        <v>30.27</v>
+        <v>27.37</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>31.17</v>
+        <v>27.83</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>29.83</v>
+        <v>27.77</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>30.28</v>
+        <v>28.52</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>33.5</v>
+        <v>28.13</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
@@ -4374,61 +4154,61 @@
         </is>
       </c>
       <c r="P47" s="6" t="n">
-        <v>31.2</v>
+        <v>27.4</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>32.07</v>
+        <v>27.75</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>32.5</v>
+        <v>27.68</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>32.17</v>
+        <v>27.72</v>
       </c>
       <c r="T47" s="6" t="n">
-        <v>29.88</v>
+        <v>28.08</v>
       </c>
       <c r="U47" s="6" t="n">
-        <v>32.85</v>
+        <v>27.73</v>
       </c>
       <c r="V47" s="6" t="n">
-        <v>29.97</v>
+        <v>28.07</v>
       </c>
       <c r="W47" s="6" t="n">
-        <v>30.85</v>
+        <v>28.58</v>
       </c>
       <c r="X47" s="6" t="n">
-        <v>31.2</v>
+        <v>28.65</v>
       </c>
       <c r="Y47" s="6" t="n">
-        <v>30.82</v>
+        <v>27.85</v>
       </c>
       <c r="Z47" s="6" t="n">
-        <v>33.93</v>
+        <v>28.33</v>
       </c>
       <c r="AA47" s="6" t="n">
-        <v>30.57</v>
+        <v>28.08</v>
       </c>
       <c r="AB47" s="6" t="n">
-        <v>30.85</v>
+        <v>29.27</v>
       </c>
       <c r="AC47" s="6" t="n">
-        <v>32.78</v>
+        <v>28.18</v>
       </c>
       <c r="AD47" s="6" t="n">
-        <v>31.38</v>
+        <v>28.13</v>
       </c>
       <c r="AE47" s="6" t="n">
-        <v>30.18</v>
+        <v>27.93</v>
       </c>
       <c r="AF47" s="6" t="n">
-        <v>31.43</v>
+        <v>28.4</v>
       </c>
       <c r="AG47" s="6" t="n">
-        <v>30.47</v>
+        <v>27.67</v>
       </c>
       <c r="AH47" s="6" t="n">
-        <v>31.29</v>
+        <v>28.04</v>
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
@@ -4437,23 +4217,23 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>TELEATAHUALPA (RTU)</t>
+          <t>DIGITAL TV</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>579.25</v>
+        <v>555.25</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>28.7</v>
+        <v>30.87</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>33.23</v>
+        <v>35.67</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>29.02</v>
+        <v>31.3</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>28.9</v>
+        <v>30.95</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
@@ -4466,223 +4246,459 @@
         </is>
       </c>
       <c r="I48" s="6" t="n">
-        <v>28.7</v>
+        <v>29.83</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>28.6</v>
+        <v>37</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>28.27</v>
+        <v>30.7</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>29.25</v>
+        <v>32.82</v>
       </c>
       <c r="M48" s="6" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="S48" s="6" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="T48" s="6" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="U48" s="6" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="V48" s="6" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="W48" s="6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="X48" s="6" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="Y48" s="6" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="Z48" s="6" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="AA48" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AB48" s="6" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="AC48" s="6" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="AD48" s="6" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="AE48" s="6" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="AF48" s="6" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="AG48" s="6" t="n">
         <v>29.67</v>
       </c>
-      <c r="N48" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O48" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v>29.18</v>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="S48" s="6" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="T48" s="6" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="U48" s="6" t="n">
-        <v>30.88</v>
-      </c>
-      <c r="V48" s="6" t="n">
-        <v>29.17</v>
-      </c>
-      <c r="W48" s="6" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="X48" s="6" t="n">
-        <v>29.23</v>
-      </c>
-      <c r="Y48" s="6" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="Z48" s="6" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="AA48" s="6" t="n">
-        <v>29.53</v>
-      </c>
-      <c r="AB48" s="6" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="AC48" s="6" t="n">
-        <v>29.28</v>
-      </c>
-      <c r="AD48" s="6" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="AE48" s="6" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="AF48" s="6" t="n">
-        <v>28.68</v>
-      </c>
-      <c r="AG48" s="6" t="n">
-        <v>29.07</v>
-      </c>
       <c r="AH48" s="6" t="n">
-        <v>29.5</v>
+        <v>32.04</v>
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
       <c r="AK48" s="7" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TV LEGISLATIVA NO AUTORIZADA</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>567.25</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="S49" s="6" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="T49" s="6" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="U49" s="6" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="V49" s="6" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="W49" s="6" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="X49" s="6" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="Y49" s="6" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="Z49" s="6" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="AA49" s="6" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="AB49" s="6" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="AC49" s="6" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="AD49" s="6" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="AE49" s="6" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="AF49" s="6" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="AG49" s="6" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="AH49" s="6" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="AI49" s="6" t="inlineStr"/>
+      <c r="AJ49" s="6" t="inlineStr"/>
+      <c r="AK49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>TELEATAHUALPA (RTU)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>579.25</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="S50" s="6" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="T50" s="6" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="U50" s="6" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="V50" s="6" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="W50" s="6" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="X50" s="6" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="Y50" s="6" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="Z50" s="6" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="AA50" s="6" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="AB50" s="6" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="AC50" s="6" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="AD50" s="6" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="AE50" s="6" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AF50" s="6" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="AG50" s="6" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="AH50" s="6" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AI50" s="6" t="inlineStr"/>
+      <c r="AJ50" s="6" t="inlineStr"/>
+      <c r="AK50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>EL CIUDADANO TV NO AUTORIZADA</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n">
+      <c r="B51" s="9" t="n">
         <v>675.25</v>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C51" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D49" s="9" t="n">
+      <c r="D51" s="9" t="n">
         <v>32.42</v>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="E51" s="9" t="n">
         <v>30.38</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F51" s="9" t="n">
         <v>28.95</v>
       </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="n">
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="n">
         <v>28.37</v>
       </c>
-      <c r="J49" s="9" t="n">
+      <c r="J51" s="9" t="n">
         <v>31.97</v>
       </c>
-      <c r="K49" s="9" t="n">
+      <c r="K51" s="9" t="n">
         <v>30.47</v>
       </c>
-      <c r="L49" s="9" t="n">
+      <c r="L51" s="9" t="n">
         <v>30.97</v>
       </c>
-      <c r="M49" s="9" t="n">
+      <c r="M51" s="9" t="n">
         <v>32.63</v>
       </c>
-      <c r="N49" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O49" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="9" t="n">
+      <c r="N51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="9" t="n">
         <v>31.6</v>
       </c>
-      <c r="Q49" s="9" t="n">
+      <c r="Q51" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="R49" s="9" t="n">
+      <c r="R51" s="9" t="n">
         <v>29.88</v>
       </c>
-      <c r="S49" s="9" t="n">
+      <c r="S51" s="9" t="n">
         <v>31.85</v>
       </c>
-      <c r="T49" s="9" t="n">
+      <c r="T51" s="9" t="n">
         <v>30.62</v>
       </c>
-      <c r="U49" s="9" t="n">
+      <c r="U51" s="9" t="n">
         <v>32.62</v>
       </c>
-      <c r="V49" s="9" t="n">
+      <c r="V51" s="9" t="n">
         <v>29.52</v>
       </c>
-      <c r="W49" s="9" t="n">
+      <c r="W51" s="9" t="n">
         <v>29.95</v>
       </c>
-      <c r="X49" s="9" t="n">
+      <c r="X51" s="9" t="n">
         <v>29.62</v>
       </c>
-      <c r="Y49" s="9" t="n">
+      <c r="Y51" s="9" t="n">
         <v>30.12</v>
       </c>
-      <c r="Z49" s="9" t="n">
+      <c r="Z51" s="9" t="n">
         <v>31.13</v>
       </c>
-      <c r="AA49" s="9" t="n">
+      <c r="AA51" s="9" t="n">
         <v>30.3</v>
       </c>
-      <c r="AB49" s="9" t="n">
+      <c r="AB51" s="9" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC49" s="9" t="n">
+      <c r="AC51" s="9" t="n">
         <v>29.95</v>
       </c>
-      <c r="AD49" s="9" t="n">
+      <c r="AD51" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="AE49" s="9" t="n">
+      <c r="AE51" s="9" t="n">
         <v>29.73</v>
       </c>
-      <c r="AF49" s="9" t="n">
+      <c r="AF51" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG49" s="9" t="n">
+      <c r="AG51" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="AH49" s="9" t="n">
+      <c r="AH51" s="9" t="n">
         <v>30.39</v>
       </c>
-      <c r="AI49" s="9" t="inlineStr"/>
-      <c r="AJ49" s="9" t="inlineStr"/>
-      <c r="AK49" s="10" t="n"/>
+      <c r="AI51" s="9" t="inlineStr"/>
+      <c r="AJ51" s="9" t="inlineStr"/>
+      <c r="AK51" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A34:AK34"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="A4:AK4"/>
     <mergeCell ref="A35:AK35"/>
     <mergeCell ref="A3:AK3"/>
+    <mergeCell ref="A39:AK39"/>
     <mergeCell ref="A7:AK7"/>
+    <mergeCell ref="A38:AK38"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A33:AK33"/>
-    <mergeCell ref="A32:AK32"/>
     <mergeCell ref="A36:AK36"/>
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="A37:AK37"/>
-    <mergeCell ref="A31:AK31"/>
+    <mergeCell ref="A9:AK9"/>
+    <mergeCell ref="A8:AK8"/>
     <mergeCell ref="A6:AK6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -218,7 +218,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -268,7 +268,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -100,11 +100,60 @@
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +185,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -644,7 +696,7 @@
     <col width="8" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="23" customWidth="1" min="36" max="36"/>
+    <col width="38" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
@@ -3393,7 +3445,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK40" s="4" t="n"/>
+      <c r="AK40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3510,7 +3562,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="7" t="n"/>
+      <c r="AK41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3627,7 +3679,7 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="7" t="n"/>
+      <c r="AK42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3744,7 +3796,7 @@
       </c>
       <c r="AI43" s="6" t="inlineStr"/>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="7" t="n"/>
+      <c r="AK43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3861,7 +3913,7 @@
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="7" t="n"/>
+      <c r="AK44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3978,7 +4030,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="7" t="n"/>
+      <c r="AK45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4095,7 +4147,7 @@
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="7" t="n"/>
+      <c r="AK46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4212,7 +4264,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="7" t="n"/>
+      <c r="AK47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4329,7 +4381,7 @@
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="7" t="n"/>
+      <c r="AK48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4446,7 +4498,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="7" t="n"/>
+      <c r="AK49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4563,7 +4615,7 @@
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="7" t="n"/>
+      <c r="AK50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -4680,26 +4732,38 @@
       </c>
       <c r="AI51" s="9" t="inlineStr"/>
       <c r="AJ51" s="9" t="inlineStr"/>
-      <c r="AK51" s="10" t="n"/>
+      <c r="AK51" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A34:AK34"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="A4:AK4"/>
-    <mergeCell ref="A35:AK35"/>
+  <mergeCells count="28">
+    <mergeCell ref="AJ47:AK47"/>
     <mergeCell ref="A3:AK3"/>
-    <mergeCell ref="A39:AK39"/>
-    <mergeCell ref="A7:AK7"/>
-    <mergeCell ref="A38:AK38"/>
+    <mergeCell ref="AJ43:AK43"/>
+    <mergeCell ref="AJ50:AK50"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A33:AK33"/>
+    <mergeCell ref="AJ51:AK51"/>
+    <mergeCell ref="AJ46:AK46"/>
+    <mergeCell ref="AJ40:AK40"/>
+    <mergeCell ref="AJ42:AK42"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="A8:AK8"/>
+    <mergeCell ref="A35:AK35"/>
+    <mergeCell ref="A4:AK4"/>
+    <mergeCell ref="A38:AK38"/>
+    <mergeCell ref="AJ48:AK48"/>
+    <mergeCell ref="A9:AK9"/>
+    <mergeCell ref="A34:AK34"/>
+    <mergeCell ref="A39:AK39"/>
+    <mergeCell ref="AJ49:AK49"/>
     <mergeCell ref="A36:AK36"/>
     <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="AJ45:AK45"/>
+    <mergeCell ref="A6:AK6"/>
+    <mergeCell ref="A7:AK7"/>
+    <mergeCell ref="AJ41:AK41"/>
+    <mergeCell ref="AJ44:AK44"/>
     <mergeCell ref="A37:AK37"/>
-    <mergeCell ref="A9:AK9"/>
-    <mergeCell ref="A8:AK8"/>
-    <mergeCell ref="A6:AK6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -30,12 +30,30 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDFECE"/>
+        <bgColor rgb="FFCDFECE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFE9F"/>
+        <bgColor rgb="FFFFFE9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFD9BCB"/>
+        <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -153,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,13 +191,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -759,7 +795,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -901,16 +937,16 @@
       <c r="B11" s="6" t="n">
         <v>88.5</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>66.56999999999999</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>80.47</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>80.86</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -923,19 +959,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>80.84</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="7" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="7" t="n">
         <v>74.51000000000001</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>72.01000000000001</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>60.2</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
@@ -948,58 +984,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="7" t="n">
         <v>81.16</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="7" t="n">
         <v>80.72</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="7" t="n">
         <v>80.48</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="7" t="n">
         <v>80.53</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="7" t="n">
         <v>66.73</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" s="7" t="n">
         <v>63.59</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="V11" s="7" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="W11" s="7" t="n">
         <v>82.92</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="7" t="n">
         <v>82.81999999999999</v>
       </c>
-      <c r="Y11" s="6" t="n">
+      <c r="Y11" s="7" t="n">
         <v>75.56</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="Z11" s="7" t="n">
         <v>73.47</v>
       </c>
-      <c r="AA11" s="6" t="n">
+      <c r="AA11" s="7" t="n">
         <v>83.01000000000001</v>
       </c>
-      <c r="AB11" s="6" t="n">
+      <c r="AB11" s="7" t="n">
         <v>82.97</v>
       </c>
-      <c r="AC11" s="6" t="n">
+      <c r="AC11" s="7" t="n">
         <v>75.53</v>
       </c>
-      <c r="AD11" s="6" t="n">
+      <c r="AD11" s="7" t="n">
         <v>82.34999999999999</v>
       </c>
-      <c r="AE11" s="6" t="n">
+      <c r="AE11" s="7" t="n">
         <v>75.8</v>
       </c>
-      <c r="AF11" s="6" t="n">
+      <c r="AF11" s="7" t="n">
         <v>72.95</v>
       </c>
-      <c r="AG11" s="6" t="n">
+      <c r="AG11" s="7" t="n">
         <v>79.95</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1009,7 +1045,7 @@
         <v>172.46</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="7" t="inlineStr"/>
+      <c r="AK11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1020,16 +1056,16 @@
       <c r="B12" s="6" t="n">
         <v>89.3</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>61.59</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>60.48</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>61.1</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>62.58</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1042,19 +1078,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>61.98</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="7" t="n">
         <v>57.81</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="7" t="n">
         <v>62.01</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="M12" s="7" t="n">
         <v>64.01000000000001</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
@@ -1067,58 +1103,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="7" t="n">
         <v>63.4</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="7" t="n">
         <v>63.42</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="7" t="n">
         <v>62.89</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="S12" s="7" t="n">
         <v>62.57</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="T12" s="7" t="n">
         <v>60.43</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="U12" s="7" t="n">
         <v>62.14</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="V12" s="7" t="n">
         <v>62.39</v>
       </c>
-      <c r="W12" s="6" t="n">
+      <c r="W12" s="7" t="n">
         <v>64.04000000000001</v>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="X12" s="7" t="n">
         <v>62.5</v>
       </c>
-      <c r="Y12" s="6" t="n">
+      <c r="Y12" s="7" t="n">
         <v>62.69</v>
       </c>
-      <c r="Z12" s="6" t="n">
+      <c r="Z12" s="7" t="n">
         <v>63.32</v>
       </c>
-      <c r="AA12" s="6" t="n">
+      <c r="AA12" s="7" t="n">
         <v>63.82</v>
       </c>
-      <c r="AB12" s="6" t="n">
+      <c r="AB12" s="7" t="n">
         <v>63.92</v>
       </c>
-      <c r="AC12" s="6" t="n">
+      <c r="AC12" s="7" t="n">
         <v>62.53</v>
       </c>
-      <c r="AD12" s="6" t="n">
+      <c r="AD12" s="7" t="n">
         <v>62.72</v>
       </c>
-      <c r="AE12" s="6" t="n">
+      <c r="AE12" s="7" t="n">
         <v>62.31</v>
       </c>
-      <c r="AF12" s="6" t="n">
+      <c r="AF12" s="7" t="n">
         <v>62.48</v>
       </c>
-      <c r="AG12" s="6" t="n">
+      <c r="AG12" s="7" t="n">
         <v>77.42</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1128,7 +1164,7 @@
         <v>205.41</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="7" t="inlineStr"/>
+      <c r="AK12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1139,16 +1175,16 @@
       <c r="B13" s="6" t="n">
         <v>89.7</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="9" t="n">
         <v>45.5</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="10" t="n">
         <v>41.8</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="9" t="n">
         <v>50.04</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>52.02</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1161,19 +1197,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>51.87</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="9" t="n">
         <v>43.55</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K13" s="10" t="n">
         <v>42.94</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="9" t="n">
         <v>52.16</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>52.39</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -1186,58 +1222,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="9" t="n">
         <v>51.88</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>53.01</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R13" s="9" t="n">
         <v>53.68</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>53.23</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="T13" s="9" t="n">
         <v>53.03</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>52.08</v>
       </c>
-      <c r="V13" s="6" t="n">
+      <c r="V13" s="9" t="n">
         <v>53.32</v>
       </c>
-      <c r="W13" s="6" t="n">
+      <c r="W13" s="7" t="n">
         <v>56.62</v>
       </c>
-      <c r="X13" s="6" t="n">
+      <c r="X13" s="7" t="n">
         <v>54.02</v>
       </c>
-      <c r="Y13" s="6" t="n">
+      <c r="Y13" s="9" t="n">
         <v>51.79</v>
       </c>
-      <c r="Z13" s="6" t="n">
+      <c r="Z13" s="9" t="n">
         <v>51.92</v>
       </c>
-      <c r="AA13" s="6" t="n">
+      <c r="AA13" s="7" t="n">
         <v>55.86</v>
       </c>
-      <c r="AB13" s="6" t="n">
+      <c r="AB13" s="7" t="n">
         <v>57.24</v>
       </c>
-      <c r="AC13" s="6" t="n">
+      <c r="AC13" s="9" t="n">
         <v>53.42</v>
       </c>
-      <c r="AD13" s="6" t="n">
+      <c r="AD13" s="7" t="n">
         <v>55.09</v>
       </c>
-      <c r="AE13" s="6" t="n">
+      <c r="AE13" s="9" t="n">
         <v>52.02</v>
       </c>
-      <c r="AF13" s="6" t="n">
+      <c r="AF13" s="9" t="n">
         <v>52.26</v>
       </c>
-      <c r="AG13" s="6" t="n">
+      <c r="AG13" s="7" t="n">
         <v>69.26000000000001</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1247,7 +1283,7 @@
         <v>237.33</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="7" t="inlineStr"/>
+      <c r="AK13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1258,16 +1294,16 @@
       <c r="B14" s="6" t="n">
         <v>90.5</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>109.78</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>106.81</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>108.96</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>109.08</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1280,19 +1316,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>109.52</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="7" t="n">
         <v>104.66</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>108.14</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>106.88</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>105.61</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
@@ -1305,58 +1341,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="7" t="n">
         <v>109.61</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <v>109.38</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="7" t="n">
         <v>108.96</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>109.92</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="7" t="n">
         <v>105.51</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="U14" s="7" t="n">
         <v>105.63</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="V14" s="7" t="n">
         <v>107.74</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="W14" s="7" t="n">
         <v>109.52</v>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="7" t="n">
         <v>109.3</v>
       </c>
-      <c r="Y14" s="6" t="n">
+      <c r="Y14" s="7" t="n">
         <v>107.91</v>
       </c>
-      <c r="Z14" s="6" t="n">
+      <c r="Z14" s="7" t="n">
         <v>107.72</v>
       </c>
-      <c r="AA14" s="6" t="n">
+      <c r="AA14" s="7" t="n">
         <v>110.12</v>
       </c>
-      <c r="AB14" s="6" t="n">
+      <c r="AB14" s="7" t="n">
         <v>109.82</v>
       </c>
-      <c r="AC14" s="6" t="n">
+      <c r="AC14" s="7" t="n">
         <v>107.43</v>
       </c>
-      <c r="AD14" s="6" t="n">
+      <c r="AD14" s="7" t="n">
         <v>109.26</v>
       </c>
-      <c r="AE14" s="6" t="n">
+      <c r="AE14" s="7" t="n">
         <v>107.44</v>
       </c>
-      <c r="AF14" s="6" t="n">
+      <c r="AF14" s="7" t="n">
         <v>106.69</v>
       </c>
-      <c r="AG14" s="6" t="n">
+      <c r="AG14" s="7" t="n">
         <v>109.6</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1366,7 +1402,7 @@
         <v>137.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="7" t="inlineStr"/>
+      <c r="AK14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1377,16 +1413,16 @@
       <c r="B15" s="6" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="9" t="n">
         <v>45.29</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="10" t="n">
         <v>42.04</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="9" t="n">
         <v>50.12</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>51.98</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1399,19 +1435,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>50.55</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="10" t="n">
         <v>42.94</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>43.26</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="9" t="n">
         <v>48.76</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>48.99</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
@@ -1424,58 +1460,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="7" t="n">
         <v>56.08</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" s="7" t="n">
         <v>56.57</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="7" t="n">
         <v>56.91</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="7" t="n">
         <v>76.69</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="T15" s="7" t="n">
         <v>95.5</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U15" s="7" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="V15" s="7" t="n">
         <v>95.66</v>
       </c>
-      <c r="W15" s="6" t="n">
+      <c r="W15" s="7" t="n">
         <v>97.03</v>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" s="7" t="n">
         <v>96.73999999999999</v>
       </c>
-      <c r="Y15" s="6" t="n">
+      <c r="Y15" s="7" t="n">
         <v>91.09</v>
       </c>
-      <c r="Z15" s="6" t="n">
+      <c r="Z15" s="7" t="n">
         <v>90.98999999999999</v>
       </c>
-      <c r="AA15" s="6" t="n">
+      <c r="AA15" s="7" t="n">
         <v>96.06</v>
       </c>
-      <c r="AB15" s="6" t="n">
+      <c r="AB15" s="7" t="n">
         <v>96.89</v>
       </c>
-      <c r="AC15" s="6" t="n">
+      <c r="AC15" s="7" t="n">
         <v>91.52</v>
       </c>
-      <c r="AD15" s="6" t="n">
+      <c r="AD15" s="7" t="n">
         <v>96.27</v>
       </c>
-      <c r="AE15" s="6" t="n">
+      <c r="AE15" s="7" t="n">
         <v>90.23999999999999</v>
       </c>
-      <c r="AF15" s="6" t="n">
+      <c r="AF15" s="7" t="n">
         <v>90.91</v>
       </c>
-      <c r="AG15" s="6" t="n">
+      <c r="AG15" s="7" t="n">
         <v>93.54000000000001</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1485,7 +1521,7 @@
         <v>299.96</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="7" t="inlineStr"/>
+      <c r="AK15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1496,16 +1532,16 @@
       <c r="B16" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>107.59</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>93.81</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>108.35</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>108.56</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1518,19 +1554,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>108.44</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="7" t="n">
         <v>89.39</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="7" t="n">
         <v>101.09</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="7" t="n">
         <v>99.14</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M16" s="7" t="n">
         <v>86.36</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
@@ -1543,58 +1579,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="7" t="n">
         <v>108.01</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="7" t="n">
         <v>107.68</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R16" s="7" t="n">
         <v>108.93</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <v>104.02</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="7" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="U16" s="7" t="n">
         <v>89.81</v>
       </c>
-      <c r="V16" s="6" t="n">
+      <c r="V16" s="7" t="n">
         <v>101.15</v>
       </c>
-      <c r="W16" s="6" t="n">
+      <c r="W16" s="7" t="n">
         <v>108.49</v>
       </c>
-      <c r="X16" s="6" t="n">
+      <c r="X16" s="7" t="n">
         <v>107.51</v>
       </c>
-      <c r="Y16" s="6" t="n">
+      <c r="Y16" s="7" t="n">
         <v>96.81999999999999</v>
       </c>
-      <c r="Z16" s="6" t="n">
+      <c r="Z16" s="7" t="n">
         <v>98.70999999999999</v>
       </c>
-      <c r="AA16" s="6" t="n">
+      <c r="AA16" s="7" t="n">
         <v>107.18</v>
       </c>
-      <c r="AB16" s="6" t="n">
+      <c r="AB16" s="7" t="n">
         <v>107.91</v>
       </c>
-      <c r="AC16" s="6" t="n">
+      <c r="AC16" s="7" t="n">
         <v>99.31</v>
       </c>
-      <c r="AD16" s="6" t="n">
+      <c r="AD16" s="7" t="n">
         <v>107.21</v>
       </c>
-      <c r="AE16" s="6" t="n">
+      <c r="AE16" s="7" t="n">
         <v>97.72</v>
       </c>
-      <c r="AF16" s="6" t="n">
+      <c r="AF16" s="7" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="AG16" s="6" t="n">
+      <c r="AG16" s="7" t="n">
         <v>104.34</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1604,7 +1640,7 @@
         <v>149.91</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="7" t="inlineStr"/>
+      <c r="AK16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1615,16 +1651,16 @@
       <c r="B17" s="6" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>105.74</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="7" t="n">
         <v>100.15</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>105.96</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>106.57</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1637,19 +1673,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>106.49</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="7" t="n">
         <v>99.04000000000001</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" s="7" t="n">
         <v>101.86</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="7" t="n">
         <v>101.58</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M17" s="7" t="n">
         <v>98.15000000000001</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
@@ -1662,58 +1698,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="P17" s="7" t="n">
         <v>106.69</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="7" t="n">
         <v>106.43</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="7" t="n">
         <v>107.08</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <v>102.64</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" s="7" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="U17" s="7" t="n">
         <v>98.48</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="V17" s="7" t="n">
         <v>103.04</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="W17" s="7" t="n">
         <v>107.46</v>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" s="7" t="n">
         <v>106.45</v>
       </c>
-      <c r="Y17" s="6" t="n">
+      <c r="Y17" s="7" t="n">
         <v>102.93</v>
       </c>
-      <c r="Z17" s="6" t="n">
+      <c r="Z17" s="7" t="n">
         <v>102.51</v>
       </c>
-      <c r="AA17" s="6" t="n">
+      <c r="AA17" s="7" t="n">
         <v>106.14</v>
       </c>
-      <c r="AB17" s="6" t="n">
+      <c r="AB17" s="7" t="n">
         <v>107.07</v>
       </c>
-      <c r="AC17" s="6" t="n">
+      <c r="AC17" s="7" t="n">
         <v>103.14</v>
       </c>
-      <c r="AD17" s="6" t="n">
+      <c r="AD17" s="7" t="n">
         <v>106.84</v>
       </c>
-      <c r="AE17" s="6" t="n">
+      <c r="AE17" s="7" t="n">
         <v>101.76</v>
       </c>
-      <c r="AF17" s="6" t="n">
+      <c r="AF17" s="7" t="n">
         <v>102.42</v>
       </c>
-      <c r="AG17" s="6" t="n">
+      <c r="AG17" s="7" t="n">
         <v>104.2</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1723,7 +1759,7 @@
         <v>187.17</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="7" t="inlineStr"/>
+      <c r="AK17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1734,16 +1770,16 @@
       <c r="B18" s="6" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="7" t="n">
         <v>63.02</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <v>58.38</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>67.68000000000001</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1756,19 +1792,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="7" t="n">
         <v>67.52</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="7" t="n">
         <v>58.28</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="7" t="n">
         <v>65.03</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="7" t="n">
         <v>62.27</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="M18" s="7" t="n">
         <v>58.3</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
@@ -1781,58 +1817,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P18" s="7" t="n">
         <v>65.92</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="7" t="n">
         <v>66.34999999999999</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="7" t="n">
         <v>62.22</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="7" t="n">
         <v>59.86</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="T18" s="7" t="n">
         <v>64.81</v>
       </c>
-      <c r="U18" s="6" t="n">
+      <c r="U18" s="7" t="n">
         <v>55.07</v>
       </c>
-      <c r="V18" s="6" t="n">
+      <c r="V18" s="7" t="n">
         <v>65.63</v>
       </c>
-      <c r="W18" s="6" t="n">
+      <c r="W18" s="7" t="n">
         <v>61.1</v>
       </c>
-      <c r="X18" s="6" t="n">
+      <c r="X18" s="7" t="n">
         <v>66.61</v>
       </c>
-      <c r="Y18" s="6" t="n">
+      <c r="Y18" s="7" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="Z18" s="6" t="n">
+      <c r="Z18" s="7" t="n">
         <v>60.84</v>
       </c>
-      <c r="AA18" s="6" t="n">
+      <c r="AA18" s="7" t="n">
         <v>65.91</v>
       </c>
-      <c r="AB18" s="6" t="n">
+      <c r="AB18" s="7" t="n">
         <v>63.78</v>
       </c>
-      <c r="AC18" s="6" t="n">
+      <c r="AC18" s="7" t="n">
         <v>62.94</v>
       </c>
-      <c r="AD18" s="6" t="n">
+      <c r="AD18" s="7" t="n">
         <v>66.7</v>
       </c>
-      <c r="AE18" s="6" t="n">
+      <c r="AE18" s="7" t="n">
         <v>59.84</v>
       </c>
-      <c r="AF18" s="6" t="n">
+      <c r="AF18" s="7" t="n">
         <v>63.09</v>
       </c>
-      <c r="AG18" s="6" t="n">
+      <c r="AG18" s="7" t="n">
         <v>64.59</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -1842,7 +1878,7 @@
         <v>174.55</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="7" t="inlineStr"/>
+      <c r="AK18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1853,16 +1889,16 @@
       <c r="B19" s="6" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="9" t="n">
         <v>45.01</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="10" t="n">
         <v>42.51</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="9" t="n">
         <v>47.62</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>48.7</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1875,19 +1911,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>50.16</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="9" t="n">
         <v>43.32</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>45.82</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="9" t="n">
         <v>45.42</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="M19" s="10" t="n">
         <v>42.99</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
@@ -1900,58 +1936,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="P19" s="9" t="n">
         <v>46.38</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>47.96</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="R19" s="9" t="n">
         <v>49.18</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>44.67</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="T19" s="9" t="n">
         <v>47.12</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>46.34</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="V19" s="9" t="n">
         <v>48.12</v>
       </c>
-      <c r="W19" s="6" t="n">
+      <c r="W19" s="9" t="n">
         <v>49.51</v>
       </c>
-      <c r="X19" s="6" t="n">
+      <c r="X19" s="9" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y19" s="6" t="n">
+      <c r="Y19" s="9" t="n">
         <v>44.94</v>
       </c>
-      <c r="Z19" s="6" t="n">
+      <c r="Z19" s="10" t="n">
         <v>42.99</v>
       </c>
-      <c r="AA19" s="6" t="n">
+      <c r="AA19" s="9" t="n">
         <v>49.02</v>
       </c>
-      <c r="AB19" s="6" t="n">
+      <c r="AB19" s="9" t="n">
         <v>49.04</v>
       </c>
-      <c r="AC19" s="6" t="n">
+      <c r="AC19" s="9" t="n">
         <v>46.11</v>
       </c>
-      <c r="AD19" s="6" t="n">
+      <c r="AD19" s="9" t="n">
         <v>47.42</v>
       </c>
-      <c r="AE19" s="6" t="n">
+      <c r="AE19" s="9" t="n">
         <v>44.98</v>
       </c>
-      <c r="AF19" s="6" t="n">
+      <c r="AF19" s="9" t="n">
         <v>47.28</v>
       </c>
-      <c r="AG19" s="6" t="n">
+      <c r="AG19" s="9" t="n">
         <v>46.35</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -1961,7 +1997,7 @@
         <v>499.13</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="7" t="inlineStr"/>
+      <c r="AK19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1972,16 +2008,16 @@
       <c r="B20" s="6" t="n">
         <v>97.7</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <v>89.51000000000001</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="7" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>89.38</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>91.45</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1994,19 +2030,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>90.48</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="7" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="K20" s="7" t="n">
         <v>86.26000000000001</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L20" s="7" t="n">
         <v>83.86</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="M20" s="7" t="n">
         <v>79.45</v>
       </c>
       <c r="N20" s="6" t="inlineStr">
@@ -2019,58 +2055,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P20" s="7" t="n">
         <v>90.51000000000001</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="7" t="n">
         <v>90.81</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="R20" s="7" t="n">
         <v>91.64</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="S20" s="7" t="n">
         <v>85.58</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="T20" s="7" t="n">
         <v>81.23999999999999</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="U20" s="7" t="n">
         <v>79.42</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="V20" s="7" t="n">
         <v>87.36</v>
       </c>
-      <c r="W20" s="6" t="n">
+      <c r="W20" s="7" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="X20" s="6" t="n">
+      <c r="X20" s="7" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="Y20" s="6" t="n">
+      <c r="Y20" s="7" t="n">
         <v>85.3</v>
       </c>
-      <c r="Z20" s="6" t="n">
+      <c r="Z20" s="7" t="n">
         <v>82.70999999999999</v>
       </c>
-      <c r="AA20" s="6" t="n">
+      <c r="AA20" s="7" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="AB20" s="6" t="n">
+      <c r="AB20" s="7" t="n">
         <v>92.29000000000001</v>
       </c>
-      <c r="AC20" s="6" t="n">
+      <c r="AC20" s="7" t="n">
         <v>85.56999999999999</v>
       </c>
-      <c r="AD20" s="6" t="n">
+      <c r="AD20" s="7" t="n">
         <v>91.02</v>
       </c>
-      <c r="AE20" s="6" t="n">
+      <c r="AE20" s="7" t="n">
         <v>85.31999999999999</v>
       </c>
-      <c r="AF20" s="6" t="n">
+      <c r="AF20" s="7" t="n">
         <v>82.48999999999999</v>
       </c>
-      <c r="AG20" s="6" t="n">
+      <c r="AG20" s="7" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2080,7 +2116,7 @@
         <v>112.27</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="7" t="inlineStr"/>
+      <c r="AK20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2091,16 +2127,16 @@
       <c r="B21" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>98.34</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>101.26</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>101.47</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -2113,19 +2149,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <v>103.69</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <v>100.86</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <v>103.41</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="7" t="n">
         <v>102.35</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="M21" s="7" t="n">
         <v>100.96</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
@@ -2138,58 +2174,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="7" t="n">
         <v>99.04000000000001</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="7" t="n">
         <v>103.47</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" s="7" t="n">
         <v>104</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <v>104.37</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="T21" s="7" t="n">
         <v>100.84</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U21" s="7" t="n">
         <v>101.53</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="V21" s="7" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="W21" s="6" t="n">
+      <c r="W21" s="7" t="n">
         <v>101.29</v>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" s="7" t="n">
         <v>103.64</v>
       </c>
-      <c r="Y21" s="6" t="n">
+      <c r="Y21" s="7" t="n">
         <v>100.18</v>
       </c>
-      <c r="Z21" s="6" t="n">
+      <c r="Z21" s="7" t="n">
         <v>100.08</v>
       </c>
-      <c r="AA21" s="6" t="n">
+      <c r="AA21" s="7" t="n">
         <v>100.99</v>
       </c>
-      <c r="AB21" s="6" t="n">
+      <c r="AB21" s="7" t="n">
         <v>103.89</v>
       </c>
-      <c r="AC21" s="6" t="n">
+      <c r="AC21" s="7" t="n">
         <v>105.16</v>
       </c>
-      <c r="AD21" s="6" t="n">
+      <c r="AD21" s="7" t="n">
         <v>101.01</v>
       </c>
-      <c r="AE21" s="6" t="n">
+      <c r="AE21" s="7" t="n">
         <v>102.46</v>
       </c>
-      <c r="AF21" s="6" t="n">
+      <c r="AF21" s="7" t="n">
         <v>105.29</v>
       </c>
-      <c r="AG21" s="6" t="n">
+      <c r="AG21" s="7" t="n">
         <v>99.95999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2199,7 +2235,7 @@
         <v>208.17</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="7" t="inlineStr"/>
+      <c r="AK21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2210,16 +2246,16 @@
       <c r="B22" s="6" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>99.5</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <v>95.20999999999999</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>99.42</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>101.61</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -2232,19 +2268,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <v>101.38</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <v>92.95999999999999</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K22" s="7" t="n">
         <v>96.08</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="7" t="n">
         <v>95.78</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M22" s="7" t="n">
         <v>93.04000000000001</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
@@ -2257,58 +2293,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="P22" s="7" t="n">
         <v>100.32</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" s="7" t="n">
         <v>100.12</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="R22" s="7" t="n">
         <v>101.44</v>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="S22" s="7" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="T22" s="7" t="n">
         <v>94.20999999999999</v>
       </c>
-      <c r="U22" s="6" t="n">
+      <c r="U22" s="7" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="V22" s="6" t="n">
+      <c r="V22" s="7" t="n">
         <v>97.48</v>
       </c>
-      <c r="W22" s="6" t="n">
+      <c r="W22" s="7" t="n">
         <v>101.01</v>
       </c>
-      <c r="X22" s="6" t="n">
+      <c r="X22" s="7" t="n">
         <v>100.29</v>
       </c>
-      <c r="Y22" s="6" t="n">
+      <c r="Y22" s="7" t="n">
         <v>97.31999999999999</v>
       </c>
-      <c r="Z22" s="6" t="n">
+      <c r="Z22" s="7" t="n">
         <v>96.56</v>
       </c>
-      <c r="AA22" s="6" t="n">
+      <c r="AA22" s="7" t="n">
         <v>99.92</v>
       </c>
-      <c r="AB22" s="6" t="n">
+      <c r="AB22" s="7" t="n">
         <v>101.01</v>
       </c>
-      <c r="AC22" s="6" t="n">
+      <c r="AC22" s="7" t="n">
         <v>97.25</v>
       </c>
-      <c r="AD22" s="6" t="n">
+      <c r="AD22" s="7" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="AE22" s="6" t="n">
+      <c r="AE22" s="7" t="n">
         <v>96.06999999999999</v>
       </c>
-      <c r="AF22" s="6" t="n">
+      <c r="AF22" s="7" t="n">
         <v>97</v>
       </c>
-      <c r="AG22" s="6" t="n">
+      <c r="AG22" s="7" t="n">
         <v>97.05</v>
       </c>
       <c r="AH22" s="6" t="n">
@@ -2318,7 +2354,7 @@
         <v>131.9</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="7" t="inlineStr"/>
+      <c r="AK22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2329,16 +2365,16 @@
       <c r="B23" s="6" t="n">
         <v>100.1</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="9" t="n">
         <v>47.7</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="9" t="n">
         <v>43.78</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="9" t="n">
         <v>49.55</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>51.52</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -2351,19 +2387,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>51.51</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>44.19</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L23" s="7" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M23" s="7" t="n">
         <v>107.6</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
@@ -2376,58 +2412,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="P23" s="7" t="n">
         <v>109.66</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q23" s="7" t="n">
         <v>109.71</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="R23" s="7" t="n">
         <v>110.36</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="S23" s="7" t="n">
         <v>108.43</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="T23" s="7" t="n">
         <v>108.78</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U23" s="7" t="n">
         <v>107.36</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="V23" s="7" t="n">
         <v>109.56</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="W23" s="7" t="n">
         <v>110.01</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" s="7" t="n">
         <v>109.64</v>
       </c>
-      <c r="Y23" s="6" t="n">
+      <c r="Y23" s="7" t="n">
         <v>109.68</v>
       </c>
-      <c r="Z23" s="6" t="n">
+      <c r="Z23" s="7" t="n">
         <v>109.14</v>
       </c>
-      <c r="AA23" s="6" t="n">
+      <c r="AA23" s="7" t="n">
         <v>109.69</v>
       </c>
-      <c r="AB23" s="6" t="n">
+      <c r="AB23" s="7" t="n">
         <v>109.97</v>
       </c>
-      <c r="AC23" s="6" t="n">
+      <c r="AC23" s="7" t="n">
         <v>109.84</v>
       </c>
-      <c r="AD23" s="6" t="n">
+      <c r="AD23" s="7" t="n">
         <v>109.11</v>
       </c>
-      <c r="AE23" s="6" t="n">
+      <c r="AE23" s="7" t="n">
         <v>109.33</v>
       </c>
-      <c r="AF23" s="6" t="n">
+      <c r="AF23" s="7" t="n">
         <v>109.56</v>
       </c>
-      <c r="AG23" s="6" t="n">
+      <c r="AG23" s="7" t="n">
         <v>109.65</v>
       </c>
       <c r="AH23" s="6" t="n">
@@ -2437,7 +2473,7 @@
         <v>217.44</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="7" t="inlineStr"/>
+      <c r="AK23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2448,16 +2484,16 @@
       <c r="B24" s="6" t="n">
         <v>100.5</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="7" t="n">
         <v>108.18</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <v>106.3</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>107.82</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>108.52</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -2470,19 +2506,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="7" t="n">
         <v>108.51</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="7" t="n">
         <v>106.51</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="K24" s="7" t="n">
         <v>107.64</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="L24" s="7" t="n">
         <v>107.61</v>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="M24" s="7" t="n">
         <v>106</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
@@ -2495,58 +2531,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="P24" s="7" t="n">
         <v>108.43</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" s="7" t="n">
         <v>108.12</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="R24" s="7" t="n">
         <v>108.58</v>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="S24" s="7" t="n">
         <v>107.31</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="T24" s="7" t="n">
         <v>107.6</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="U24" s="7" t="n">
         <v>107.37</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="V24" s="7" t="n">
         <v>108.86</v>
       </c>
-      <c r="W24" s="6" t="n">
+      <c r="W24" s="7" t="n">
         <v>108.52</v>
       </c>
-      <c r="X24" s="6" t="n">
+      <c r="X24" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="Y24" s="6" t="n">
+      <c r="Y24" s="7" t="n">
         <v>108.71</v>
       </c>
-      <c r="Z24" s="6" t="n">
+      <c r="Z24" s="7" t="n">
         <v>107.91</v>
       </c>
-      <c r="AA24" s="6" t="n">
+      <c r="AA24" s="7" t="n">
         <v>108.32</v>
       </c>
-      <c r="AB24" s="6" t="n">
+      <c r="AB24" s="7" t="n">
         <v>108.39</v>
       </c>
-      <c r="AC24" s="6" t="n">
+      <c r="AC24" s="7" t="n">
         <v>109.13</v>
       </c>
-      <c r="AD24" s="6" t="n">
+      <c r="AD24" s="7" t="n">
         <v>107.91</v>
       </c>
-      <c r="AE24" s="6" t="n">
+      <c r="AE24" s="7" t="n">
         <v>107.97</v>
       </c>
-      <c r="AF24" s="6" t="n">
+      <c r="AF24" s="7" t="n">
         <v>108.65</v>
       </c>
-      <c r="AG24" s="6" t="n">
+      <c r="AG24" s="7" t="n">
         <v>107.92</v>
       </c>
       <c r="AH24" s="6" t="n">
@@ -2556,7 +2592,7 @@
         <v>179.35</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="7" t="inlineStr"/>
+      <c r="AK24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2567,16 +2603,16 @@
       <c r="B25" s="6" t="n">
         <v>101.7</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="7" t="n">
         <v>99.59</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="7" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>99.61</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>100.02</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -2589,19 +2625,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <v>99.69</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="7" t="n">
         <v>98.56</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" s="7" t="n">
         <v>98.23999999999999</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" s="7" t="n">
         <v>98.36</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="M25" s="7" t="n">
         <v>97.34</v>
       </c>
       <c r="N25" s="6" t="inlineStr">
@@ -2614,58 +2650,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="P25" s="7" t="n">
         <v>100.28</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" s="7" t="n">
         <v>99.61</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="R25" s="7" t="n">
         <v>99.86</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="7" t="n">
         <v>98.62</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="T25" s="7" t="n">
         <v>97.48</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U25" s="7" t="n">
         <v>95.91</v>
       </c>
-      <c r="V25" s="6" t="n">
+      <c r="V25" s="7" t="n">
         <v>99.28</v>
       </c>
-      <c r="W25" s="6" t="n">
+      <c r="W25" s="7" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="X25" s="6" t="n">
+      <c r="X25" s="7" t="n">
         <v>100.02</v>
       </c>
-      <c r="Y25" s="6" t="n">
+      <c r="Y25" s="7" t="n">
         <v>99.62</v>
       </c>
-      <c r="Z25" s="6" t="n">
+      <c r="Z25" s="7" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="AA25" s="6" t="n">
+      <c r="AA25" s="7" t="n">
         <v>99.52</v>
       </c>
-      <c r="AB25" s="6" t="n">
+      <c r="AB25" s="7" t="n">
         <v>99.69</v>
       </c>
-      <c r="AC25" s="6" t="n">
+      <c r="AC25" s="7" t="n">
         <v>98.75</v>
       </c>
-      <c r="AD25" s="6" t="n">
+      <c r="AD25" s="7" t="n">
         <v>99.54000000000001</v>
       </c>
-      <c r="AE25" s="6" t="n">
+      <c r="AE25" s="7" t="n">
         <v>99.41</v>
       </c>
-      <c r="AF25" s="6" t="n">
+      <c r="AF25" s="7" t="n">
         <v>99.84</v>
       </c>
-      <c r="AG25" s="6" t="n">
+      <c r="AG25" s="7" t="n">
         <v>99.05</v>
       </c>
       <c r="AH25" s="6" t="n">
@@ -2675,7 +2711,7 @@
         <v>37.91</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="7" t="inlineStr"/>
+      <c r="AK25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2686,16 +2722,16 @@
       <c r="B26" s="6" t="n">
         <v>102.5</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="7" t="n">
         <v>92.06</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <v>86.98999999999999</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>92.64</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2708,19 +2744,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="7" t="n">
         <v>92.51000000000001</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="7" t="n">
         <v>86.19</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="K26" s="7" t="n">
         <v>90.39</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="L26" s="7" t="n">
         <v>87.59</v>
       </c>
-      <c r="M26" s="6" t="n">
+      <c r="M26" s="7" t="n">
         <v>80.54000000000001</v>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -2733,58 +2769,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="P26" s="7" t="n">
         <v>92.56</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" s="7" t="n">
         <v>91.94</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="R26" s="7" t="n">
         <v>92.38</v>
       </c>
-      <c r="S26" s="6" t="n">
+      <c r="S26" s="7" t="n">
         <v>89.69</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="T26" s="7" t="n">
         <v>85.63</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="U26" s="7" t="n">
         <v>79.22</v>
       </c>
-      <c r="V26" s="6" t="n">
+      <c r="V26" s="7" t="n">
         <v>90.13</v>
       </c>
-      <c r="W26" s="6" t="n">
+      <c r="W26" s="7" t="n">
         <v>92.39</v>
       </c>
-      <c r="X26" s="6" t="n">
+      <c r="X26" s="7" t="n">
         <v>92.28</v>
       </c>
-      <c r="Y26" s="6" t="n">
+      <c r="Y26" s="7" t="n">
         <v>87.91</v>
       </c>
-      <c r="Z26" s="6" t="n">
+      <c r="Z26" s="7" t="n">
         <v>87.38</v>
       </c>
-      <c r="AA26" s="6" t="n">
+      <c r="AA26" s="7" t="n">
         <v>92.01000000000001</v>
       </c>
-      <c r="AB26" s="6" t="n">
+      <c r="AB26" s="7" t="n">
         <v>92.16</v>
       </c>
-      <c r="AC26" s="6" t="n">
+      <c r="AC26" s="7" t="n">
         <v>88.69</v>
       </c>
-      <c r="AD26" s="6" t="n">
+      <c r="AD26" s="7" t="n">
         <v>92.31</v>
       </c>
-      <c r="AE26" s="6" t="n">
+      <c r="AE26" s="7" t="n">
         <v>89.11</v>
       </c>
-      <c r="AF26" s="6" t="n">
+      <c r="AF26" s="7" t="n">
         <v>89.39</v>
       </c>
-      <c r="AG26" s="6" t="n">
+      <c r="AG26" s="7" t="n">
         <v>90.84999999999999</v>
       </c>
       <c r="AH26" s="6" t="n">
@@ -2794,7 +2830,7 @@
         <v>162.72</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="7" t="inlineStr"/>
+      <c r="AK26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2805,16 +2841,16 @@
       <c r="B27" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="10" t="n">
         <v>40.55</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="10" t="n">
         <v>40.37</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="9" t="n">
         <v>45.01</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>45.64</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -2827,19 +2863,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>45.92</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="9" t="n">
         <v>44.02</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="K27" s="10" t="n">
         <v>39.78</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="L27" s="10" t="n">
         <v>42.79</v>
       </c>
-      <c r="M27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>43.6</v>
       </c>
       <c r="N27" s="6" t="inlineStr">
@@ -2852,58 +2888,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="P27" s="9" t="n">
         <v>43.68</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>44.51</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="R27" s="9" t="n">
         <v>45.51</v>
       </c>
-      <c r="S27" s="6" t="n">
+      <c r="S27" s="10" t="n">
         <v>41.6</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="T27" s="9" t="n">
         <v>47.68</v>
       </c>
-      <c r="U27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>47.97</v>
       </c>
-      <c r="V27" s="6" t="n">
+      <c r="V27" s="9" t="n">
         <v>48.11</v>
       </c>
-      <c r="W27" s="6" t="n">
+      <c r="W27" s="9" t="n">
         <v>46.76</v>
       </c>
-      <c r="X27" s="6" t="n">
+      <c r="X27" s="9" t="n">
         <v>45.13</v>
       </c>
-      <c r="Y27" s="6" t="n">
+      <c r="Y27" s="9" t="n">
         <v>43.96</v>
       </c>
-      <c r="Z27" s="6" t="n">
+      <c r="Z27" s="10" t="n">
         <v>42.04</v>
       </c>
-      <c r="AA27" s="6" t="n">
+      <c r="AA27" s="9" t="n">
         <v>46.09</v>
       </c>
-      <c r="AB27" s="6" t="n">
+      <c r="AB27" s="9" t="n">
         <v>44.94</v>
       </c>
-      <c r="AC27" s="6" t="n">
+      <c r="AC27" s="10" t="n">
         <v>42.45</v>
       </c>
-      <c r="AD27" s="6" t="n">
+      <c r="AD27" s="9" t="n">
         <v>45.12</v>
       </c>
-      <c r="AE27" s="6" t="n">
+      <c r="AE27" s="10" t="n">
         <v>42.72</v>
       </c>
-      <c r="AF27" s="6" t="n">
+      <c r="AF27" s="9" t="n">
         <v>44.48</v>
       </c>
-      <c r="AG27" s="6" t="n">
+      <c r="AG27" s="9" t="n">
         <v>46.65</v>
       </c>
       <c r="AH27" s="6" t="n">
@@ -2913,7 +2949,7 @@
         <v>499.69</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="7" t="inlineStr"/>
+      <c r="AK27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2924,16 +2960,16 @@
       <c r="B28" s="6" t="n">
         <v>104.9</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="10" t="n">
         <v>42.55</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="10" t="n">
         <v>40.56</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="9" t="n">
         <v>45.41</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>46</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2946,19 +2982,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>47.29</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="9" t="n">
         <v>43.31</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>43.66</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="L28" s="9" t="n">
         <v>43.66</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>43.85</v>
       </c>
       <c r="N28" s="6" t="inlineStr">
@@ -2971,58 +3007,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="P28" s="9" t="n">
         <v>44.41</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>46.52</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="R28" s="9" t="n">
         <v>46.61</v>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>43.24</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="T28" s="9" t="n">
         <v>47.58</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>47.44</v>
       </c>
-      <c r="V28" s="6" t="n">
+      <c r="V28" s="9" t="n">
         <v>47.52</v>
       </c>
-      <c r="W28" s="6" t="n">
+      <c r="W28" s="9" t="n">
         <v>47.36</v>
       </c>
-      <c r="X28" s="6" t="n">
+      <c r="X28" s="9" t="n">
         <v>46.7</v>
       </c>
-      <c r="Y28" s="6" t="n">
+      <c r="Y28" s="9" t="n">
         <v>43.12</v>
       </c>
-      <c r="Z28" s="6" t="n">
+      <c r="Z28" s="9" t="n">
         <v>43.08</v>
       </c>
-      <c r="AA28" s="6" t="n">
+      <c r="AA28" s="9" t="n">
         <v>46.76</v>
       </c>
-      <c r="AB28" s="6" t="n">
+      <c r="AB28" s="9" t="n">
         <v>46.58</v>
       </c>
-      <c r="AC28" s="6" t="n">
+      <c r="AC28" s="9" t="n">
         <v>44.84</v>
       </c>
-      <c r="AD28" s="6" t="n">
+      <c r="AD28" s="9" t="n">
         <v>46.04</v>
       </c>
-      <c r="AE28" s="6" t="n">
+      <c r="AE28" s="9" t="n">
         <v>44.46</v>
       </c>
-      <c r="AF28" s="6" t="n">
+      <c r="AF28" s="9" t="n">
         <v>46.29</v>
       </c>
-      <c r="AG28" s="6" t="n">
+      <c r="AG28" s="9" t="n">
         <v>47.22</v>
       </c>
       <c r="AH28" s="6" t="n">
@@ -3032,7 +3068,7 @@
         <v>499.61</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="7" t="inlineStr"/>
+      <c r="AK28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3043,16 +3079,16 @@
       <c r="B29" s="6" t="n">
         <v>106.5</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C29" s="7" t="n">
         <v>75.36</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <v>75.08</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>74.23999999999999</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>74.31999999999999</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -3065,19 +3101,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="7" t="n">
         <v>74.01000000000001</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="7" t="n">
         <v>74.62</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="K29" s="7" t="n">
         <v>75.54000000000001</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="L29" s="7" t="n">
         <v>74.73</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="M29" s="7" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="N29" s="6" t="inlineStr">
@@ -3090,58 +3126,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="P29" s="7" t="n">
         <v>74.02</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="Q29" s="7" t="n">
         <v>73.97</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="R29" s="7" t="n">
         <v>74.06</v>
       </c>
-      <c r="S29" s="6" t="n">
+      <c r="S29" s="7" t="n">
         <v>74.39</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="T29" s="7" t="n">
         <v>74.88</v>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="U29" s="7" t="n">
         <v>74.45999999999999</v>
       </c>
-      <c r="V29" s="6" t="n">
+      <c r="V29" s="7" t="n">
         <v>75.29000000000001</v>
       </c>
-      <c r="W29" s="6" t="n">
+      <c r="W29" s="7" t="n">
         <v>74.34</v>
       </c>
-      <c r="X29" s="6" t="n">
+      <c r="X29" s="7" t="n">
         <v>74.42</v>
       </c>
-      <c r="Y29" s="6" t="n">
+      <c r="Y29" s="7" t="n">
         <v>73.54000000000001</v>
       </c>
-      <c r="Z29" s="6" t="n">
+      <c r="Z29" s="7" t="n">
         <v>74.66</v>
       </c>
-      <c r="AA29" s="6" t="n">
+      <c r="AA29" s="7" t="n">
         <v>74.95</v>
       </c>
-      <c r="AB29" s="6" t="n">
+      <c r="AB29" s="7" t="n">
         <v>74.91</v>
       </c>
-      <c r="AC29" s="6" t="n">
+      <c r="AC29" s="7" t="n">
         <v>74.06</v>
       </c>
-      <c r="AD29" s="6" t="n">
+      <c r="AD29" s="7" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="AE29" s="6" t="n">
+      <c r="AE29" s="7" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="AF29" s="6" t="n">
+      <c r="AF29" s="7" t="n">
         <v>73.91</v>
       </c>
-      <c r="AG29" s="6" t="n">
+      <c r="AG29" s="7" t="n">
         <v>74.38</v>
       </c>
       <c r="AH29" s="6" t="n">
@@ -3151,126 +3187,126 @@
         <v>273.47</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="7" t="inlineStr"/>
+      <c r="AK29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>LA VOZ DE ARUTAM (NO AUTORIZADA)</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="12" t="n">
         <v>107.3</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="13" t="n">
         <v>43.06</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="14" t="n">
         <v>41.51</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="13" t="n">
         <v>47.48</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="13" t="n">
         <v>48.84</v>
       </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="n">
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="n">
         <v>49.17</v>
       </c>
-      <c r="J30" s="9" t="n">
+      <c r="J30" s="14" t="n">
         <v>40.76</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="14" t="n">
         <v>41.36</v>
       </c>
-      <c r="L30" s="9" t="n">
+      <c r="L30" s="13" t="n">
         <v>46.16</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="13" t="n">
         <v>43.89</v>
       </c>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" s="9" t="n">
+      <c r="N30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="13" t="n">
         <v>53.46</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="15" t="n">
         <v>54.55</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="15" t="n">
         <v>56.15</v>
       </c>
-      <c r="S30" s="9" t="n">
+      <c r="S30" s="13" t="n">
         <v>49.19</v>
       </c>
-      <c r="T30" s="9" t="n">
+      <c r="T30" s="13" t="n">
         <v>47.4</v>
       </c>
-      <c r="U30" s="9" t="n">
+      <c r="U30" s="13" t="n">
         <v>46.51</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="13" t="n">
         <v>50.82</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="15" t="n">
         <v>55.1</v>
       </c>
-      <c r="X30" s="9" t="n">
+      <c r="X30" s="15" t="n">
         <v>54.54</v>
       </c>
-      <c r="Y30" s="9" t="n">
+      <c r="Y30" s="13" t="n">
         <v>49.52</v>
       </c>
-      <c r="Z30" s="9" t="n">
+      <c r="Z30" s="13" t="n">
         <v>47.54</v>
       </c>
-      <c r="AA30" s="9" t="n">
+      <c r="AA30" s="15" t="n">
         <v>54.18</v>
       </c>
-      <c r="AB30" s="9" t="n">
+      <c r="AB30" s="15" t="n">
         <v>55.12</v>
       </c>
-      <c r="AC30" s="9" t="n">
+      <c r="AC30" s="13" t="n">
         <v>48.65</v>
       </c>
-      <c r="AD30" s="9" t="n">
+      <c r="AD30" s="13" t="n">
         <v>53.31</v>
       </c>
-      <c r="AE30" s="9" t="n">
+      <c r="AE30" s="13" t="n">
         <v>49.16</v>
       </c>
-      <c r="AF30" s="9" t="n">
+      <c r="AF30" s="13" t="n">
         <v>50.49</v>
       </c>
-      <c r="AG30" s="9" t="n">
+      <c r="AG30" s="13" t="n">
         <v>51.46</v>
       </c>
-      <c r="AH30" s="9" t="n">
+      <c r="AH30" s="12" t="n">
         <v>49.24</v>
       </c>
-      <c r="AI30" s="9" t="n">
+      <c r="AI30" s="12" t="n">
         <v>498.71</v>
       </c>
-      <c r="AJ30" s="9" t="inlineStr"/>
-      <c r="AK30" s="10" t="inlineStr"/>
+      <c r="AJ30" s="12" t="inlineStr"/>
+      <c r="AK30" s="16" t="inlineStr"/>
     </row>
     <row r="31"/>
     <row r="32"/>
@@ -3319,7 +3355,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3481,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK40" s="11" t="n"/>
+      <c r="AK40" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3456,16 +3492,16 @@
       <c r="B41" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="C41" s="7" t="n">
         <v>86.73</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="7" t="n">
         <v>82.92</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>87.48</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>87.08</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -3478,19 +3514,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I41" s="7" t="n">
         <v>87.06999999999999</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="J41" s="7" t="n">
         <v>81.53</v>
       </c>
-      <c r="K41" s="6" t="n">
+      <c r="K41" s="7" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="L41" s="7" t="n">
         <v>84.2</v>
       </c>
-      <c r="M41" s="6" t="n">
+      <c r="M41" s="7" t="n">
         <v>85.23</v>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -3503,58 +3539,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="P41" s="7" t="n">
         <v>87.17</v>
       </c>
-      <c r="Q41" s="6" t="n">
+      <c r="Q41" s="7" t="n">
         <v>87.3</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="R41" s="7" t="n">
         <v>87.05</v>
       </c>
-      <c r="S41" s="6" t="n">
+      <c r="S41" s="7" t="n">
         <v>86.67</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="T41" s="7" t="n">
         <v>84.38</v>
       </c>
-      <c r="U41" s="6" t="n">
+      <c r="U41" s="7" t="n">
         <v>84.83</v>
       </c>
-      <c r="V41" s="6" t="n">
+      <c r="V41" s="7" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="W41" s="6" t="n">
+      <c r="W41" s="7" t="n">
         <v>87.38</v>
       </c>
-      <c r="X41" s="6" t="n">
+      <c r="X41" s="7" t="n">
         <v>86.98</v>
       </c>
-      <c r="Y41" s="6" t="n">
+      <c r="Y41" s="7" t="n">
         <v>87.37</v>
       </c>
-      <c r="Z41" s="6" t="n">
+      <c r="Z41" s="7" t="n">
         <v>84.87</v>
       </c>
-      <c r="AA41" s="6" t="n">
+      <c r="AA41" s="7" t="n">
         <v>86.98</v>
       </c>
-      <c r="AB41" s="6" t="n">
+      <c r="AB41" s="7" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="AC41" s="6" t="n">
+      <c r="AC41" s="7" t="n">
         <v>87.02</v>
       </c>
-      <c r="AD41" s="6" t="n">
+      <c r="AD41" s="7" t="n">
         <v>86.87</v>
       </c>
-      <c r="AE41" s="6" t="n">
+      <c r="AE41" s="7" t="n">
         <v>86.73</v>
       </c>
-      <c r="AF41" s="6" t="n">
+      <c r="AF41" s="7" t="n">
         <v>86.87</v>
       </c>
-      <c r="AG41" s="6" t="n">
+      <c r="AG41" s="7" t="n">
         <v>86.90000000000001</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -3562,7 +3598,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="12" t="n"/>
+      <c r="AK41" s="18" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3573,16 +3609,16 @@
       <c r="B42" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C42" s="7" t="n">
         <v>108.83</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="7" t="n">
         <v>109.62</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>109.3</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="7" t="n">
         <v>109.05</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -3595,19 +3631,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" s="7" t="n">
         <v>108.47</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" s="7" t="n">
         <v>109.17</v>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="K42" s="7" t="n">
         <v>108.9</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="L42" s="7" t="n">
         <v>108.75</v>
       </c>
-      <c r="M42" s="6" t="n">
+      <c r="M42" s="7" t="n">
         <v>108.4</v>
       </c>
       <c r="N42" s="6" t="inlineStr">
@@ -3620,58 +3656,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="P42" s="7" t="n">
         <v>109.07</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="Q42" s="7" t="n">
         <v>109.23</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="R42" s="7" t="n">
         <v>109.03</v>
       </c>
-      <c r="S42" s="6" t="n">
+      <c r="S42" s="7" t="n">
         <v>110.05</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="T42" s="7" t="n">
         <v>109.6</v>
       </c>
-      <c r="U42" s="6" t="n">
+      <c r="U42" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="V42" s="6" t="n">
+      <c r="V42" s="7" t="n">
         <v>108.9</v>
       </c>
-      <c r="W42" s="6" t="n">
+      <c r="W42" s="7" t="n">
         <v>109.3</v>
       </c>
-      <c r="X42" s="6" t="n">
+      <c r="X42" s="7" t="n">
         <v>109.07</v>
       </c>
-      <c r="Y42" s="6" t="n">
+      <c r="Y42" s="7" t="n">
         <v>108.78</v>
       </c>
-      <c r="Z42" s="6" t="n">
+      <c r="Z42" s="7" t="n">
         <v>108.83</v>
       </c>
-      <c r="AA42" s="6" t="n">
+      <c r="AA42" s="7" t="n">
         <v>109.1</v>
       </c>
-      <c r="AB42" s="6" t="n">
+      <c r="AB42" s="7" t="n">
         <v>109.03</v>
       </c>
-      <c r="AC42" s="6" t="n">
+      <c r="AC42" s="7" t="n">
         <v>108.75</v>
       </c>
-      <c r="AD42" s="6" t="n">
+      <c r="AD42" s="7" t="n">
         <v>108.88</v>
       </c>
-      <c r="AE42" s="6" t="n">
+      <c r="AE42" s="7" t="n">
         <v>108.47</v>
       </c>
-      <c r="AF42" s="6" t="n">
+      <c r="AF42" s="7" t="n">
         <v>108.88</v>
       </c>
-      <c r="AG42" s="6" t="n">
+      <c r="AG42" s="7" t="n">
         <v>109.2</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -3679,7 +3715,7 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="12" t="n"/>
+      <c r="AK42" s="18" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3690,16 +3726,16 @@
       <c r="B43" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="C43" s="10" t="n">
         <v>38.13</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="10" t="n">
         <v>41.13</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="10" t="n">
         <v>41.17</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -3712,19 +3748,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" s="10" t="n">
         <v>36.3</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="9" t="n">
         <v>49.5</v>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="K43" s="10" t="n">
         <v>37.1</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="L43" s="10" t="n">
         <v>40.53</v>
       </c>
-      <c r="M43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>50.5</v>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -3737,58 +3773,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="P43" s="10" t="n">
         <v>39.87</v>
       </c>
-      <c r="Q43" s="6" t="n">
+      <c r="Q43" s="10" t="n">
         <v>38.13</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="R43" s="10" t="n">
         <v>37.27</v>
       </c>
-      <c r="S43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>47.38</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="T43" s="9" t="n">
         <v>51.48</v>
       </c>
-      <c r="U43" s="6" t="n">
+      <c r="U43" s="7" t="n">
         <v>56.65</v>
       </c>
-      <c r="V43" s="6" t="n">
+      <c r="V43" s="9" t="n">
         <v>45.32</v>
       </c>
-      <c r="W43" s="6" t="n">
+      <c r="W43" s="10" t="n">
         <v>41.1</v>
       </c>
-      <c r="X43" s="6" t="n">
+      <c r="X43" s="10" t="n">
         <v>39.07</v>
       </c>
-      <c r="Y43" s="6" t="n">
+      <c r="Y43" s="10" t="n">
         <v>41.78</v>
       </c>
-      <c r="Z43" s="6" t="n">
+      <c r="Z43" s="9" t="n">
         <v>44.7</v>
       </c>
-      <c r="AA43" s="6" t="n">
+      <c r="AA43" s="10" t="n">
         <v>42.47</v>
       </c>
-      <c r="AB43" s="6" t="n">
+      <c r="AB43" s="10" t="n">
         <v>37.5</v>
       </c>
-      <c r="AC43" s="6" t="n">
+      <c r="AC43" s="10" t="n">
         <v>39.95</v>
       </c>
-      <c r="AD43" s="6" t="n">
+      <c r="AD43" s="10" t="n">
         <v>38.4</v>
       </c>
-      <c r="AE43" s="6" t="n">
+      <c r="AE43" s="10" t="n">
         <v>39.77</v>
       </c>
-      <c r="AF43" s="6" t="n">
+      <c r="AF43" s="10" t="n">
         <v>41.9</v>
       </c>
-      <c r="AG43" s="6" t="n">
+      <c r="AG43" s="10" t="n">
         <v>39.3</v>
       </c>
       <c r="AH43" s="6" t="n">
@@ -3796,7 +3832,7 @@
       </c>
       <c r="AI43" s="6" t="inlineStr"/>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="12" t="n"/>
+      <c r="AK43" s="18" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3807,16 +3843,16 @@
       <c r="B44" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="10" t="n">
         <v>36.4</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="10" t="n">
         <v>37.47</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="10" t="n">
         <v>39.78</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="10" t="n">
         <v>41.35</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3829,19 +3865,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" s="10" t="n">
         <v>36.1</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="K44" s="6" t="n">
+      <c r="K44" s="10" t="n">
         <v>37.07</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="L44" s="10" t="n">
         <v>37.3</v>
       </c>
-      <c r="M44" s="6" t="n">
+      <c r="M44" s="10" t="n">
         <v>39.17</v>
       </c>
       <c r="N44" s="6" t="inlineStr">
@@ -3854,58 +3890,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="P44" s="10" t="n">
         <v>36.13</v>
       </c>
-      <c r="Q44" s="6" t="n">
+      <c r="Q44" s="10" t="n">
         <v>36.55</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="R44" s="10" t="n">
         <v>37.55</v>
       </c>
-      <c r="S44" s="6" t="n">
+      <c r="S44" s="10" t="n">
         <v>37.77</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="T44" s="10" t="n">
         <v>42.85</v>
       </c>
-      <c r="U44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>43.72</v>
       </c>
-      <c r="V44" s="6" t="n">
+      <c r="V44" s="10" t="n">
         <v>42.25</v>
       </c>
-      <c r="W44" s="6" t="n">
+      <c r="W44" s="10" t="n">
         <v>39.5</v>
       </c>
-      <c r="X44" s="6" t="n">
+      <c r="X44" s="10" t="n">
         <v>37.32</v>
       </c>
-      <c r="Y44" s="6" t="n">
+      <c r="Y44" s="10" t="n">
         <v>38.07</v>
       </c>
-      <c r="Z44" s="6" t="n">
+      <c r="Z44" s="10" t="n">
         <v>37.63</v>
       </c>
-      <c r="AA44" s="6" t="n">
+      <c r="AA44" s="10" t="n">
         <v>40.42</v>
       </c>
-      <c r="AB44" s="6" t="n">
+      <c r="AB44" s="10" t="n">
         <v>38.12</v>
       </c>
-      <c r="AC44" s="6" t="n">
+      <c r="AC44" s="10" t="n">
         <v>36.5</v>
       </c>
-      <c r="AD44" s="6" t="n">
+      <c r="AD44" s="10" t="n">
         <v>36.72</v>
       </c>
-      <c r="AE44" s="6" t="n">
+      <c r="AE44" s="10" t="n">
         <v>36.95</v>
       </c>
-      <c r="AF44" s="6" t="n">
+      <c r="AF44" s="10" t="n">
         <v>39.42</v>
       </c>
-      <c r="AG44" s="6" t="n">
+      <c r="AG44" s="10" t="n">
         <v>37.27</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -3913,7 +3949,7 @@
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="12" t="n"/>
+      <c r="AK44" s="18" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3924,16 +3960,16 @@
       <c r="B45" s="6" t="n">
         <v>211.25</v>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="C45" s="7" t="n">
         <v>92.83</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="7" t="n">
         <v>96.5</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>92.88</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -3946,19 +3982,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" s="7" t="n">
         <v>92.53</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="7" t="n">
         <v>96.27</v>
       </c>
-      <c r="K45" s="6" t="n">
+      <c r="K45" s="7" t="n">
         <v>93.27</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="L45" s="7" t="n">
         <v>94.75</v>
       </c>
-      <c r="M45" s="6" t="n">
+      <c r="M45" s="7" t="n">
         <v>96.56999999999999</v>
       </c>
       <c r="N45" s="6" t="inlineStr">
@@ -3971,58 +4007,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="P45" s="7" t="n">
         <v>92.67</v>
       </c>
-      <c r="Q45" s="6" t="n">
+      <c r="Q45" s="7" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="R45" s="7" t="n">
         <v>92.52</v>
       </c>
-      <c r="S45" s="6" t="n">
+      <c r="S45" s="7" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="T45" s="7" t="n">
         <v>94.47</v>
       </c>
-      <c r="U45" s="6" t="n">
+      <c r="U45" s="7" t="n">
         <v>96.7</v>
       </c>
-      <c r="V45" s="6" t="n">
+      <c r="V45" s="7" t="n">
         <v>92.53</v>
       </c>
-      <c r="W45" s="6" t="n">
+      <c r="W45" s="7" t="n">
         <v>92.92</v>
       </c>
-      <c r="X45" s="6" t="n">
+      <c r="X45" s="7" t="n">
         <v>93.13</v>
       </c>
-      <c r="Y45" s="6" t="n">
+      <c r="Y45" s="7" t="n">
         <v>93.31999999999999</v>
       </c>
-      <c r="Z45" s="6" t="n">
+      <c r="Z45" s="7" t="n">
         <v>94.62</v>
       </c>
-      <c r="AA45" s="6" t="n">
+      <c r="AA45" s="7" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="AB45" s="6" t="n">
+      <c r="AB45" s="7" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="AC45" s="6" t="n">
+      <c r="AC45" s="7" t="n">
         <v>93.2</v>
       </c>
-      <c r="AD45" s="6" t="n">
+      <c r="AD45" s="7" t="n">
         <v>92.87</v>
       </c>
-      <c r="AE45" s="6" t="n">
+      <c r="AE45" s="7" t="n">
         <v>92.92</v>
       </c>
-      <c r="AF45" s="6" t="n">
+      <c r="AF45" s="7" t="n">
         <v>93.48</v>
       </c>
-      <c r="AG45" s="6" t="n">
+      <c r="AG45" s="7" t="n">
         <v>93.43000000000001</v>
       </c>
       <c r="AH45" s="6" t="n">
@@ -4030,7 +4066,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="12" t="n"/>
+      <c r="AK45" s="18" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4041,16 +4077,16 @@
       <c r="B46" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="10" t="n">
         <v>27.47</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="10" t="n">
         <v>26.83</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="10" t="n">
         <v>28.47</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="10" t="n">
         <v>27.65</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -4063,19 +4099,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I46" s="10" t="n">
         <v>26.77</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="J46" s="10" t="n">
         <v>27.47</v>
       </c>
-      <c r="K46" s="6" t="n">
+      <c r="K46" s="10" t="n">
         <v>26.73</v>
       </c>
-      <c r="L46" s="6" t="n">
+      <c r="L46" s="10" t="n">
         <v>26.62</v>
       </c>
-      <c r="M46" s="6" t="n">
+      <c r="M46" s="10" t="n">
         <v>26.77</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -4088,58 +4124,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="6" t="n">
+      <c r="P46" s="10" t="n">
         <v>27.73</v>
       </c>
-      <c r="Q46" s="6" t="n">
+      <c r="Q46" s="10" t="n">
         <v>26.82</v>
       </c>
-      <c r="R46" s="6" t="n">
+      <c r="R46" s="10" t="n">
         <v>26.38</v>
       </c>
-      <c r="S46" s="6" t="n">
+      <c r="S46" s="10" t="n">
         <v>27.02</v>
       </c>
-      <c r="T46" s="6" t="n">
+      <c r="T46" s="10" t="n">
         <v>26.75</v>
       </c>
-      <c r="U46" s="6" t="n">
+      <c r="U46" s="10" t="n">
         <v>27.97</v>
       </c>
-      <c r="V46" s="6" t="n">
+      <c r="V46" s="10" t="n">
         <v>26.12</v>
       </c>
-      <c r="W46" s="6" t="n">
+      <c r="W46" s="10" t="n">
         <v>26.88</v>
       </c>
-      <c r="X46" s="6" t="n">
+      <c r="X46" s="10" t="n">
         <v>26.98</v>
       </c>
-      <c r="Y46" s="6" t="n">
+      <c r="Y46" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="Z46" s="6" t="n">
+      <c r="Z46" s="10" t="n">
         <v>35.83</v>
       </c>
-      <c r="AA46" s="6" t="n">
+      <c r="AA46" s="10" t="n">
         <v>27.43</v>
       </c>
-      <c r="AB46" s="6" t="n">
+      <c r="AB46" s="10" t="n">
         <v>26.72</v>
       </c>
-      <c r="AC46" s="6" t="n">
+      <c r="AC46" s="10" t="n">
         <v>26.77</v>
       </c>
-      <c r="AD46" s="6" t="n">
+      <c r="AD46" s="10" t="n">
         <v>26.87</v>
       </c>
-      <c r="AE46" s="6" t="n">
+      <c r="AE46" s="10" t="n">
         <v>28.92</v>
       </c>
-      <c r="AF46" s="6" t="n">
+      <c r="AF46" s="10" t="n">
         <v>27.12</v>
       </c>
-      <c r="AG46" s="6" t="n">
+      <c r="AG46" s="10" t="n">
         <v>26.6</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4147,7 +4183,7 @@
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="12" t="n"/>
+      <c r="AK46" s="18" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4158,16 +4194,16 @@
       <c r="B47" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="C47" s="10" t="n">
         <v>28.37</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="10" t="n">
         <v>27.92</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="10" t="n">
         <v>27.95</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="10" t="n">
         <v>27.78</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -4180,19 +4216,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" s="10" t="n">
         <v>27.37</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="J47" s="10" t="n">
         <v>27.83</v>
       </c>
-      <c r="K47" s="6" t="n">
+      <c r="K47" s="10" t="n">
         <v>27.77</v>
       </c>
-      <c r="L47" s="6" t="n">
+      <c r="L47" s="10" t="n">
         <v>28.52</v>
       </c>
-      <c r="M47" s="6" t="n">
+      <c r="M47" s="10" t="n">
         <v>28.13</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -4205,58 +4241,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="6" t="n">
+      <c r="P47" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="Q47" s="6" t="n">
+      <c r="Q47" s="10" t="n">
         <v>27.75</v>
       </c>
-      <c r="R47" s="6" t="n">
+      <c r="R47" s="10" t="n">
         <v>27.68</v>
       </c>
-      <c r="S47" s="6" t="n">
+      <c r="S47" s="10" t="n">
         <v>27.72</v>
       </c>
-      <c r="T47" s="6" t="n">
+      <c r="T47" s="10" t="n">
         <v>28.08</v>
       </c>
-      <c r="U47" s="6" t="n">
+      <c r="U47" s="10" t="n">
         <v>27.73</v>
       </c>
-      <c r="V47" s="6" t="n">
+      <c r="V47" s="10" t="n">
         <v>28.07</v>
       </c>
-      <c r="W47" s="6" t="n">
+      <c r="W47" s="10" t="n">
         <v>28.58</v>
       </c>
-      <c r="X47" s="6" t="n">
+      <c r="X47" s="10" t="n">
         <v>28.65</v>
       </c>
-      <c r="Y47" s="6" t="n">
+      <c r="Y47" s="10" t="n">
         <v>27.85</v>
       </c>
-      <c r="Z47" s="6" t="n">
+      <c r="Z47" s="10" t="n">
         <v>28.33</v>
       </c>
-      <c r="AA47" s="6" t="n">
+      <c r="AA47" s="10" t="n">
         <v>28.08</v>
       </c>
-      <c r="AB47" s="6" t="n">
+      <c r="AB47" s="10" t="n">
         <v>29.27</v>
       </c>
-      <c r="AC47" s="6" t="n">
+      <c r="AC47" s="10" t="n">
         <v>28.18</v>
       </c>
-      <c r="AD47" s="6" t="n">
+      <c r="AD47" s="10" t="n">
         <v>28.13</v>
       </c>
-      <c r="AE47" s="6" t="n">
+      <c r="AE47" s="10" t="n">
         <v>27.93</v>
       </c>
-      <c r="AF47" s="6" t="n">
+      <c r="AF47" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="AG47" s="6" t="n">
+      <c r="AG47" s="10" t="n">
         <v>27.67</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -4264,7 +4300,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="12" t="n"/>
+      <c r="AK47" s="18" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4275,16 +4311,16 @@
       <c r="B48" s="6" t="n">
         <v>555.25</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="10" t="n">
         <v>30.87</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="10" t="n">
         <v>35.67</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="10" t="n">
         <v>31.3</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="10" t="n">
         <v>30.95</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -4297,19 +4333,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" s="10" t="n">
         <v>29.83</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="K48" s="10" t="n">
         <v>30.7</v>
       </c>
-      <c r="L48" s="6" t="n">
+      <c r="L48" s="10" t="n">
         <v>32.82</v>
       </c>
-      <c r="M48" s="6" t="n">
+      <c r="M48" s="10" t="n">
         <v>36.93</v>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -4322,58 +4358,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="6" t="n">
+      <c r="P48" s="10" t="n">
         <v>30.17</v>
       </c>
-      <c r="Q48" s="6" t="n">
+      <c r="Q48" s="10" t="n">
         <v>30.43</v>
       </c>
-      <c r="R48" s="6" t="n">
+      <c r="R48" s="10" t="n">
         <v>30.48</v>
       </c>
-      <c r="S48" s="6" t="n">
+      <c r="S48" s="10" t="n">
         <v>35.07</v>
       </c>
-      <c r="T48" s="6" t="n">
+      <c r="T48" s="10" t="n">
         <v>35.13</v>
       </c>
-      <c r="U48" s="6" t="n">
+      <c r="U48" s="10" t="n">
         <v>38.18</v>
       </c>
-      <c r="V48" s="6" t="n">
+      <c r="V48" s="10" t="n">
         <v>30.97</v>
       </c>
-      <c r="W48" s="6" t="n">
+      <c r="W48" s="10" t="n">
         <v>29.7</v>
       </c>
-      <c r="X48" s="6" t="n">
+      <c r="X48" s="10" t="n">
         <v>30.2</v>
       </c>
-      <c r="Y48" s="6" t="n">
+      <c r="Y48" s="10" t="n">
         <v>30.97</v>
       </c>
-      <c r="Z48" s="6" t="n">
+      <c r="Z48" s="10" t="n">
         <v>34.18</v>
       </c>
-      <c r="AA48" s="6" t="n">
+      <c r="AA48" s="10" t="n">
         <v>30.1</v>
       </c>
-      <c r="AB48" s="6" t="n">
+      <c r="AB48" s="10" t="n">
         <v>29.78</v>
       </c>
-      <c r="AC48" s="6" t="n">
+      <c r="AC48" s="10" t="n">
         <v>31.43</v>
       </c>
-      <c r="AD48" s="6" t="n">
+      <c r="AD48" s="10" t="n">
         <v>30.87</v>
       </c>
-      <c r="AE48" s="6" t="n">
+      <c r="AE48" s="10" t="n">
         <v>29.88</v>
       </c>
-      <c r="AF48" s="6" t="n">
+      <c r="AF48" s="10" t="n">
         <v>31.67</v>
       </c>
-      <c r="AG48" s="6" t="n">
+      <c r="AG48" s="10" t="n">
         <v>29.67</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -4381,7 +4417,7 @@
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="12" t="n"/>
+      <c r="AK48" s="18" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4392,16 +4428,16 @@
       <c r="B49" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="C49" s="10" t="n">
         <v>29.83</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="10" t="n">
         <v>34.67</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="10" t="n">
         <v>30.1</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="10" t="n">
         <v>30.13</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -4414,19 +4450,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" s="10" t="n">
         <v>30.27</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" s="10" t="n">
         <v>31.17</v>
       </c>
-      <c r="K49" s="6" t="n">
+      <c r="K49" s="10" t="n">
         <v>29.83</v>
       </c>
-      <c r="L49" s="6" t="n">
+      <c r="L49" s="10" t="n">
         <v>30.28</v>
       </c>
-      <c r="M49" s="6" t="n">
+      <c r="M49" s="10" t="n">
         <v>33.5</v>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -4439,58 +4475,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P49" s="6" t="n">
+      <c r="P49" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="Q49" s="6" t="n">
+      <c r="Q49" s="10" t="n">
         <v>32.07</v>
       </c>
-      <c r="R49" s="6" t="n">
+      <c r="R49" s="10" t="n">
         <v>32.5</v>
       </c>
-      <c r="S49" s="6" t="n">
+      <c r="S49" s="10" t="n">
         <v>32.17</v>
       </c>
-      <c r="T49" s="6" t="n">
+      <c r="T49" s="10" t="n">
         <v>29.88</v>
       </c>
-      <c r="U49" s="6" t="n">
+      <c r="U49" s="10" t="n">
         <v>32.85</v>
       </c>
-      <c r="V49" s="6" t="n">
+      <c r="V49" s="10" t="n">
         <v>29.97</v>
       </c>
-      <c r="W49" s="6" t="n">
+      <c r="W49" s="10" t="n">
         <v>30.85</v>
       </c>
-      <c r="X49" s="6" t="n">
+      <c r="X49" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="Y49" s="6" t="n">
+      <c r="Y49" s="10" t="n">
         <v>30.82</v>
       </c>
-      <c r="Z49" s="6" t="n">
+      <c r="Z49" s="10" t="n">
         <v>33.93</v>
       </c>
-      <c r="AA49" s="6" t="n">
+      <c r="AA49" s="10" t="n">
         <v>30.57</v>
       </c>
-      <c r="AB49" s="6" t="n">
+      <c r="AB49" s="10" t="n">
         <v>30.85</v>
       </c>
-      <c r="AC49" s="6" t="n">
+      <c r="AC49" s="10" t="n">
         <v>32.78</v>
       </c>
-      <c r="AD49" s="6" t="n">
+      <c r="AD49" s="10" t="n">
         <v>31.38</v>
       </c>
-      <c r="AE49" s="6" t="n">
+      <c r="AE49" s="10" t="n">
         <v>30.18</v>
       </c>
-      <c r="AF49" s="6" t="n">
+      <c r="AF49" s="10" t="n">
         <v>31.43</v>
       </c>
-      <c r="AG49" s="6" t="n">
+      <c r="AG49" s="10" t="n">
         <v>30.47</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -4498,7 +4534,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="12" t="n"/>
+      <c r="AK49" s="18" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4509,16 +4545,16 @@
       <c r="B50" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C50" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="10" t="n">
         <v>33.23</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="10" t="n">
         <v>29.02</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="10" t="n">
         <v>28.9</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -4531,19 +4567,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I50" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="K50" s="6" t="n">
+      <c r="K50" s="10" t="n">
         <v>28.27</v>
       </c>
-      <c r="L50" s="6" t="n">
+      <c r="L50" s="10" t="n">
         <v>29.25</v>
       </c>
-      <c r="M50" s="6" t="n">
+      <c r="M50" s="10" t="n">
         <v>29.67</v>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -4556,58 +4592,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P50" s="6" t="n">
+      <c r="P50" s="10" t="n">
         <v>28.9</v>
       </c>
-      <c r="Q50" s="6" t="n">
+      <c r="Q50" s="10" t="n">
         <v>29.18</v>
       </c>
-      <c r="R50" s="6" t="n">
+      <c r="R50" s="10" t="n">
         <v>31.72</v>
       </c>
-      <c r="S50" s="6" t="n">
+      <c r="S50" s="10" t="n">
         <v>31.28</v>
       </c>
-      <c r="T50" s="6" t="n">
+      <c r="T50" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="U50" s="6" t="n">
+      <c r="U50" s="10" t="n">
         <v>30.88</v>
       </c>
-      <c r="V50" s="6" t="n">
+      <c r="V50" s="10" t="n">
         <v>29.17</v>
       </c>
-      <c r="W50" s="6" t="n">
+      <c r="W50" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="X50" s="6" t="n">
+      <c r="X50" s="10" t="n">
         <v>29.23</v>
       </c>
-      <c r="Y50" s="6" t="n">
+      <c r="Y50" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="Z50" s="6" t="n">
+      <c r="Z50" s="10" t="n">
         <v>28.92</v>
       </c>
-      <c r="AA50" s="6" t="n">
+      <c r="AA50" s="10" t="n">
         <v>29.53</v>
       </c>
-      <c r="AB50" s="6" t="n">
+      <c r="AB50" s="10" t="n">
         <v>29.12</v>
       </c>
-      <c r="AC50" s="6" t="n">
+      <c r="AC50" s="10" t="n">
         <v>29.28</v>
       </c>
-      <c r="AD50" s="6" t="n">
+      <c r="AD50" s="10" t="n">
         <v>29.4</v>
       </c>
-      <c r="AE50" s="6" t="n">
+      <c r="AE50" s="10" t="n">
         <v>28.3</v>
       </c>
-      <c r="AF50" s="6" t="n">
+      <c r="AF50" s="10" t="n">
         <v>28.68</v>
       </c>
-      <c r="AG50" s="6" t="n">
+      <c r="AG50" s="10" t="n">
         <v>29.07</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -4615,124 +4651,124 @@
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="12" t="n"/>
+      <c r="AK50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>EL CIUDADANO TV NO AUTORIZADA</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
+      <c r="B51" s="12" t="n">
         <v>675.25</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D51" s="14" t="n">
         <v>32.42</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" s="14" t="n">
         <v>30.38</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="14" t="n">
         <v>28.95</v>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="n">
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="n">
         <v>28.37</v>
       </c>
-      <c r="J51" s="9" t="n">
+      <c r="J51" s="14" t="n">
         <v>31.97</v>
       </c>
-      <c r="K51" s="9" t="n">
+      <c r="K51" s="14" t="n">
         <v>30.47</v>
       </c>
-      <c r="L51" s="9" t="n">
+      <c r="L51" s="14" t="n">
         <v>30.97</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M51" s="14" t="n">
         <v>32.63</v>
       </c>
-      <c r="N51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="9" t="n">
+      <c r="N51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="14" t="n">
         <v>31.6</v>
       </c>
-      <c r="Q51" s="9" t="n">
+      <c r="Q51" s="14" t="n">
         <v>29.1</v>
       </c>
-      <c r="R51" s="9" t="n">
+      <c r="R51" s="14" t="n">
         <v>29.88</v>
       </c>
-      <c r="S51" s="9" t="n">
+      <c r="S51" s="14" t="n">
         <v>31.85</v>
       </c>
-      <c r="T51" s="9" t="n">
+      <c r="T51" s="14" t="n">
         <v>30.62</v>
       </c>
-      <c r="U51" s="9" t="n">
+      <c r="U51" s="14" t="n">
         <v>32.62</v>
       </c>
-      <c r="V51" s="9" t="n">
+      <c r="V51" s="14" t="n">
         <v>29.52</v>
       </c>
-      <c r="W51" s="9" t="n">
+      <c r="W51" s="14" t="n">
         <v>29.95</v>
       </c>
-      <c r="X51" s="9" t="n">
+      <c r="X51" s="14" t="n">
         <v>29.62</v>
       </c>
-      <c r="Y51" s="9" t="n">
+      <c r="Y51" s="14" t="n">
         <v>30.12</v>
       </c>
-      <c r="Z51" s="9" t="n">
+      <c r="Z51" s="14" t="n">
         <v>31.13</v>
       </c>
-      <c r="AA51" s="9" t="n">
+      <c r="AA51" s="14" t="n">
         <v>30.3</v>
       </c>
-      <c r="AB51" s="9" t="n">
+      <c r="AB51" s="14" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC51" s="9" t="n">
+      <c r="AC51" s="14" t="n">
         <v>29.95</v>
       </c>
-      <c r="AD51" s="9" t="n">
+      <c r="AD51" s="14" t="n">
         <v>28.9</v>
       </c>
-      <c r="AE51" s="9" t="n">
+      <c r="AE51" s="14" t="n">
         <v>29.73</v>
       </c>
-      <c r="AF51" s="9" t="n">
+      <c r="AF51" s="14" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG51" s="9" t="n">
+      <c r="AG51" s="14" t="n">
         <v>30.4</v>
       </c>
-      <c r="AH51" s="9" t="n">
+      <c r="AH51" s="12" t="n">
         <v>30.39</v>
       </c>
-      <c r="AI51" s="9" t="inlineStr"/>
-      <c r="AJ51" s="9" t="inlineStr"/>
-      <c r="AK51" s="13" t="n"/>
+      <c r="AI51" s="12" t="inlineStr"/>
+      <c r="AJ51" s="12" t="inlineStr"/>
+      <c r="AK51" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -30,30 +30,12 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDFECE"/>
-        <bgColor rgb="FFCDFECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFE9F"/>
-        <bgColor rgb="FFFFFE9F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFD9BCB"/>
-        <bgColor rgb="FFFD9BCB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -171,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,31 +173,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -795,7 +759,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -937,16 +901,16 @@
       <c r="B11" s="6" t="n">
         <v>88.5</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>66.56999999999999</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="6" t="n">
         <v>80.47</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>80.86</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -959,19 +923,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="6" t="n">
         <v>80.84</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="6" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" s="6" t="n">
         <v>74.51000000000001</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="6" t="n">
         <v>72.01000000000001</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="6" t="n">
         <v>60.2</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
@@ -984,58 +948,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="6" t="n">
         <v>81.16</v>
       </c>
-      <c r="Q11" s="7" t="n">
+      <c r="Q11" s="6" t="n">
         <v>80.72</v>
       </c>
-      <c r="R11" s="7" t="n">
+      <c r="R11" s="6" t="n">
         <v>80.48</v>
       </c>
-      <c r="S11" s="7" t="n">
+      <c r="S11" s="6" t="n">
         <v>80.53</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="T11" s="6" t="n">
         <v>66.73</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="6" t="n">
         <v>63.59</v>
       </c>
-      <c r="V11" s="7" t="n">
+      <c r="V11" s="6" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="W11" s="7" t="n">
+      <c r="W11" s="6" t="n">
         <v>82.92</v>
       </c>
-      <c r="X11" s="7" t="n">
+      <c r="X11" s="6" t="n">
         <v>82.81999999999999</v>
       </c>
-      <c r="Y11" s="7" t="n">
+      <c r="Y11" s="6" t="n">
         <v>75.56</v>
       </c>
-      <c r="Z11" s="7" t="n">
+      <c r="Z11" s="6" t="n">
         <v>73.47</v>
       </c>
-      <c r="AA11" s="7" t="n">
+      <c r="AA11" s="6" t="n">
         <v>83.01000000000001</v>
       </c>
-      <c r="AB11" s="7" t="n">
+      <c r="AB11" s="6" t="n">
         <v>82.97</v>
       </c>
-      <c r="AC11" s="7" t="n">
+      <c r="AC11" s="6" t="n">
         <v>75.53</v>
       </c>
-      <c r="AD11" s="7" t="n">
+      <c r="AD11" s="6" t="n">
         <v>82.34999999999999</v>
       </c>
-      <c r="AE11" s="7" t="n">
+      <c r="AE11" s="6" t="n">
         <v>75.8</v>
       </c>
-      <c r="AF11" s="7" t="n">
+      <c r="AF11" s="6" t="n">
         <v>72.95</v>
       </c>
-      <c r="AG11" s="7" t="n">
+      <c r="AG11" s="6" t="n">
         <v>79.95</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1045,7 +1009,7 @@
         <v>172.46</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1056,16 +1020,16 @@
       <c r="B12" s="6" t="n">
         <v>89.3</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>61.59</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>60.48</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="6" t="n">
         <v>61.1</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="6" t="n">
         <v>62.58</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1078,19 +1042,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="6" t="n">
         <v>61.98</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="6" t="n">
         <v>57.81</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="6" t="n">
         <v>62.01</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="6" t="n">
         <v>64.01000000000001</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
@@ -1103,58 +1067,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="P12" s="6" t="n">
         <v>63.4</v>
       </c>
-      <c r="Q12" s="7" t="n">
+      <c r="Q12" s="6" t="n">
         <v>63.42</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="R12" s="6" t="n">
         <v>62.89</v>
       </c>
-      <c r="S12" s="7" t="n">
+      <c r="S12" s="6" t="n">
         <v>62.57</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="T12" s="6" t="n">
         <v>60.43</v>
       </c>
-      <c r="U12" s="7" t="n">
+      <c r="U12" s="6" t="n">
         <v>62.14</v>
       </c>
-      <c r="V12" s="7" t="n">
+      <c r="V12" s="6" t="n">
         <v>62.39</v>
       </c>
-      <c r="W12" s="7" t="n">
+      <c r="W12" s="6" t="n">
         <v>64.04000000000001</v>
       </c>
-      <c r="X12" s="7" t="n">
+      <c r="X12" s="6" t="n">
         <v>62.5</v>
       </c>
-      <c r="Y12" s="7" t="n">
+      <c r="Y12" s="6" t="n">
         <v>62.69</v>
       </c>
-      <c r="Z12" s="7" t="n">
+      <c r="Z12" s="6" t="n">
         <v>63.32</v>
       </c>
-      <c r="AA12" s="7" t="n">
+      <c r="AA12" s="6" t="n">
         <v>63.82</v>
       </c>
-      <c r="AB12" s="7" t="n">
+      <c r="AB12" s="6" t="n">
         <v>63.92</v>
       </c>
-      <c r="AC12" s="7" t="n">
+      <c r="AC12" s="6" t="n">
         <v>62.53</v>
       </c>
-      <c r="AD12" s="7" t="n">
+      <c r="AD12" s="6" t="n">
         <v>62.72</v>
       </c>
-      <c r="AE12" s="7" t="n">
+      <c r="AE12" s="6" t="n">
         <v>62.31</v>
       </c>
-      <c r="AF12" s="7" t="n">
+      <c r="AF12" s="6" t="n">
         <v>62.48</v>
       </c>
-      <c r="AG12" s="7" t="n">
+      <c r="AG12" s="6" t="n">
         <v>77.42</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1164,7 +1128,7 @@
         <v>205.41</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1175,16 +1139,16 @@
       <c r="B13" s="6" t="n">
         <v>89.7</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="6" t="n">
         <v>45.5</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="6" t="n">
         <v>41.8</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="6" t="n">
         <v>50.04</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="6" t="n">
         <v>52.02</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1197,19 +1161,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="6" t="n">
         <v>51.87</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="6" t="n">
         <v>43.55</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K13" s="6" t="n">
         <v>42.94</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="6" t="n">
         <v>52.16</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="6" t="n">
         <v>52.39</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -1222,58 +1186,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P13" s="9" t="n">
+      <c r="P13" s="6" t="n">
         <v>51.88</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="6" t="n">
         <v>53.01</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="6" t="n">
         <v>53.68</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="6" t="n">
         <v>53.23</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="6" t="n">
         <v>53.03</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="6" t="n">
         <v>52.08</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="6" t="n">
         <v>53.32</v>
       </c>
-      <c r="W13" s="7" t="n">
+      <c r="W13" s="6" t="n">
         <v>56.62</v>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="X13" s="6" t="n">
         <v>54.02</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="6" t="n">
         <v>51.79</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="Z13" s="6" t="n">
         <v>51.92</v>
       </c>
-      <c r="AA13" s="7" t="n">
+      <c r="AA13" s="6" t="n">
         <v>55.86</v>
       </c>
-      <c r="AB13" s="7" t="n">
+      <c r="AB13" s="6" t="n">
         <v>57.24</v>
       </c>
-      <c r="AC13" s="9" t="n">
+      <c r="AC13" s="6" t="n">
         <v>53.42</v>
       </c>
-      <c r="AD13" s="7" t="n">
+      <c r="AD13" s="6" t="n">
         <v>55.09</v>
       </c>
-      <c r="AE13" s="9" t="n">
+      <c r="AE13" s="6" t="n">
         <v>52.02</v>
       </c>
-      <c r="AF13" s="9" t="n">
+      <c r="AF13" s="6" t="n">
         <v>52.26</v>
       </c>
-      <c r="AG13" s="7" t="n">
+      <c r="AG13" s="6" t="n">
         <v>69.26000000000001</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1283,7 +1247,7 @@
         <v>237.33</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1294,16 +1258,16 @@
       <c r="B14" s="6" t="n">
         <v>90.5</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>109.78</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>106.81</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="6" t="n">
         <v>108.96</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>109.08</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1316,19 +1280,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="6" t="n">
         <v>109.52</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="6" t="n">
         <v>104.66</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="6" t="n">
         <v>108.14</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="6" t="n">
         <v>106.88</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="6" t="n">
         <v>105.61</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
@@ -1341,58 +1305,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="P14" s="6" t="n">
         <v>109.61</v>
       </c>
-      <c r="Q14" s="7" t="n">
+      <c r="Q14" s="6" t="n">
         <v>109.38</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="R14" s="6" t="n">
         <v>108.96</v>
       </c>
-      <c r="S14" s="7" t="n">
+      <c r="S14" s="6" t="n">
         <v>109.92</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="T14" s="6" t="n">
         <v>105.51</v>
       </c>
-      <c r="U14" s="7" t="n">
+      <c r="U14" s="6" t="n">
         <v>105.63</v>
       </c>
-      <c r="V14" s="7" t="n">
+      <c r="V14" s="6" t="n">
         <v>107.74</v>
       </c>
-      <c r="W14" s="7" t="n">
+      <c r="W14" s="6" t="n">
         <v>109.52</v>
       </c>
-      <c r="X14" s="7" t="n">
+      <c r="X14" s="6" t="n">
         <v>109.3</v>
       </c>
-      <c r="Y14" s="7" t="n">
+      <c r="Y14" s="6" t="n">
         <v>107.91</v>
       </c>
-      <c r="Z14" s="7" t="n">
+      <c r="Z14" s="6" t="n">
         <v>107.72</v>
       </c>
-      <c r="AA14" s="7" t="n">
+      <c r="AA14" s="6" t="n">
         <v>110.12</v>
       </c>
-      <c r="AB14" s="7" t="n">
+      <c r="AB14" s="6" t="n">
         <v>109.82</v>
       </c>
-      <c r="AC14" s="7" t="n">
+      <c r="AC14" s="6" t="n">
         <v>107.43</v>
       </c>
-      <c r="AD14" s="7" t="n">
+      <c r="AD14" s="6" t="n">
         <v>109.26</v>
       </c>
-      <c r="AE14" s="7" t="n">
+      <c r="AE14" s="6" t="n">
         <v>107.44</v>
       </c>
-      <c r="AF14" s="7" t="n">
+      <c r="AF14" s="6" t="n">
         <v>106.69</v>
       </c>
-      <c r="AG14" s="7" t="n">
+      <c r="AG14" s="6" t="n">
         <v>109.6</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1402,7 +1366,7 @@
         <v>137.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1413,16 +1377,16 @@
       <c r="B15" s="6" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="6" t="n">
         <v>45.29</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="6" t="n">
         <v>42.04</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="6" t="n">
         <v>50.12</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="6" t="n">
         <v>51.98</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1435,19 +1399,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="6" t="n">
         <v>50.55</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" s="6" t="n">
         <v>42.94</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="6" t="n">
         <v>43.26</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="6" t="n">
         <v>48.76</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="6" t="n">
         <v>48.99</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
@@ -1460,58 +1424,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="P15" s="6" t="n">
         <v>56.08</v>
       </c>
-      <c r="Q15" s="7" t="n">
+      <c r="Q15" s="6" t="n">
         <v>56.57</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="R15" s="6" t="n">
         <v>56.91</v>
       </c>
-      <c r="S15" s="7" t="n">
+      <c r="S15" s="6" t="n">
         <v>76.69</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="T15" s="6" t="n">
         <v>95.5</v>
       </c>
-      <c r="U15" s="7" t="n">
+      <c r="U15" s="6" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="V15" s="7" t="n">
+      <c r="V15" s="6" t="n">
         <v>95.66</v>
       </c>
-      <c r="W15" s="7" t="n">
+      <c r="W15" s="6" t="n">
         <v>97.03</v>
       </c>
-      <c r="X15" s="7" t="n">
+      <c r="X15" s="6" t="n">
         <v>96.73999999999999</v>
       </c>
-      <c r="Y15" s="7" t="n">
+      <c r="Y15" s="6" t="n">
         <v>91.09</v>
       </c>
-      <c r="Z15" s="7" t="n">
+      <c r="Z15" s="6" t="n">
         <v>90.98999999999999</v>
       </c>
-      <c r="AA15" s="7" t="n">
+      <c r="AA15" s="6" t="n">
         <v>96.06</v>
       </c>
-      <c r="AB15" s="7" t="n">
+      <c r="AB15" s="6" t="n">
         <v>96.89</v>
       </c>
-      <c r="AC15" s="7" t="n">
+      <c r="AC15" s="6" t="n">
         <v>91.52</v>
       </c>
-      <c r="AD15" s="7" t="n">
+      <c r="AD15" s="6" t="n">
         <v>96.27</v>
       </c>
-      <c r="AE15" s="7" t="n">
+      <c r="AE15" s="6" t="n">
         <v>90.23999999999999</v>
       </c>
-      <c r="AF15" s="7" t="n">
+      <c r="AF15" s="6" t="n">
         <v>90.91</v>
       </c>
-      <c r="AG15" s="7" t="n">
+      <c r="AG15" s="6" t="n">
         <v>93.54000000000001</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1521,7 +1485,7 @@
         <v>299.96</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1532,16 +1496,16 @@
       <c r="B16" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>107.59</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>93.81</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="6" t="n">
         <v>108.35</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>108.56</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1554,19 +1518,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="6" t="n">
         <v>108.44</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="6" t="n">
         <v>89.39</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="6" t="n">
         <v>101.09</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="6" t="n">
         <v>99.14</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="6" t="n">
         <v>86.36</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
@@ -1579,58 +1543,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="P16" s="6" t="n">
         <v>108.01</v>
       </c>
-      <c r="Q16" s="7" t="n">
+      <c r="Q16" s="6" t="n">
         <v>107.68</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="R16" s="6" t="n">
         <v>108.93</v>
       </c>
-      <c r="S16" s="7" t="n">
+      <c r="S16" s="6" t="n">
         <v>104.02</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="T16" s="6" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="U16" s="7" t="n">
+      <c r="U16" s="6" t="n">
         <v>89.81</v>
       </c>
-      <c r="V16" s="7" t="n">
+      <c r="V16" s="6" t="n">
         <v>101.15</v>
       </c>
-      <c r="W16" s="7" t="n">
+      <c r="W16" s="6" t="n">
         <v>108.49</v>
       </c>
-      <c r="X16" s="7" t="n">
+      <c r="X16" s="6" t="n">
         <v>107.51</v>
       </c>
-      <c r="Y16" s="7" t="n">
+      <c r="Y16" s="6" t="n">
         <v>96.81999999999999</v>
       </c>
-      <c r="Z16" s="7" t="n">
+      <c r="Z16" s="6" t="n">
         <v>98.70999999999999</v>
       </c>
-      <c r="AA16" s="7" t="n">
+      <c r="AA16" s="6" t="n">
         <v>107.18</v>
       </c>
-      <c r="AB16" s="7" t="n">
+      <c r="AB16" s="6" t="n">
         <v>107.91</v>
       </c>
-      <c r="AC16" s="7" t="n">
+      <c r="AC16" s="6" t="n">
         <v>99.31</v>
       </c>
-      <c r="AD16" s="7" t="n">
+      <c r="AD16" s="6" t="n">
         <v>107.21</v>
       </c>
-      <c r="AE16" s="7" t="n">
+      <c r="AE16" s="6" t="n">
         <v>97.72</v>
       </c>
-      <c r="AF16" s="7" t="n">
+      <c r="AF16" s="6" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="AG16" s="7" t="n">
+      <c r="AG16" s="6" t="n">
         <v>104.34</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1640,7 +1604,7 @@
         <v>149.91</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1651,16 +1615,16 @@
       <c r="B17" s="6" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="6" t="n">
         <v>105.74</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>100.15</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="6" t="n">
         <v>105.96</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="6" t="n">
         <v>106.57</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1673,19 +1637,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="6" t="n">
         <v>106.49</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="6" t="n">
         <v>99.04000000000001</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="6" t="n">
         <v>101.86</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="6" t="n">
         <v>101.58</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="6" t="n">
         <v>98.15000000000001</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
@@ -1698,58 +1662,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="P17" s="6" t="n">
         <v>106.69</v>
       </c>
-      <c r="Q17" s="7" t="n">
+      <c r="Q17" s="6" t="n">
         <v>106.43</v>
       </c>
-      <c r="R17" s="7" t="n">
+      <c r="R17" s="6" t="n">
         <v>107.08</v>
       </c>
-      <c r="S17" s="7" t="n">
+      <c r="S17" s="6" t="n">
         <v>102.64</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="T17" s="6" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="U17" s="7" t="n">
+      <c r="U17" s="6" t="n">
         <v>98.48</v>
       </c>
-      <c r="V17" s="7" t="n">
+      <c r="V17" s="6" t="n">
         <v>103.04</v>
       </c>
-      <c r="W17" s="7" t="n">
+      <c r="W17" s="6" t="n">
         <v>107.46</v>
       </c>
-      <c r="X17" s="7" t="n">
+      <c r="X17" s="6" t="n">
         <v>106.45</v>
       </c>
-      <c r="Y17" s="7" t="n">
+      <c r="Y17" s="6" t="n">
         <v>102.93</v>
       </c>
-      <c r="Z17" s="7" t="n">
+      <c r="Z17" s="6" t="n">
         <v>102.51</v>
       </c>
-      <c r="AA17" s="7" t="n">
+      <c r="AA17" s="6" t="n">
         <v>106.14</v>
       </c>
-      <c r="AB17" s="7" t="n">
+      <c r="AB17" s="6" t="n">
         <v>107.07</v>
       </c>
-      <c r="AC17" s="7" t="n">
+      <c r="AC17" s="6" t="n">
         <v>103.14</v>
       </c>
-      <c r="AD17" s="7" t="n">
+      <c r="AD17" s="6" t="n">
         <v>106.84</v>
       </c>
-      <c r="AE17" s="7" t="n">
+      <c r="AE17" s="6" t="n">
         <v>101.76</v>
       </c>
-      <c r="AF17" s="7" t="n">
+      <c r="AF17" s="6" t="n">
         <v>102.42</v>
       </c>
-      <c r="AG17" s="7" t="n">
+      <c r="AG17" s="6" t="n">
         <v>104.2</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1759,7 +1723,7 @@
         <v>187.17</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1770,16 +1734,16 @@
       <c r="B18" s="6" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="6" t="n">
         <v>63.02</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>58.38</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="6" t="n">
         <v>67.68000000000001</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1792,19 +1756,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="6" t="n">
         <v>67.52</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="J18" s="6" t="n">
         <v>58.28</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="6" t="n">
         <v>65.03</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="6" t="n">
         <v>62.27</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="6" t="n">
         <v>58.3</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
@@ -1817,58 +1781,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="P18" s="6" t="n">
         <v>65.92</v>
       </c>
-      <c r="Q18" s="7" t="n">
+      <c r="Q18" s="6" t="n">
         <v>66.34999999999999</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="R18" s="6" t="n">
         <v>62.22</v>
       </c>
-      <c r="S18" s="7" t="n">
+      <c r="S18" s="6" t="n">
         <v>59.86</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="T18" s="6" t="n">
         <v>64.81</v>
       </c>
-      <c r="U18" s="7" t="n">
+      <c r="U18" s="6" t="n">
         <v>55.07</v>
       </c>
-      <c r="V18" s="7" t="n">
+      <c r="V18" s="6" t="n">
         <v>65.63</v>
       </c>
-      <c r="W18" s="7" t="n">
+      <c r="W18" s="6" t="n">
         <v>61.1</v>
       </c>
-      <c r="X18" s="7" t="n">
+      <c r="X18" s="6" t="n">
         <v>66.61</v>
       </c>
-      <c r="Y18" s="7" t="n">
+      <c r="Y18" s="6" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="Z18" s="7" t="n">
+      <c r="Z18" s="6" t="n">
         <v>60.84</v>
       </c>
-      <c r="AA18" s="7" t="n">
+      <c r="AA18" s="6" t="n">
         <v>65.91</v>
       </c>
-      <c r="AB18" s="7" t="n">
+      <c r="AB18" s="6" t="n">
         <v>63.78</v>
       </c>
-      <c r="AC18" s="7" t="n">
+      <c r="AC18" s="6" t="n">
         <v>62.94</v>
       </c>
-      <c r="AD18" s="7" t="n">
+      <c r="AD18" s="6" t="n">
         <v>66.7</v>
       </c>
-      <c r="AE18" s="7" t="n">
+      <c r="AE18" s="6" t="n">
         <v>59.84</v>
       </c>
-      <c r="AF18" s="7" t="n">
+      <c r="AF18" s="6" t="n">
         <v>63.09</v>
       </c>
-      <c r="AG18" s="7" t="n">
+      <c r="AG18" s="6" t="n">
         <v>64.59</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -1878,7 +1842,7 @@
         <v>174.55</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1889,16 +1853,16 @@
       <c r="B19" s="6" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="6" t="n">
         <v>45.01</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="6" t="n">
         <v>42.51</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="6" t="n">
         <v>47.62</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="6" t="n">
         <v>48.7</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1911,19 +1875,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="6" t="n">
         <v>50.16</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="6" t="n">
         <v>43.32</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="6" t="n">
         <v>45.82</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="6" t="n">
         <v>45.42</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="6" t="n">
         <v>42.99</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
@@ -1936,58 +1900,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P19" s="9" t="n">
+      <c r="P19" s="6" t="n">
         <v>46.38</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="6" t="n">
         <v>47.96</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="6" t="n">
         <v>49.18</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="6" t="n">
         <v>44.67</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="6" t="n">
         <v>47.12</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="6" t="n">
         <v>46.34</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="6" t="n">
         <v>48.12</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="6" t="n">
         <v>49.51</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" s="6" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="Y19" s="6" t="n">
         <v>44.94</v>
       </c>
-      <c r="Z19" s="10" t="n">
+      <c r="Z19" s="6" t="n">
         <v>42.99</v>
       </c>
-      <c r="AA19" s="9" t="n">
+      <c r="AA19" s="6" t="n">
         <v>49.02</v>
       </c>
-      <c r="AB19" s="9" t="n">
+      <c r="AB19" s="6" t="n">
         <v>49.04</v>
       </c>
-      <c r="AC19" s="9" t="n">
+      <c r="AC19" s="6" t="n">
         <v>46.11</v>
       </c>
-      <c r="AD19" s="9" t="n">
+      <c r="AD19" s="6" t="n">
         <v>47.42</v>
       </c>
-      <c r="AE19" s="9" t="n">
+      <c r="AE19" s="6" t="n">
         <v>44.98</v>
       </c>
-      <c r="AF19" s="9" t="n">
+      <c r="AF19" s="6" t="n">
         <v>47.28</v>
       </c>
-      <c r="AG19" s="9" t="n">
+      <c r="AG19" s="6" t="n">
         <v>46.35</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -1997,7 +1961,7 @@
         <v>499.13</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2008,16 +1972,16 @@
       <c r="B20" s="6" t="n">
         <v>97.7</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="6" t="n">
         <v>89.51000000000001</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="6" t="n">
         <v>89.38</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="6" t="n">
         <v>91.45</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -2030,19 +1994,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="6" t="n">
         <v>90.48</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="6" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K20" s="6" t="n">
         <v>86.26000000000001</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="6" t="n">
         <v>83.86</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="6" t="n">
         <v>79.45</v>
       </c>
       <c r="N20" s="6" t="inlineStr">
@@ -2055,58 +2019,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="P20" s="6" t="n">
         <v>90.51000000000001</v>
       </c>
-      <c r="Q20" s="7" t="n">
+      <c r="Q20" s="6" t="n">
         <v>90.81</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="R20" s="6" t="n">
         <v>91.64</v>
       </c>
-      <c r="S20" s="7" t="n">
+      <c r="S20" s="6" t="n">
         <v>85.58</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="T20" s="6" t="n">
         <v>81.23999999999999</v>
       </c>
-      <c r="U20" s="7" t="n">
+      <c r="U20" s="6" t="n">
         <v>79.42</v>
       </c>
-      <c r="V20" s="7" t="n">
+      <c r="V20" s="6" t="n">
         <v>87.36</v>
       </c>
-      <c r="W20" s="7" t="n">
+      <c r="W20" s="6" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="X20" s="7" t="n">
+      <c r="X20" s="6" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="Y20" s="7" t="n">
+      <c r="Y20" s="6" t="n">
         <v>85.3</v>
       </c>
-      <c r="Z20" s="7" t="n">
+      <c r="Z20" s="6" t="n">
         <v>82.70999999999999</v>
       </c>
-      <c r="AA20" s="7" t="n">
+      <c r="AA20" s="6" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="AB20" s="7" t="n">
+      <c r="AB20" s="6" t="n">
         <v>92.29000000000001</v>
       </c>
-      <c r="AC20" s="7" t="n">
+      <c r="AC20" s="6" t="n">
         <v>85.56999999999999</v>
       </c>
-      <c r="AD20" s="7" t="n">
+      <c r="AD20" s="6" t="n">
         <v>91.02</v>
       </c>
-      <c r="AE20" s="7" t="n">
+      <c r="AE20" s="6" t="n">
         <v>85.31999999999999</v>
       </c>
-      <c r="AF20" s="7" t="n">
+      <c r="AF20" s="6" t="n">
         <v>82.48999999999999</v>
       </c>
-      <c r="AG20" s="7" t="n">
+      <c r="AG20" s="6" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2116,7 +2080,7 @@
         <v>112.27</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2127,16 +2091,16 @@
       <c r="B21" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="6" t="n">
         <v>98.34</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="6" t="n">
         <v>101.26</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>101.47</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -2149,19 +2113,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="6" t="n">
         <v>103.69</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>100.86</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" s="6" t="n">
         <v>103.41</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="6" t="n">
         <v>102.35</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="6" t="n">
         <v>100.96</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
@@ -2174,58 +2138,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="P21" s="6" t="n">
         <v>99.04000000000001</v>
       </c>
-      <c r="Q21" s="7" t="n">
+      <c r="Q21" s="6" t="n">
         <v>103.47</v>
       </c>
-      <c r="R21" s="7" t="n">
+      <c r="R21" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="S21" s="7" t="n">
+      <c r="S21" s="6" t="n">
         <v>104.37</v>
       </c>
-      <c r="T21" s="7" t="n">
+      <c r="T21" s="6" t="n">
         <v>100.84</v>
       </c>
-      <c r="U21" s="7" t="n">
+      <c r="U21" s="6" t="n">
         <v>101.53</v>
       </c>
-      <c r="V21" s="7" t="n">
+      <c r="V21" s="6" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="W21" s="7" t="n">
+      <c r="W21" s="6" t="n">
         <v>101.29</v>
       </c>
-      <c r="X21" s="7" t="n">
+      <c r="X21" s="6" t="n">
         <v>103.64</v>
       </c>
-      <c r="Y21" s="7" t="n">
+      <c r="Y21" s="6" t="n">
         <v>100.18</v>
       </c>
-      <c r="Z21" s="7" t="n">
+      <c r="Z21" s="6" t="n">
         <v>100.08</v>
       </c>
-      <c r="AA21" s="7" t="n">
+      <c r="AA21" s="6" t="n">
         <v>100.99</v>
       </c>
-      <c r="AB21" s="7" t="n">
+      <c r="AB21" s="6" t="n">
         <v>103.89</v>
       </c>
-      <c r="AC21" s="7" t="n">
+      <c r="AC21" s="6" t="n">
         <v>105.16</v>
       </c>
-      <c r="AD21" s="7" t="n">
+      <c r="AD21" s="6" t="n">
         <v>101.01</v>
       </c>
-      <c r="AE21" s="7" t="n">
+      <c r="AE21" s="6" t="n">
         <v>102.46</v>
       </c>
-      <c r="AF21" s="7" t="n">
+      <c r="AF21" s="6" t="n">
         <v>105.29</v>
       </c>
-      <c r="AG21" s="7" t="n">
+      <c r="AG21" s="6" t="n">
         <v>99.95999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2235,7 +2199,7 @@
         <v>208.17</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2246,16 +2210,16 @@
       <c r="B22" s="6" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="6" t="n">
         <v>99.5</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>95.20999999999999</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="6" t="n">
         <v>99.42</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>101.61</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -2268,19 +2232,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="6" t="n">
         <v>101.38</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>92.95999999999999</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K22" s="6" t="n">
         <v>96.08</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="6" t="n">
         <v>95.78</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="6" t="n">
         <v>93.04000000000001</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
@@ -2293,58 +2257,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="P22" s="6" t="n">
         <v>100.32</v>
       </c>
-      <c r="Q22" s="7" t="n">
+      <c r="Q22" s="6" t="n">
         <v>100.12</v>
       </c>
-      <c r="R22" s="7" t="n">
+      <c r="R22" s="6" t="n">
         <v>101.44</v>
       </c>
-      <c r="S22" s="7" t="n">
+      <c r="S22" s="6" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="T22" s="7" t="n">
+      <c r="T22" s="6" t="n">
         <v>94.20999999999999</v>
       </c>
-      <c r="U22" s="7" t="n">
+      <c r="U22" s="6" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="V22" s="7" t="n">
+      <c r="V22" s="6" t="n">
         <v>97.48</v>
       </c>
-      <c r="W22" s="7" t="n">
+      <c r="W22" s="6" t="n">
         <v>101.01</v>
       </c>
-      <c r="X22" s="7" t="n">
+      <c r="X22" s="6" t="n">
         <v>100.29</v>
       </c>
-      <c r="Y22" s="7" t="n">
+      <c r="Y22" s="6" t="n">
         <v>97.31999999999999</v>
       </c>
-      <c r="Z22" s="7" t="n">
+      <c r="Z22" s="6" t="n">
         <v>96.56</v>
       </c>
-      <c r="AA22" s="7" t="n">
+      <c r="AA22" s="6" t="n">
         <v>99.92</v>
       </c>
-      <c r="AB22" s="7" t="n">
+      <c r="AB22" s="6" t="n">
         <v>101.01</v>
       </c>
-      <c r="AC22" s="7" t="n">
+      <c r="AC22" s="6" t="n">
         <v>97.25</v>
       </c>
-      <c r="AD22" s="7" t="n">
+      <c r="AD22" s="6" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="AE22" s="7" t="n">
+      <c r="AE22" s="6" t="n">
         <v>96.06999999999999</v>
       </c>
-      <c r="AF22" s="7" t="n">
+      <c r="AF22" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="AG22" s="7" t="n">
+      <c r="AG22" s="6" t="n">
         <v>97.05</v>
       </c>
       <c r="AH22" s="6" t="n">
@@ -2354,7 +2318,7 @@
         <v>131.9</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2365,16 +2329,16 @@
       <c r="B23" s="6" t="n">
         <v>100.1</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="6" t="n">
         <v>47.7</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="6" t="n">
         <v>43.78</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="6" t="n">
         <v>49.55</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="6" t="n">
         <v>51.52</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -2387,19 +2351,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="6" t="n">
         <v>51.51</v>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="J23" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="6" t="n">
         <v>44.19</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="6" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="6" t="n">
         <v>107.6</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
@@ -2412,58 +2376,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="P23" s="6" t="n">
         <v>109.66</v>
       </c>
-      <c r="Q23" s="7" t="n">
+      <c r="Q23" s="6" t="n">
         <v>109.71</v>
       </c>
-      <c r="R23" s="7" t="n">
+      <c r="R23" s="6" t="n">
         <v>110.36</v>
       </c>
-      <c r="S23" s="7" t="n">
+      <c r="S23" s="6" t="n">
         <v>108.43</v>
       </c>
-      <c r="T23" s="7" t="n">
+      <c r="T23" s="6" t="n">
         <v>108.78</v>
       </c>
-      <c r="U23" s="7" t="n">
+      <c r="U23" s="6" t="n">
         <v>107.36</v>
       </c>
-      <c r="V23" s="7" t="n">
+      <c r="V23" s="6" t="n">
         <v>109.56</v>
       </c>
-      <c r="W23" s="7" t="n">
+      <c r="W23" s="6" t="n">
         <v>110.01</v>
       </c>
-      <c r="X23" s="7" t="n">
+      <c r="X23" s="6" t="n">
         <v>109.64</v>
       </c>
-      <c r="Y23" s="7" t="n">
+      <c r="Y23" s="6" t="n">
         <v>109.68</v>
       </c>
-      <c r="Z23" s="7" t="n">
+      <c r="Z23" s="6" t="n">
         <v>109.14</v>
       </c>
-      <c r="AA23" s="7" t="n">
+      <c r="AA23" s="6" t="n">
         <v>109.69</v>
       </c>
-      <c r="AB23" s="7" t="n">
+      <c r="AB23" s="6" t="n">
         <v>109.97</v>
       </c>
-      <c r="AC23" s="7" t="n">
+      <c r="AC23" s="6" t="n">
         <v>109.84</v>
       </c>
-      <c r="AD23" s="7" t="n">
+      <c r="AD23" s="6" t="n">
         <v>109.11</v>
       </c>
-      <c r="AE23" s="7" t="n">
+      <c r="AE23" s="6" t="n">
         <v>109.33</v>
       </c>
-      <c r="AF23" s="7" t="n">
+      <c r="AF23" s="6" t="n">
         <v>109.56</v>
       </c>
-      <c r="AG23" s="7" t="n">
+      <c r="AG23" s="6" t="n">
         <v>109.65</v>
       </c>
       <c r="AH23" s="6" t="n">
@@ -2473,7 +2437,7 @@
         <v>217.44</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2484,16 +2448,16 @@
       <c r="B24" s="6" t="n">
         <v>100.5</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="6" t="n">
         <v>108.18</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>106.3</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="6" t="n">
         <v>107.82</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="6" t="n">
         <v>108.52</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -2506,19 +2470,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="6" t="n">
         <v>108.51</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="6" t="n">
         <v>106.51</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K24" s="6" t="n">
         <v>107.64</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="6" t="n">
         <v>107.61</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="6" t="n">
         <v>106</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
@@ -2531,58 +2495,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="P24" s="6" t="n">
         <v>108.43</v>
       </c>
-      <c r="Q24" s="7" t="n">
+      <c r="Q24" s="6" t="n">
         <v>108.12</v>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="R24" s="6" t="n">
         <v>108.58</v>
       </c>
-      <c r="S24" s="7" t="n">
+      <c r="S24" s="6" t="n">
         <v>107.31</v>
       </c>
-      <c r="T24" s="7" t="n">
+      <c r="T24" s="6" t="n">
         <v>107.6</v>
       </c>
-      <c r="U24" s="7" t="n">
+      <c r="U24" s="6" t="n">
         <v>107.37</v>
       </c>
-      <c r="V24" s="7" t="n">
+      <c r="V24" s="6" t="n">
         <v>108.86</v>
       </c>
-      <c r="W24" s="7" t="n">
+      <c r="W24" s="6" t="n">
         <v>108.52</v>
       </c>
-      <c r="X24" s="7" t="n">
+      <c r="X24" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="Y24" s="7" t="n">
+      <c r="Y24" s="6" t="n">
         <v>108.71</v>
       </c>
-      <c r="Z24" s="7" t="n">
+      <c r="Z24" s="6" t="n">
         <v>107.91</v>
       </c>
-      <c r="AA24" s="7" t="n">
+      <c r="AA24" s="6" t="n">
         <v>108.32</v>
       </c>
-      <c r="AB24" s="7" t="n">
+      <c r="AB24" s="6" t="n">
         <v>108.39</v>
       </c>
-      <c r="AC24" s="7" t="n">
+      <c r="AC24" s="6" t="n">
         <v>109.13</v>
       </c>
-      <c r="AD24" s="7" t="n">
+      <c r="AD24" s="6" t="n">
         <v>107.91</v>
       </c>
-      <c r="AE24" s="7" t="n">
+      <c r="AE24" s="6" t="n">
         <v>107.97</v>
       </c>
-      <c r="AF24" s="7" t="n">
+      <c r="AF24" s="6" t="n">
         <v>108.65</v>
       </c>
-      <c r="AG24" s="7" t="n">
+      <c r="AG24" s="6" t="n">
         <v>107.92</v>
       </c>
       <c r="AH24" s="6" t="n">
@@ -2592,7 +2556,7 @@
         <v>179.35</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2603,16 +2567,16 @@
       <c r="B25" s="6" t="n">
         <v>101.7</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="6" t="n">
         <v>99.59</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="6" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="6" t="n">
         <v>99.61</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="6" t="n">
         <v>100.02</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -2625,19 +2589,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="6" t="n">
         <v>99.69</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="J25" s="6" t="n">
         <v>98.56</v>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="K25" s="6" t="n">
         <v>98.23999999999999</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" s="6" t="n">
         <v>98.36</v>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="6" t="n">
         <v>97.34</v>
       </c>
       <c r="N25" s="6" t="inlineStr">
@@ -2650,58 +2614,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="P25" s="6" t="n">
         <v>100.28</v>
       </c>
-      <c r="Q25" s="7" t="n">
+      <c r="Q25" s="6" t="n">
         <v>99.61</v>
       </c>
-      <c r="R25" s="7" t="n">
+      <c r="R25" s="6" t="n">
         <v>99.86</v>
       </c>
-      <c r="S25" s="7" t="n">
+      <c r="S25" s="6" t="n">
         <v>98.62</v>
       </c>
-      <c r="T25" s="7" t="n">
+      <c r="T25" s="6" t="n">
         <v>97.48</v>
       </c>
-      <c r="U25" s="7" t="n">
+      <c r="U25" s="6" t="n">
         <v>95.91</v>
       </c>
-      <c r="V25" s="7" t="n">
+      <c r="V25" s="6" t="n">
         <v>99.28</v>
       </c>
-      <c r="W25" s="7" t="n">
+      <c r="W25" s="6" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="X25" s="7" t="n">
+      <c r="X25" s="6" t="n">
         <v>100.02</v>
       </c>
-      <c r="Y25" s="7" t="n">
+      <c r="Y25" s="6" t="n">
         <v>99.62</v>
       </c>
-      <c r="Z25" s="7" t="n">
+      <c r="Z25" s="6" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="AA25" s="7" t="n">
+      <c r="AA25" s="6" t="n">
         <v>99.52</v>
       </c>
-      <c r="AB25" s="7" t="n">
+      <c r="AB25" s="6" t="n">
         <v>99.69</v>
       </c>
-      <c r="AC25" s="7" t="n">
+      <c r="AC25" s="6" t="n">
         <v>98.75</v>
       </c>
-      <c r="AD25" s="7" t="n">
+      <c r="AD25" s="6" t="n">
         <v>99.54000000000001</v>
       </c>
-      <c r="AE25" s="7" t="n">
+      <c r="AE25" s="6" t="n">
         <v>99.41</v>
       </c>
-      <c r="AF25" s="7" t="n">
+      <c r="AF25" s="6" t="n">
         <v>99.84</v>
       </c>
-      <c r="AG25" s="7" t="n">
+      <c r="AG25" s="6" t="n">
         <v>99.05</v>
       </c>
       <c r="AH25" s="6" t="n">
@@ -2711,7 +2675,7 @@
         <v>37.91</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2722,16 +2686,16 @@
       <c r="B26" s="6" t="n">
         <v>102.5</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="6" t="n">
         <v>92.06</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>86.98999999999999</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="6" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>92.64</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2744,19 +2708,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="6" t="n">
         <v>92.51000000000001</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="6" t="n">
         <v>86.19</v>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="K26" s="6" t="n">
         <v>90.39</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="L26" s="6" t="n">
         <v>87.59</v>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="6" t="n">
         <v>80.54000000000001</v>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -2769,58 +2733,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="P26" s="6" t="n">
         <v>92.56</v>
       </c>
-      <c r="Q26" s="7" t="n">
+      <c r="Q26" s="6" t="n">
         <v>91.94</v>
       </c>
-      <c r="R26" s="7" t="n">
+      <c r="R26" s="6" t="n">
         <v>92.38</v>
       </c>
-      <c r="S26" s="7" t="n">
+      <c r="S26" s="6" t="n">
         <v>89.69</v>
       </c>
-      <c r="T26" s="7" t="n">
+      <c r="T26" s="6" t="n">
         <v>85.63</v>
       </c>
-      <c r="U26" s="7" t="n">
+      <c r="U26" s="6" t="n">
         <v>79.22</v>
       </c>
-      <c r="V26" s="7" t="n">
+      <c r="V26" s="6" t="n">
         <v>90.13</v>
       </c>
-      <c r="W26" s="7" t="n">
+      <c r="W26" s="6" t="n">
         <v>92.39</v>
       </c>
-      <c r="X26" s="7" t="n">
+      <c r="X26" s="6" t="n">
         <v>92.28</v>
       </c>
-      <c r="Y26" s="7" t="n">
+      <c r="Y26" s="6" t="n">
         <v>87.91</v>
       </c>
-      <c r="Z26" s="7" t="n">
+      <c r="Z26" s="6" t="n">
         <v>87.38</v>
       </c>
-      <c r="AA26" s="7" t="n">
+      <c r="AA26" s="6" t="n">
         <v>92.01000000000001</v>
       </c>
-      <c r="AB26" s="7" t="n">
+      <c r="AB26" s="6" t="n">
         <v>92.16</v>
       </c>
-      <c r="AC26" s="7" t="n">
+      <c r="AC26" s="6" t="n">
         <v>88.69</v>
       </c>
-      <c r="AD26" s="7" t="n">
+      <c r="AD26" s="6" t="n">
         <v>92.31</v>
       </c>
-      <c r="AE26" s="7" t="n">
+      <c r="AE26" s="6" t="n">
         <v>89.11</v>
       </c>
-      <c r="AF26" s="7" t="n">
+      <c r="AF26" s="6" t="n">
         <v>89.39</v>
       </c>
-      <c r="AG26" s="7" t="n">
+      <c r="AG26" s="6" t="n">
         <v>90.84999999999999</v>
       </c>
       <c r="AH26" s="6" t="n">
@@ -2830,7 +2794,7 @@
         <v>162.72</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2841,16 +2805,16 @@
       <c r="B27" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="6" t="n">
         <v>40.55</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="6" t="n">
         <v>40.37</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="6" t="n">
         <v>45.01</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="6" t="n">
         <v>45.64</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -2863,19 +2827,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="6" t="n">
         <v>45.92</v>
       </c>
-      <c r="J27" s="9" t="n">
+      <c r="J27" s="6" t="n">
         <v>44.02</v>
       </c>
-      <c r="K27" s="10" t="n">
+      <c r="K27" s="6" t="n">
         <v>39.78</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L27" s="6" t="n">
         <v>42.79</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="6" t="n">
         <v>43.6</v>
       </c>
       <c r="N27" s="6" t="inlineStr">
@@ -2888,58 +2852,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="6" t="n">
         <v>43.68</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="6" t="n">
         <v>44.51</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="6" t="n">
         <v>45.51</v>
       </c>
-      <c r="S27" s="10" t="n">
+      <c r="S27" s="6" t="n">
         <v>41.6</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="6" t="n">
         <v>47.68</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" s="6" t="n">
         <v>47.97</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="6" t="n">
         <v>48.11</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="6" t="n">
         <v>46.76</v>
       </c>
-      <c r="X27" s="9" t="n">
+      <c r="X27" s="6" t="n">
         <v>45.13</v>
       </c>
-      <c r="Y27" s="9" t="n">
+      <c r="Y27" s="6" t="n">
         <v>43.96</v>
       </c>
-      <c r="Z27" s="10" t="n">
+      <c r="Z27" s="6" t="n">
         <v>42.04</v>
       </c>
-      <c r="AA27" s="9" t="n">
+      <c r="AA27" s="6" t="n">
         <v>46.09</v>
       </c>
-      <c r="AB27" s="9" t="n">
+      <c r="AB27" s="6" t="n">
         <v>44.94</v>
       </c>
-      <c r="AC27" s="10" t="n">
+      <c r="AC27" s="6" t="n">
         <v>42.45</v>
       </c>
-      <c r="AD27" s="9" t="n">
+      <c r="AD27" s="6" t="n">
         <v>45.12</v>
       </c>
-      <c r="AE27" s="10" t="n">
+      <c r="AE27" s="6" t="n">
         <v>42.72</v>
       </c>
-      <c r="AF27" s="9" t="n">
+      <c r="AF27" s="6" t="n">
         <v>44.48</v>
       </c>
-      <c r="AG27" s="9" t="n">
+      <c r="AG27" s="6" t="n">
         <v>46.65</v>
       </c>
       <c r="AH27" s="6" t="n">
@@ -2949,7 +2913,7 @@
         <v>499.69</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2960,16 +2924,16 @@
       <c r="B28" s="6" t="n">
         <v>104.9</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="6" t="n">
         <v>42.55</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="6" t="n">
         <v>40.56</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="6" t="n">
         <v>45.41</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2982,19 +2946,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I28" s="6" t="n">
         <v>47.29</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="6" t="n">
         <v>43.31</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="6" t="n">
         <v>43.66</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="6" t="n">
         <v>43.66</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="6" t="n">
         <v>43.85</v>
       </c>
       <c r="N28" s="6" t="inlineStr">
@@ -3007,58 +2971,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P28" s="9" t="n">
+      <c r="P28" s="6" t="n">
         <v>44.41</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="6" t="n">
         <v>46.52</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="6" t="n">
         <v>46.61</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" s="6" t="n">
         <v>43.24</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" s="6" t="n">
         <v>47.58</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="6" t="n">
         <v>47.44</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="6" t="n">
         <v>47.52</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="6" t="n">
         <v>47.36</v>
       </c>
-      <c r="X28" s="9" t="n">
+      <c r="X28" s="6" t="n">
         <v>46.7</v>
       </c>
-      <c r="Y28" s="9" t="n">
+      <c r="Y28" s="6" t="n">
         <v>43.12</v>
       </c>
-      <c r="Z28" s="9" t="n">
+      <c r="Z28" s="6" t="n">
         <v>43.08</v>
       </c>
-      <c r="AA28" s="9" t="n">
+      <c r="AA28" s="6" t="n">
         <v>46.76</v>
       </c>
-      <c r="AB28" s="9" t="n">
+      <c r="AB28" s="6" t="n">
         <v>46.58</v>
       </c>
-      <c r="AC28" s="9" t="n">
+      <c r="AC28" s="6" t="n">
         <v>44.84</v>
       </c>
-      <c r="AD28" s="9" t="n">
+      <c r="AD28" s="6" t="n">
         <v>46.04</v>
       </c>
-      <c r="AE28" s="9" t="n">
+      <c r="AE28" s="6" t="n">
         <v>44.46</v>
       </c>
-      <c r="AF28" s="9" t="n">
+      <c r="AF28" s="6" t="n">
         <v>46.29</v>
       </c>
-      <c r="AG28" s="9" t="n">
+      <c r="AG28" s="6" t="n">
         <v>47.22</v>
       </c>
       <c r="AH28" s="6" t="n">
@@ -3068,7 +3032,7 @@
         <v>499.61</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3079,16 +3043,16 @@
       <c r="B29" s="6" t="n">
         <v>106.5</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="6" t="n">
         <v>75.36</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="6" t="n">
         <v>75.08</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="6" t="n">
         <v>74.23999999999999</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>74.31999999999999</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -3101,19 +3065,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="6" t="n">
         <v>74.01000000000001</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="J29" s="6" t="n">
         <v>74.62</v>
       </c>
-      <c r="K29" s="7" t="n">
+      <c r="K29" s="6" t="n">
         <v>75.54000000000001</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="L29" s="6" t="n">
         <v>74.73</v>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="6" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="N29" s="6" t="inlineStr">
@@ -3126,58 +3090,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="P29" s="6" t="n">
         <v>74.02</v>
       </c>
-      <c r="Q29" s="7" t="n">
+      <c r="Q29" s="6" t="n">
         <v>73.97</v>
       </c>
-      <c r="R29" s="7" t="n">
+      <c r="R29" s="6" t="n">
         <v>74.06</v>
       </c>
-      <c r="S29" s="7" t="n">
+      <c r="S29" s="6" t="n">
         <v>74.39</v>
       </c>
-      <c r="T29" s="7" t="n">
+      <c r="T29" s="6" t="n">
         <v>74.88</v>
       </c>
-      <c r="U29" s="7" t="n">
+      <c r="U29" s="6" t="n">
         <v>74.45999999999999</v>
       </c>
-      <c r="V29" s="7" t="n">
+      <c r="V29" s="6" t="n">
         <v>75.29000000000001</v>
       </c>
-      <c r="W29" s="7" t="n">
+      <c r="W29" s="6" t="n">
         <v>74.34</v>
       </c>
-      <c r="X29" s="7" t="n">
+      <c r="X29" s="6" t="n">
         <v>74.42</v>
       </c>
-      <c r="Y29" s="7" t="n">
+      <c r="Y29" s="6" t="n">
         <v>73.54000000000001</v>
       </c>
-      <c r="Z29" s="7" t="n">
+      <c r="Z29" s="6" t="n">
         <v>74.66</v>
       </c>
-      <c r="AA29" s="7" t="n">
+      <c r="AA29" s="6" t="n">
         <v>74.95</v>
       </c>
-      <c r="AB29" s="7" t="n">
+      <c r="AB29" s="6" t="n">
         <v>74.91</v>
       </c>
-      <c r="AC29" s="7" t="n">
+      <c r="AC29" s="6" t="n">
         <v>74.06</v>
       </c>
-      <c r="AD29" s="7" t="n">
+      <c r="AD29" s="6" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="AE29" s="7" t="n">
+      <c r="AE29" s="6" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="AF29" s="7" t="n">
+      <c r="AF29" s="6" t="n">
         <v>73.91</v>
       </c>
-      <c r="AG29" s="7" t="n">
+      <c r="AG29" s="6" t="n">
         <v>74.38</v>
       </c>
       <c r="AH29" s="6" t="n">
@@ -3187,126 +3151,126 @@
         <v>273.47</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>LA VOZ DE ARUTAM (NO AUTORIZADA)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="9" t="n">
         <v>107.3</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="9" t="n">
         <v>43.06</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="9" t="n">
         <v>41.51</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="9" t="n">
         <v>47.48</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="9" t="n">
         <v>48.84</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="n">
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="n">
         <v>49.17</v>
       </c>
-      <c r="J30" s="14" t="n">
+      <c r="J30" s="9" t="n">
         <v>40.76</v>
       </c>
-      <c r="K30" s="14" t="n">
+      <c r="K30" s="9" t="n">
         <v>41.36</v>
       </c>
-      <c r="L30" s="13" t="n">
+      <c r="L30" s="9" t="n">
         <v>46.16</v>
       </c>
-      <c r="M30" s="13" t="n">
+      <c r="M30" s="9" t="n">
         <v>43.89</v>
       </c>
-      <c r="N30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" s="13" t="n">
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="9" t="n">
         <v>53.46</v>
       </c>
-      <c r="Q30" s="15" t="n">
+      <c r="Q30" s="9" t="n">
         <v>54.55</v>
       </c>
-      <c r="R30" s="15" t="n">
+      <c r="R30" s="9" t="n">
         <v>56.15</v>
       </c>
-      <c r="S30" s="13" t="n">
+      <c r="S30" s="9" t="n">
         <v>49.19</v>
       </c>
-      <c r="T30" s="13" t="n">
+      <c r="T30" s="9" t="n">
         <v>47.4</v>
       </c>
-      <c r="U30" s="13" t="n">
+      <c r="U30" s="9" t="n">
         <v>46.51</v>
       </c>
-      <c r="V30" s="13" t="n">
+      <c r="V30" s="9" t="n">
         <v>50.82</v>
       </c>
-      <c r="W30" s="15" t="n">
+      <c r="W30" s="9" t="n">
         <v>55.1</v>
       </c>
-      <c r="X30" s="15" t="n">
+      <c r="X30" s="9" t="n">
         <v>54.54</v>
       </c>
-      <c r="Y30" s="13" t="n">
+      <c r="Y30" s="9" t="n">
         <v>49.52</v>
       </c>
-      <c r="Z30" s="13" t="n">
+      <c r="Z30" s="9" t="n">
         <v>47.54</v>
       </c>
-      <c r="AA30" s="15" t="n">
+      <c r="AA30" s="9" t="n">
         <v>54.18</v>
       </c>
-      <c r="AB30" s="15" t="n">
+      <c r="AB30" s="9" t="n">
         <v>55.12</v>
       </c>
-      <c r="AC30" s="13" t="n">
+      <c r="AC30" s="9" t="n">
         <v>48.65</v>
       </c>
-      <c r="AD30" s="13" t="n">
+      <c r="AD30" s="9" t="n">
         <v>53.31</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="9" t="n">
         <v>49.16</v>
       </c>
-      <c r="AF30" s="13" t="n">
+      <c r="AF30" s="9" t="n">
         <v>50.49</v>
       </c>
-      <c r="AG30" s="13" t="n">
+      <c r="AG30" s="9" t="n">
         <v>51.46</v>
       </c>
-      <c r="AH30" s="12" t="n">
+      <c r="AH30" s="9" t="n">
         <v>49.24</v>
       </c>
-      <c r="AI30" s="12" t="n">
+      <c r="AI30" s="9" t="n">
         <v>498.71</v>
       </c>
-      <c r="AJ30" s="12" t="inlineStr"/>
-      <c r="AK30" s="16" t="inlineStr"/>
+      <c r="AJ30" s="9" t="inlineStr"/>
+      <c r="AK30" s="10" t="inlineStr"/>
     </row>
     <row r="31"/>
     <row r="32"/>
@@ -3355,7 +3319,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3445,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK40" s="17" t="n"/>
+      <c r="AK40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3492,16 +3456,16 @@
       <c r="B41" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="6" t="n">
         <v>86.73</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="6" t="n">
         <v>82.92</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E41" s="6" t="n">
         <v>87.48</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="6" t="n">
         <v>87.08</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -3514,19 +3478,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="I41" s="6" t="n">
         <v>87.06999999999999</v>
       </c>
-      <c r="J41" s="7" t="n">
+      <c r="J41" s="6" t="n">
         <v>81.53</v>
       </c>
-      <c r="K41" s="7" t="n">
+      <c r="K41" s="6" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="L41" s="7" t="n">
+      <c r="L41" s="6" t="n">
         <v>84.2</v>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="6" t="n">
         <v>85.23</v>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -3539,58 +3503,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P41" s="7" t="n">
+      <c r="P41" s="6" t="n">
         <v>87.17</v>
       </c>
-      <c r="Q41" s="7" t="n">
+      <c r="Q41" s="6" t="n">
         <v>87.3</v>
       </c>
-      <c r="R41" s="7" t="n">
+      <c r="R41" s="6" t="n">
         <v>87.05</v>
       </c>
-      <c r="S41" s="7" t="n">
+      <c r="S41" s="6" t="n">
         <v>86.67</v>
       </c>
-      <c r="T41" s="7" t="n">
+      <c r="T41" s="6" t="n">
         <v>84.38</v>
       </c>
-      <c r="U41" s="7" t="n">
+      <c r="U41" s="6" t="n">
         <v>84.83</v>
       </c>
-      <c r="V41" s="7" t="n">
+      <c r="V41" s="6" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="W41" s="7" t="n">
+      <c r="W41" s="6" t="n">
         <v>87.38</v>
       </c>
-      <c r="X41" s="7" t="n">
+      <c r="X41" s="6" t="n">
         <v>86.98</v>
       </c>
-      <c r="Y41" s="7" t="n">
+      <c r="Y41" s="6" t="n">
         <v>87.37</v>
       </c>
-      <c r="Z41" s="7" t="n">
+      <c r="Z41" s="6" t="n">
         <v>84.87</v>
       </c>
-      <c r="AA41" s="7" t="n">
+      <c r="AA41" s="6" t="n">
         <v>86.98</v>
       </c>
-      <c r="AB41" s="7" t="n">
+      <c r="AB41" s="6" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="AC41" s="7" t="n">
+      <c r="AC41" s="6" t="n">
         <v>87.02</v>
       </c>
-      <c r="AD41" s="7" t="n">
+      <c r="AD41" s="6" t="n">
         <v>86.87</v>
       </c>
-      <c r="AE41" s="7" t="n">
+      <c r="AE41" s="6" t="n">
         <v>86.73</v>
       </c>
-      <c r="AF41" s="7" t="n">
+      <c r="AF41" s="6" t="n">
         <v>86.87</v>
       </c>
-      <c r="AG41" s="7" t="n">
+      <c r="AG41" s="6" t="n">
         <v>86.90000000000001</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -3598,7 +3562,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="18" t="n"/>
+      <c r="AK41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3609,16 +3573,16 @@
       <c r="B42" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="6" t="n">
         <v>108.83</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D42" s="6" t="n">
         <v>109.62</v>
       </c>
-      <c r="E42" s="7" t="n">
+      <c r="E42" s="6" t="n">
         <v>109.3</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="6" t="n">
         <v>109.05</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -3631,19 +3595,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="I42" s="6" t="n">
         <v>108.47</v>
       </c>
-      <c r="J42" s="7" t="n">
+      <c r="J42" s="6" t="n">
         <v>109.17</v>
       </c>
-      <c r="K42" s="7" t="n">
+      <c r="K42" s="6" t="n">
         <v>108.9</v>
       </c>
-      <c r="L42" s="7" t="n">
+      <c r="L42" s="6" t="n">
         <v>108.75</v>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="M42" s="6" t="n">
         <v>108.4</v>
       </c>
       <c r="N42" s="6" t="inlineStr">
@@ -3656,58 +3620,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P42" s="7" t="n">
+      <c r="P42" s="6" t="n">
         <v>109.07</v>
       </c>
-      <c r="Q42" s="7" t="n">
+      <c r="Q42" s="6" t="n">
         <v>109.23</v>
       </c>
-      <c r="R42" s="7" t="n">
+      <c r="R42" s="6" t="n">
         <v>109.03</v>
       </c>
-      <c r="S42" s="7" t="n">
+      <c r="S42" s="6" t="n">
         <v>110.05</v>
       </c>
-      <c r="T42" s="7" t="n">
+      <c r="T42" s="6" t="n">
         <v>109.6</v>
       </c>
-      <c r="U42" s="7" t="n">
+      <c r="U42" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="V42" s="7" t="n">
+      <c r="V42" s="6" t="n">
         <v>108.9</v>
       </c>
-      <c r="W42" s="7" t="n">
+      <c r="W42" s="6" t="n">
         <v>109.3</v>
       </c>
-      <c r="X42" s="7" t="n">
+      <c r="X42" s="6" t="n">
         <v>109.07</v>
       </c>
-      <c r="Y42" s="7" t="n">
+      <c r="Y42" s="6" t="n">
         <v>108.78</v>
       </c>
-      <c r="Z42" s="7" t="n">
+      <c r="Z42" s="6" t="n">
         <v>108.83</v>
       </c>
-      <c r="AA42" s="7" t="n">
+      <c r="AA42" s="6" t="n">
         <v>109.1</v>
       </c>
-      <c r="AB42" s="7" t="n">
+      <c r="AB42" s="6" t="n">
         <v>109.03</v>
       </c>
-      <c r="AC42" s="7" t="n">
+      <c r="AC42" s="6" t="n">
         <v>108.75</v>
       </c>
-      <c r="AD42" s="7" t="n">
+      <c r="AD42" s="6" t="n">
         <v>108.88</v>
       </c>
-      <c r="AE42" s="7" t="n">
+      <c r="AE42" s="6" t="n">
         <v>108.47</v>
       </c>
-      <c r="AF42" s="7" t="n">
+      <c r="AF42" s="6" t="n">
         <v>108.88</v>
       </c>
-      <c r="AG42" s="7" t="n">
+      <c r="AG42" s="6" t="n">
         <v>109.2</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -3715,7 +3679,7 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="18" t="n"/>
+      <c r="AK42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3726,16 +3690,16 @@
       <c r="B43" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="6" t="n">
         <v>38.13</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="6" t="n">
         <v>41.13</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="6" t="n">
         <v>41.17</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -3748,19 +3712,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="6" t="n">
         <v>36.3</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" s="6" t="n">
         <v>49.5</v>
       </c>
-      <c r="K43" s="10" t="n">
+      <c r="K43" s="6" t="n">
         <v>37.1</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L43" s="6" t="n">
         <v>40.53</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="6" t="n">
         <v>50.5</v>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -3773,58 +3737,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P43" s="10" t="n">
+      <c r="P43" s="6" t="n">
         <v>39.87</v>
       </c>
-      <c r="Q43" s="10" t="n">
+      <c r="Q43" s="6" t="n">
         <v>38.13</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="6" t="n">
         <v>37.27</v>
       </c>
-      <c r="S43" s="9" t="n">
+      <c r="S43" s="6" t="n">
         <v>47.38</v>
       </c>
-      <c r="T43" s="9" t="n">
+      <c r="T43" s="6" t="n">
         <v>51.48</v>
       </c>
-      <c r="U43" s="7" t="n">
+      <c r="U43" s="6" t="n">
         <v>56.65</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="6" t="n">
         <v>45.32</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="6" t="n">
         <v>41.1</v>
       </c>
-      <c r="X43" s="10" t="n">
+      <c r="X43" s="6" t="n">
         <v>39.07</v>
       </c>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="6" t="n">
         <v>41.78</v>
       </c>
-      <c r="Z43" s="9" t="n">
+      <c r="Z43" s="6" t="n">
         <v>44.7</v>
       </c>
-      <c r="AA43" s="10" t="n">
+      <c r="AA43" s="6" t="n">
         <v>42.47</v>
       </c>
-      <c r="AB43" s="10" t="n">
+      <c r="AB43" s="6" t="n">
         <v>37.5</v>
       </c>
-      <c r="AC43" s="10" t="n">
+      <c r="AC43" s="6" t="n">
         <v>39.95</v>
       </c>
-      <c r="AD43" s="10" t="n">
+      <c r="AD43" s="6" t="n">
         <v>38.4</v>
       </c>
-      <c r="AE43" s="10" t="n">
+      <c r="AE43" s="6" t="n">
         <v>39.77</v>
       </c>
-      <c r="AF43" s="10" t="n">
+      <c r="AF43" s="6" t="n">
         <v>41.9</v>
       </c>
-      <c r="AG43" s="10" t="n">
+      <c r="AG43" s="6" t="n">
         <v>39.3</v>
       </c>
       <c r="AH43" s="6" t="n">
@@ -3832,7 +3796,7 @@
       </c>
       <c r="AI43" s="6" t="inlineStr"/>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="18" t="n"/>
+      <c r="AK43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3843,16 +3807,16 @@
       <c r="B44" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="6" t="n">
         <v>36.4</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="6" t="n">
         <v>37.47</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="6" t="n">
         <v>39.78</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="6" t="n">
         <v>41.35</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3865,19 +3829,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="10" t="n">
+      <c r="I44" s="6" t="n">
         <v>36.1</v>
       </c>
-      <c r="J44" s="10" t="n">
+      <c r="J44" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="K44" s="10" t="n">
+      <c r="K44" s="6" t="n">
         <v>37.07</v>
       </c>
-      <c r="L44" s="10" t="n">
+      <c r="L44" s="6" t="n">
         <v>37.3</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="6" t="n">
         <v>39.17</v>
       </c>
       <c r="N44" s="6" t="inlineStr">
@@ -3890,58 +3854,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P44" s="10" t="n">
+      <c r="P44" s="6" t="n">
         <v>36.13</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="6" t="n">
         <v>36.55</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="6" t="n">
         <v>37.55</v>
       </c>
-      <c r="S44" s="10" t="n">
+      <c r="S44" s="6" t="n">
         <v>37.77</v>
       </c>
-      <c r="T44" s="10" t="n">
+      <c r="T44" s="6" t="n">
         <v>42.85</v>
       </c>
-      <c r="U44" s="9" t="n">
+      <c r="U44" s="6" t="n">
         <v>43.72</v>
       </c>
-      <c r="V44" s="10" t="n">
+      <c r="V44" s="6" t="n">
         <v>42.25</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="6" t="n">
         <v>39.5</v>
       </c>
-      <c r="X44" s="10" t="n">
+      <c r="X44" s="6" t="n">
         <v>37.32</v>
       </c>
-      <c r="Y44" s="10" t="n">
+      <c r="Y44" s="6" t="n">
         <v>38.07</v>
       </c>
-      <c r="Z44" s="10" t="n">
+      <c r="Z44" s="6" t="n">
         <v>37.63</v>
       </c>
-      <c r="AA44" s="10" t="n">
+      <c r="AA44" s="6" t="n">
         <v>40.42</v>
       </c>
-      <c r="AB44" s="10" t="n">
+      <c r="AB44" s="6" t="n">
         <v>38.12</v>
       </c>
-      <c r="AC44" s="10" t="n">
+      <c r="AC44" s="6" t="n">
         <v>36.5</v>
       </c>
-      <c r="AD44" s="10" t="n">
+      <c r="AD44" s="6" t="n">
         <v>36.72</v>
       </c>
-      <c r="AE44" s="10" t="n">
+      <c r="AE44" s="6" t="n">
         <v>36.95</v>
       </c>
-      <c r="AF44" s="10" t="n">
+      <c r="AF44" s="6" t="n">
         <v>39.42</v>
       </c>
-      <c r="AG44" s="10" t="n">
+      <c r="AG44" s="6" t="n">
         <v>37.27</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -3949,7 +3913,7 @@
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="18" t="n"/>
+      <c r="AK44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3960,16 +3924,16 @@
       <c r="B45" s="6" t="n">
         <v>211.25</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="6" t="n">
         <v>92.83</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="6" t="n">
         <v>96.5</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="6" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="6" t="n">
         <v>92.88</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -3982,19 +3946,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="6" t="n">
         <v>92.53</v>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="J45" s="6" t="n">
         <v>96.27</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="K45" s="6" t="n">
         <v>93.27</v>
       </c>
-      <c r="L45" s="7" t="n">
+      <c r="L45" s="6" t="n">
         <v>94.75</v>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="6" t="n">
         <v>96.56999999999999</v>
       </c>
       <c r="N45" s="6" t="inlineStr">
@@ -4007,58 +3971,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P45" s="7" t="n">
+      <c r="P45" s="6" t="n">
         <v>92.67</v>
       </c>
-      <c r="Q45" s="7" t="n">
+      <c r="Q45" s="6" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="R45" s="7" t="n">
+      <c r="R45" s="6" t="n">
         <v>92.52</v>
       </c>
-      <c r="S45" s="7" t="n">
+      <c r="S45" s="6" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="T45" s="7" t="n">
+      <c r="T45" s="6" t="n">
         <v>94.47</v>
       </c>
-      <c r="U45" s="7" t="n">
+      <c r="U45" s="6" t="n">
         <v>96.7</v>
       </c>
-      <c r="V45" s="7" t="n">
+      <c r="V45" s="6" t="n">
         <v>92.53</v>
       </c>
-      <c r="W45" s="7" t="n">
+      <c r="W45" s="6" t="n">
         <v>92.92</v>
       </c>
-      <c r="X45" s="7" t="n">
+      <c r="X45" s="6" t="n">
         <v>93.13</v>
       </c>
-      <c r="Y45" s="7" t="n">
+      <c r="Y45" s="6" t="n">
         <v>93.31999999999999</v>
       </c>
-      <c r="Z45" s="7" t="n">
+      <c r="Z45" s="6" t="n">
         <v>94.62</v>
       </c>
-      <c r="AA45" s="7" t="n">
+      <c r="AA45" s="6" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="AB45" s="7" t="n">
+      <c r="AB45" s="6" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="AC45" s="7" t="n">
+      <c r="AC45" s="6" t="n">
         <v>93.2</v>
       </c>
-      <c r="AD45" s="7" t="n">
+      <c r="AD45" s="6" t="n">
         <v>92.87</v>
       </c>
-      <c r="AE45" s="7" t="n">
+      <c r="AE45" s="6" t="n">
         <v>92.92</v>
       </c>
-      <c r="AF45" s="7" t="n">
+      <c r="AF45" s="6" t="n">
         <v>93.48</v>
       </c>
-      <c r="AG45" s="7" t="n">
+      <c r="AG45" s="6" t="n">
         <v>93.43000000000001</v>
       </c>
       <c r="AH45" s="6" t="n">
@@ -4066,7 +4030,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="18" t="n"/>
+      <c r="AK45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4077,16 +4041,16 @@
       <c r="B46" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="6" t="n">
         <v>27.47</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="6" t="n">
         <v>26.83</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="6" t="n">
         <v>28.47</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="6" t="n">
         <v>27.65</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -4099,19 +4063,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="10" t="n">
+      <c r="I46" s="6" t="n">
         <v>26.77</v>
       </c>
-      <c r="J46" s="10" t="n">
+      <c r="J46" s="6" t="n">
         <v>27.47</v>
       </c>
-      <c r="K46" s="10" t="n">
+      <c r="K46" s="6" t="n">
         <v>26.73</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" s="6" t="n">
         <v>26.62</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="6" t="n">
         <v>26.77</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -4124,58 +4088,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="10" t="n">
+      <c r="P46" s="6" t="n">
         <v>27.73</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="6" t="n">
         <v>26.82</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="6" t="n">
         <v>26.38</v>
       </c>
-      <c r="S46" s="10" t="n">
+      <c r="S46" s="6" t="n">
         <v>27.02</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="T46" s="6" t="n">
         <v>26.75</v>
       </c>
-      <c r="U46" s="10" t="n">
+      <c r="U46" s="6" t="n">
         <v>27.97</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="6" t="n">
         <v>26.12</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="6" t="n">
         <v>26.88</v>
       </c>
-      <c r="X46" s="10" t="n">
+      <c r="X46" s="6" t="n">
         <v>26.98</v>
       </c>
-      <c r="Y46" s="10" t="n">
+      <c r="Y46" s="6" t="n">
         <v>26.9</v>
       </c>
-      <c r="Z46" s="10" t="n">
+      <c r="Z46" s="6" t="n">
         <v>35.83</v>
       </c>
-      <c r="AA46" s="10" t="n">
+      <c r="AA46" s="6" t="n">
         <v>27.43</v>
       </c>
-      <c r="AB46" s="10" t="n">
+      <c r="AB46" s="6" t="n">
         <v>26.72</v>
       </c>
-      <c r="AC46" s="10" t="n">
+      <c r="AC46" s="6" t="n">
         <v>26.77</v>
       </c>
-      <c r="AD46" s="10" t="n">
+      <c r="AD46" s="6" t="n">
         <v>26.87</v>
       </c>
-      <c r="AE46" s="10" t="n">
+      <c r="AE46" s="6" t="n">
         <v>28.92</v>
       </c>
-      <c r="AF46" s="10" t="n">
+      <c r="AF46" s="6" t="n">
         <v>27.12</v>
       </c>
-      <c r="AG46" s="10" t="n">
+      <c r="AG46" s="6" t="n">
         <v>26.6</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4183,7 +4147,7 @@
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="18" t="n"/>
+      <c r="AK46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4194,16 +4158,16 @@
       <c r="B47" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="6" t="n">
         <v>28.37</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D47" s="6" t="n">
         <v>27.92</v>
       </c>
-      <c r="E47" s="10" t="n">
+      <c r="E47" s="6" t="n">
         <v>27.95</v>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F47" s="6" t="n">
         <v>27.78</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -4216,19 +4180,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="10" t="n">
+      <c r="I47" s="6" t="n">
         <v>27.37</v>
       </c>
-      <c r="J47" s="10" t="n">
+      <c r="J47" s="6" t="n">
         <v>27.83</v>
       </c>
-      <c r="K47" s="10" t="n">
+      <c r="K47" s="6" t="n">
         <v>27.77</v>
       </c>
-      <c r="L47" s="10" t="n">
+      <c r="L47" s="6" t="n">
         <v>28.52</v>
       </c>
-      <c r="M47" s="10" t="n">
+      <c r="M47" s="6" t="n">
         <v>28.13</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -4241,58 +4205,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="10" t="n">
+      <c r="P47" s="6" t="n">
         <v>27.4</v>
       </c>
-      <c r="Q47" s="10" t="n">
+      <c r="Q47" s="6" t="n">
         <v>27.75</v>
       </c>
-      <c r="R47" s="10" t="n">
+      <c r="R47" s="6" t="n">
         <v>27.68</v>
       </c>
-      <c r="S47" s="10" t="n">
+      <c r="S47" s="6" t="n">
         <v>27.72</v>
       </c>
-      <c r="T47" s="10" t="n">
+      <c r="T47" s="6" t="n">
         <v>28.08</v>
       </c>
-      <c r="U47" s="10" t="n">
+      <c r="U47" s="6" t="n">
         <v>27.73</v>
       </c>
-      <c r="V47" s="10" t="n">
+      <c r="V47" s="6" t="n">
         <v>28.07</v>
       </c>
-      <c r="W47" s="10" t="n">
+      <c r="W47" s="6" t="n">
         <v>28.58</v>
       </c>
-      <c r="X47" s="10" t="n">
+      <c r="X47" s="6" t="n">
         <v>28.65</v>
       </c>
-      <c r="Y47" s="10" t="n">
+      <c r="Y47" s="6" t="n">
         <v>27.85</v>
       </c>
-      <c r="Z47" s="10" t="n">
+      <c r="Z47" s="6" t="n">
         <v>28.33</v>
       </c>
-      <c r="AA47" s="10" t="n">
+      <c r="AA47" s="6" t="n">
         <v>28.08</v>
       </c>
-      <c r="AB47" s="10" t="n">
+      <c r="AB47" s="6" t="n">
         <v>29.27</v>
       </c>
-      <c r="AC47" s="10" t="n">
+      <c r="AC47" s="6" t="n">
         <v>28.18</v>
       </c>
-      <c r="AD47" s="10" t="n">
+      <c r="AD47" s="6" t="n">
         <v>28.13</v>
       </c>
-      <c r="AE47" s="10" t="n">
+      <c r="AE47" s="6" t="n">
         <v>27.93</v>
       </c>
-      <c r="AF47" s="10" t="n">
+      <c r="AF47" s="6" t="n">
         <v>28.4</v>
       </c>
-      <c r="AG47" s="10" t="n">
+      <c r="AG47" s="6" t="n">
         <v>27.67</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -4300,7 +4264,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="18" t="n"/>
+      <c r="AK47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4311,16 +4275,16 @@
       <c r="B48" s="6" t="n">
         <v>555.25</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="6" t="n">
         <v>30.87</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="6" t="n">
         <v>35.67</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E48" s="6" t="n">
         <v>31.3</v>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="6" t="n">
         <v>30.95</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -4333,19 +4297,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="10" t="n">
+      <c r="I48" s="6" t="n">
         <v>29.83</v>
       </c>
-      <c r="J48" s="10" t="n">
+      <c r="J48" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="K48" s="10" t="n">
+      <c r="K48" s="6" t="n">
         <v>30.7</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L48" s="6" t="n">
         <v>32.82</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="6" t="n">
         <v>36.93</v>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -4358,58 +4322,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="10" t="n">
+      <c r="P48" s="6" t="n">
         <v>30.17</v>
       </c>
-      <c r="Q48" s="10" t="n">
+      <c r="Q48" s="6" t="n">
         <v>30.43</v>
       </c>
-      <c r="R48" s="10" t="n">
+      <c r="R48" s="6" t="n">
         <v>30.48</v>
       </c>
-      <c r="S48" s="10" t="n">
+      <c r="S48" s="6" t="n">
         <v>35.07</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="T48" s="6" t="n">
         <v>35.13</v>
       </c>
-      <c r="U48" s="10" t="n">
+      <c r="U48" s="6" t="n">
         <v>38.18</v>
       </c>
-      <c r="V48" s="10" t="n">
+      <c r="V48" s="6" t="n">
         <v>30.97</v>
       </c>
-      <c r="W48" s="10" t="n">
+      <c r="W48" s="6" t="n">
         <v>29.7</v>
       </c>
-      <c r="X48" s="10" t="n">
+      <c r="X48" s="6" t="n">
         <v>30.2</v>
       </c>
-      <c r="Y48" s="10" t="n">
+      <c r="Y48" s="6" t="n">
         <v>30.97</v>
       </c>
-      <c r="Z48" s="10" t="n">
+      <c r="Z48" s="6" t="n">
         <v>34.18</v>
       </c>
-      <c r="AA48" s="10" t="n">
+      <c r="AA48" s="6" t="n">
         <v>30.1</v>
       </c>
-      <c r="AB48" s="10" t="n">
+      <c r="AB48" s="6" t="n">
         <v>29.78</v>
       </c>
-      <c r="AC48" s="10" t="n">
+      <c r="AC48" s="6" t="n">
         <v>31.43</v>
       </c>
-      <c r="AD48" s="10" t="n">
+      <c r="AD48" s="6" t="n">
         <v>30.87</v>
       </c>
-      <c r="AE48" s="10" t="n">
+      <c r="AE48" s="6" t="n">
         <v>29.88</v>
       </c>
-      <c r="AF48" s="10" t="n">
+      <c r="AF48" s="6" t="n">
         <v>31.67</v>
       </c>
-      <c r="AG48" s="10" t="n">
+      <c r="AG48" s="6" t="n">
         <v>29.67</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -4417,7 +4381,7 @@
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="18" t="n"/>
+      <c r="AK48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4428,16 +4392,16 @@
       <c r="B49" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="6" t="n">
         <v>29.83</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D49" s="6" t="n">
         <v>34.67</v>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="E49" s="6" t="n">
         <v>30.1</v>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="F49" s="6" t="n">
         <v>30.13</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -4450,19 +4414,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="10" t="n">
+      <c r="I49" s="6" t="n">
         <v>30.27</v>
       </c>
-      <c r="J49" s="10" t="n">
+      <c r="J49" s="6" t="n">
         <v>31.17</v>
       </c>
-      <c r="K49" s="10" t="n">
+      <c r="K49" s="6" t="n">
         <v>29.83</v>
       </c>
-      <c r="L49" s="10" t="n">
+      <c r="L49" s="6" t="n">
         <v>30.28</v>
       </c>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="6" t="n">
         <v>33.5</v>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -4475,58 +4439,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P49" s="10" t="n">
+      <c r="P49" s="6" t="n">
         <v>31.2</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="6" t="n">
         <v>32.07</v>
       </c>
-      <c r="R49" s="10" t="n">
+      <c r="R49" s="6" t="n">
         <v>32.5</v>
       </c>
-      <c r="S49" s="10" t="n">
+      <c r="S49" s="6" t="n">
         <v>32.17</v>
       </c>
-      <c r="T49" s="10" t="n">
+      <c r="T49" s="6" t="n">
         <v>29.88</v>
       </c>
-      <c r="U49" s="10" t="n">
+      <c r="U49" s="6" t="n">
         <v>32.85</v>
       </c>
-      <c r="V49" s="10" t="n">
+      <c r="V49" s="6" t="n">
         <v>29.97</v>
       </c>
-      <c r="W49" s="10" t="n">
+      <c r="W49" s="6" t="n">
         <v>30.85</v>
       </c>
-      <c r="X49" s="10" t="n">
+      <c r="X49" s="6" t="n">
         <v>31.2</v>
       </c>
-      <c r="Y49" s="10" t="n">
+      <c r="Y49" s="6" t="n">
         <v>30.82</v>
       </c>
-      <c r="Z49" s="10" t="n">
+      <c r="Z49" s="6" t="n">
         <v>33.93</v>
       </c>
-      <c r="AA49" s="10" t="n">
+      <c r="AA49" s="6" t="n">
         <v>30.57</v>
       </c>
-      <c r="AB49" s="10" t="n">
+      <c r="AB49" s="6" t="n">
         <v>30.85</v>
       </c>
-      <c r="AC49" s="10" t="n">
+      <c r="AC49" s="6" t="n">
         <v>32.78</v>
       </c>
-      <c r="AD49" s="10" t="n">
+      <c r="AD49" s="6" t="n">
         <v>31.38</v>
       </c>
-      <c r="AE49" s="10" t="n">
+      <c r="AE49" s="6" t="n">
         <v>30.18</v>
       </c>
-      <c r="AF49" s="10" t="n">
+      <c r="AF49" s="6" t="n">
         <v>31.43</v>
       </c>
-      <c r="AG49" s="10" t="n">
+      <c r="AG49" s="6" t="n">
         <v>30.47</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -4534,7 +4498,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="18" t="n"/>
+      <c r="AK49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4545,16 +4509,16 @@
       <c r="B50" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="6" t="n">
         <v>28.7</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="6" t="n">
         <v>33.23</v>
       </c>
-      <c r="E50" s="10" t="n">
+      <c r="E50" s="6" t="n">
         <v>29.02</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="6" t="n">
         <v>28.9</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -4567,19 +4531,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="10" t="n">
+      <c r="I50" s="6" t="n">
         <v>28.7</v>
       </c>
-      <c r="J50" s="10" t="n">
+      <c r="J50" s="6" t="n">
         <v>28.6</v>
       </c>
-      <c r="K50" s="10" t="n">
+      <c r="K50" s="6" t="n">
         <v>28.27</v>
       </c>
-      <c r="L50" s="10" t="n">
+      <c r="L50" s="6" t="n">
         <v>29.25</v>
       </c>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="6" t="n">
         <v>29.67</v>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -4592,58 +4556,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P50" s="10" t="n">
+      <c r="P50" s="6" t="n">
         <v>28.9</v>
       </c>
-      <c r="Q50" s="10" t="n">
+      <c r="Q50" s="6" t="n">
         <v>29.18</v>
       </c>
-      <c r="R50" s="10" t="n">
+      <c r="R50" s="6" t="n">
         <v>31.72</v>
       </c>
-      <c r="S50" s="10" t="n">
+      <c r="S50" s="6" t="n">
         <v>31.28</v>
       </c>
-      <c r="T50" s="10" t="n">
+      <c r="T50" s="6" t="n">
         <v>28.7</v>
       </c>
-      <c r="U50" s="10" t="n">
+      <c r="U50" s="6" t="n">
         <v>30.88</v>
       </c>
-      <c r="V50" s="10" t="n">
+      <c r="V50" s="6" t="n">
         <v>29.17</v>
       </c>
-      <c r="W50" s="10" t="n">
+      <c r="W50" s="6" t="n">
         <v>28.6</v>
       </c>
-      <c r="X50" s="10" t="n">
+      <c r="X50" s="6" t="n">
         <v>29.23</v>
       </c>
-      <c r="Y50" s="10" t="n">
+      <c r="Y50" s="6" t="n">
         <v>32.1</v>
       </c>
-      <c r="Z50" s="10" t="n">
+      <c r="Z50" s="6" t="n">
         <v>28.92</v>
       </c>
-      <c r="AA50" s="10" t="n">
+      <c r="AA50" s="6" t="n">
         <v>29.53</v>
       </c>
-      <c r="AB50" s="10" t="n">
+      <c r="AB50" s="6" t="n">
         <v>29.12</v>
       </c>
-      <c r="AC50" s="10" t="n">
+      <c r="AC50" s="6" t="n">
         <v>29.28</v>
       </c>
-      <c r="AD50" s="10" t="n">
+      <c r="AD50" s="6" t="n">
         <v>29.4</v>
       </c>
-      <c r="AE50" s="10" t="n">
+      <c r="AE50" s="6" t="n">
         <v>28.3</v>
       </c>
-      <c r="AF50" s="10" t="n">
+      <c r="AF50" s="6" t="n">
         <v>28.68</v>
       </c>
-      <c r="AG50" s="10" t="n">
+      <c r="AG50" s="6" t="n">
         <v>29.07</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -4651,124 +4615,124 @@
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="18" t="n"/>
+      <c r="AK50" s="12" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>EL CIUDADANO TV NO AUTORIZADA</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="9" t="n">
         <v>675.25</v>
       </c>
-      <c r="C51" s="14" t="n">
+      <c r="C51" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="9" t="n">
         <v>32.42</v>
       </c>
-      <c r="E51" s="14" t="n">
+      <c r="E51" s="9" t="n">
         <v>30.38</v>
       </c>
-      <c r="F51" s="14" t="n">
+      <c r="F51" s="9" t="n">
         <v>28.95</v>
       </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="n">
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="n">
         <v>28.37</v>
       </c>
-      <c r="J51" s="14" t="n">
+      <c r="J51" s="9" t="n">
         <v>31.97</v>
       </c>
-      <c r="K51" s="14" t="n">
+      <c r="K51" s="9" t="n">
         <v>30.47</v>
       </c>
-      <c r="L51" s="14" t="n">
+      <c r="L51" s="9" t="n">
         <v>30.97</v>
       </c>
-      <c r="M51" s="14" t="n">
+      <c r="M51" s="9" t="n">
         <v>32.63</v>
       </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="14" t="n">
+      <c r="N51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="9" t="n">
         <v>31.6</v>
       </c>
-      <c r="Q51" s="14" t="n">
+      <c r="Q51" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="R51" s="14" t="n">
+      <c r="R51" s="9" t="n">
         <v>29.88</v>
       </c>
-      <c r="S51" s="14" t="n">
+      <c r="S51" s="9" t="n">
         <v>31.85</v>
       </c>
-      <c r="T51" s="14" t="n">
+      <c r="T51" s="9" t="n">
         <v>30.62</v>
       </c>
-      <c r="U51" s="14" t="n">
+      <c r="U51" s="9" t="n">
         <v>32.62</v>
       </c>
-      <c r="V51" s="14" t="n">
+      <c r="V51" s="9" t="n">
         <v>29.52</v>
       </c>
-      <c r="W51" s="14" t="n">
+      <c r="W51" s="9" t="n">
         <v>29.95</v>
       </c>
-      <c r="X51" s="14" t="n">
+      <c r="X51" s="9" t="n">
         <v>29.62</v>
       </c>
-      <c r="Y51" s="14" t="n">
+      <c r="Y51" s="9" t="n">
         <v>30.12</v>
       </c>
-      <c r="Z51" s="14" t="n">
+      <c r="Z51" s="9" t="n">
         <v>31.13</v>
       </c>
-      <c r="AA51" s="14" t="n">
+      <c r="AA51" s="9" t="n">
         <v>30.3</v>
       </c>
-      <c r="AB51" s="14" t="n">
+      <c r="AB51" s="9" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC51" s="14" t="n">
+      <c r="AC51" s="9" t="n">
         <v>29.95</v>
       </c>
-      <c r="AD51" s="14" t="n">
+      <c r="AD51" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="AE51" s="14" t="n">
+      <c r="AE51" s="9" t="n">
         <v>29.73</v>
       </c>
-      <c r="AF51" s="14" t="n">
+      <c r="AF51" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG51" s="14" t="n">
+      <c r="AG51" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="AH51" s="12" t="n">
+      <c r="AH51" s="9" t="n">
         <v>30.39</v>
       </c>
-      <c r="AI51" s="12" t="inlineStr"/>
-      <c r="AJ51" s="12" t="inlineStr"/>
-      <c r="AK51" s="19" t="n"/>
+      <c r="AI51" s="9" t="inlineStr"/>
+      <c r="AJ51" s="9" t="inlineStr"/>
+      <c r="AK51" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFD9BCB"/>
         <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6666"/>
+        <bgColor rgb="FFFF6666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,7 +206,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -216,6 +234,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1038,14 +1059,14 @@
       <c r="AG11" s="7" t="n">
         <v>79.95</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="8" t="n">
         <v>76.17</v>
       </c>
       <c r="AI11" s="6" t="n">
         <v>172.46</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1157,14 +1178,14 @@
       <c r="AG12" s="7" t="n">
         <v>77.42</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="8" t="n">
         <v>62.84</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="10" t="n">
         <v>205.41</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1175,16 +1196,16 @@
       <c r="B13" s="6" t="n">
         <v>89.7</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="11" t="n">
         <v>45.5</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="12" t="n">
         <v>41.8</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="11" t="n">
         <v>50.04</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="11" t="n">
         <v>52.02</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1197,19 +1218,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="11" t="n">
         <v>51.87</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="11" t="n">
         <v>43.55</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K13" s="12" t="n">
         <v>42.94</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="11" t="n">
         <v>52.16</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="11" t="n">
         <v>52.39</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -1222,25 +1243,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P13" s="9" t="n">
+      <c r="P13" s="11" t="n">
         <v>51.88</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="11" t="n">
         <v>53.01</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="11" t="n">
         <v>53.68</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="11" t="n">
         <v>53.23</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="11" t="n">
         <v>53.03</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="11" t="n">
         <v>52.08</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="11" t="n">
         <v>53.32</v>
       </c>
       <c r="W13" s="7" t="n">
@@ -1249,10 +1270,10 @@
       <c r="X13" s="7" t="n">
         <v>54.02</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="11" t="n">
         <v>51.79</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="Z13" s="11" t="n">
         <v>51.92</v>
       </c>
       <c r="AA13" s="7" t="n">
@@ -1261,16 +1282,16 @@
       <c r="AB13" s="7" t="n">
         <v>57.24</v>
       </c>
-      <c r="AC13" s="9" t="n">
+      <c r="AC13" s="11" t="n">
         <v>53.42</v>
       </c>
       <c r="AD13" s="7" t="n">
         <v>55.09</v>
       </c>
-      <c r="AE13" s="9" t="n">
+      <c r="AE13" s="11" t="n">
         <v>52.02</v>
       </c>
-      <c r="AF13" s="9" t="n">
+      <c r="AF13" s="11" t="n">
         <v>52.26</v>
       </c>
       <c r="AG13" s="7" t="n">
@@ -1279,11 +1300,11 @@
       <c r="AH13" s="6" t="n">
         <v>52.3</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="10" t="n">
         <v>237.33</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1395,14 +1416,14 @@
       <c r="AG14" s="7" t="n">
         <v>109.6</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="8" t="n">
         <v>108.19</v>
       </c>
       <c r="AI14" s="6" t="n">
         <v>137.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1413,16 +1434,16 @@
       <c r="B15" s="6" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="11" t="n">
         <v>45.29</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="12" t="n">
         <v>42.04</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="11" t="n">
         <v>50.12</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="11" t="n">
         <v>51.98</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1435,19 +1456,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="11" t="n">
         <v>50.55</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" s="12" t="n">
         <v>42.94</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="11" t="n">
         <v>43.26</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="11" t="n">
         <v>48.76</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="11" t="n">
         <v>48.99</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
@@ -1514,14 +1535,14 @@
       <c r="AG15" s="7" t="n">
         <v>93.54000000000001</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="8" t="n">
         <v>73.55</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="10" t="n">
         <v>299.96</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1633,14 +1654,14 @@
       <c r="AG16" s="7" t="n">
         <v>104.34</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="8" t="n">
         <v>101.88</v>
       </c>
       <c r="AI16" s="6" t="n">
         <v>149.91</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1752,14 +1773,14 @@
       <c r="AG17" s="7" t="n">
         <v>104.2</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="8" t="n">
         <v>103.73</v>
       </c>
       <c r="AI17" s="6" t="n">
         <v>187.17</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1871,14 +1892,14 @@
       <c r="AG18" s="7" t="n">
         <v>64.59</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="8" t="n">
         <v>63.23</v>
       </c>
       <c r="AI18" s="6" t="n">
         <v>174.55</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1889,16 +1910,16 @@
       <c r="B19" s="6" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="11" t="n">
         <v>45.01</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="12" t="n">
         <v>42.51</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="11" t="n">
         <v>47.62</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="11" t="n">
         <v>48.7</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1911,19 +1932,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="11" t="n">
         <v>50.16</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="11" t="n">
         <v>43.32</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="11" t="n">
         <v>45.82</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="11" t="n">
         <v>45.42</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="12" t="n">
         <v>42.99</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
@@ -1936,68 +1957,68 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P19" s="9" t="n">
+      <c r="P19" s="11" t="n">
         <v>46.38</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="11" t="n">
         <v>47.96</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="11" t="n">
         <v>49.18</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="11" t="n">
         <v>44.67</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="11" t="n">
         <v>47.12</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="11" t="n">
         <v>46.34</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="11" t="n">
         <v>48.12</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="11" t="n">
         <v>49.51</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" s="11" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="Y19" s="11" t="n">
         <v>44.94</v>
       </c>
-      <c r="Z19" s="10" t="n">
+      <c r="Z19" s="12" t="n">
         <v>42.99</v>
       </c>
-      <c r="AA19" s="9" t="n">
+      <c r="AA19" s="11" t="n">
         <v>49.02</v>
       </c>
-      <c r="AB19" s="9" t="n">
+      <c r="AB19" s="11" t="n">
         <v>49.04</v>
       </c>
-      <c r="AC19" s="9" t="n">
+      <c r="AC19" s="11" t="n">
         <v>46.11</v>
       </c>
-      <c r="AD19" s="9" t="n">
+      <c r="AD19" s="11" t="n">
         <v>47.42</v>
       </c>
-      <c r="AE19" s="9" t="n">
+      <c r="AE19" s="11" t="n">
         <v>44.98</v>
       </c>
-      <c r="AF19" s="9" t="n">
+      <c r="AF19" s="11" t="n">
         <v>47.28</v>
       </c>
-      <c r="AG19" s="9" t="n">
+      <c r="AG19" s="11" t="n">
         <v>46.35</v>
       </c>
       <c r="AH19" s="6" t="n">
         <v>46.54</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="10" t="n">
         <v>499.13</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2109,14 +2130,14 @@
       <c r="AG20" s="7" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="8" t="n">
         <v>86.86</v>
       </c>
       <c r="AI20" s="6" t="n">
         <v>112.27</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2228,14 +2249,14 @@
       <c r="AG21" s="7" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="8" t="n">
         <v>101.82</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="10" t="n">
         <v>208.17</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2347,14 +2368,14 @@
       <c r="AG22" s="7" t="n">
         <v>97.05</v>
       </c>
-      <c r="AH22" s="6" t="n">
+      <c r="AH22" s="8" t="n">
         <v>97.83</v>
       </c>
       <c r="AI22" s="6" t="n">
         <v>131.9</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2365,16 +2386,16 @@
       <c r="B23" s="6" t="n">
         <v>100.1</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="11" t="n">
         <v>47.7</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="11" t="n">
         <v>43.78</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="11" t="n">
         <v>49.55</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="11" t="n">
         <v>51.52</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -2387,13 +2408,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="11" t="n">
         <v>51.51</v>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="J23" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="11" t="n">
         <v>44.19</v>
       </c>
       <c r="L23" s="7" t="n">
@@ -2466,14 +2487,14 @@
       <c r="AG23" s="7" t="n">
         <v>109.65</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH23" s="8" t="n">
         <v>92.2</v>
       </c>
-      <c r="AI23" s="6" t="n">
+      <c r="AI23" s="10" t="n">
         <v>217.44</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2585,14 +2606,14 @@
       <c r="AG24" s="7" t="n">
         <v>107.92</v>
       </c>
-      <c r="AH24" s="6" t="n">
+      <c r="AH24" s="8" t="n">
         <v>107.96</v>
       </c>
       <c r="AI24" s="6" t="n">
         <v>179.35</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2704,14 +2725,14 @@
       <c r="AG25" s="7" t="n">
         <v>99.05</v>
       </c>
-      <c r="AH25" s="6" t="n">
+      <c r="AH25" s="8" t="n">
         <v>99.06</v>
       </c>
       <c r="AI25" s="6" t="n">
         <v>37.91</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2823,14 +2844,14 @@
       <c r="AG26" s="7" t="n">
         <v>90.84999999999999</v>
       </c>
-      <c r="AH26" s="6" t="n">
+      <c r="AH26" s="8" t="n">
         <v>89.51000000000001</v>
       </c>
       <c r="AI26" s="6" t="n">
         <v>162.72</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2841,16 +2862,16 @@
       <c r="B27" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="12" t="n">
         <v>40.55</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="12" t="n">
         <v>40.37</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="11" t="n">
         <v>45.01</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="11" t="n">
         <v>45.64</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -2863,19 +2884,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="11" t="n">
         <v>45.92</v>
       </c>
-      <c r="J27" s="9" t="n">
+      <c r="J27" s="11" t="n">
         <v>44.02</v>
       </c>
-      <c r="K27" s="10" t="n">
+      <c r="K27" s="12" t="n">
         <v>39.78</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L27" s="12" t="n">
         <v>42.79</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="11" t="n">
         <v>43.6</v>
       </c>
       <c r="N27" s="6" t="inlineStr">
@@ -2888,68 +2909,68 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="11" t="n">
         <v>43.68</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="11" t="n">
         <v>44.51</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="11" t="n">
         <v>45.51</v>
       </c>
-      <c r="S27" s="10" t="n">
+      <c r="S27" s="12" t="n">
         <v>41.6</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="11" t="n">
         <v>47.68</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" s="11" t="n">
         <v>47.97</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="11" t="n">
         <v>48.11</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="11" t="n">
         <v>46.76</v>
       </c>
-      <c r="X27" s="9" t="n">
+      <c r="X27" s="11" t="n">
         <v>45.13</v>
       </c>
-      <c r="Y27" s="9" t="n">
+      <c r="Y27" s="11" t="n">
         <v>43.96</v>
       </c>
-      <c r="Z27" s="10" t="n">
+      <c r="Z27" s="12" t="n">
         <v>42.04</v>
       </c>
-      <c r="AA27" s="9" t="n">
+      <c r="AA27" s="11" t="n">
         <v>46.09</v>
       </c>
-      <c r="AB27" s="9" t="n">
+      <c r="AB27" s="11" t="n">
         <v>44.94</v>
       </c>
-      <c r="AC27" s="10" t="n">
+      <c r="AC27" s="12" t="n">
         <v>42.45</v>
       </c>
-      <c r="AD27" s="9" t="n">
+      <c r="AD27" s="11" t="n">
         <v>45.12</v>
       </c>
-      <c r="AE27" s="10" t="n">
+      <c r="AE27" s="12" t="n">
         <v>42.72</v>
       </c>
-      <c r="AF27" s="9" t="n">
+      <c r="AF27" s="11" t="n">
         <v>44.48</v>
       </c>
-      <c r="AG27" s="9" t="n">
+      <c r="AG27" s="11" t="n">
         <v>46.65</v>
       </c>
       <c r="AH27" s="6" t="n">
         <v>44.34</v>
       </c>
-      <c r="AI27" s="6" t="n">
+      <c r="AI27" s="10" t="n">
         <v>499.69</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2960,16 +2981,16 @@
       <c r="B28" s="6" t="n">
         <v>104.9</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="12" t="n">
         <v>42.55</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="12" t="n">
         <v>40.56</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="11" t="n">
         <v>45.41</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="11" t="n">
         <v>46</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2982,19 +3003,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I28" s="11" t="n">
         <v>47.29</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="11" t="n">
         <v>43.31</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="11" t="n">
         <v>43.66</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="11" t="n">
         <v>43.66</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="11" t="n">
         <v>43.85</v>
       </c>
       <c r="N28" s="6" t="inlineStr">
@@ -3007,68 +3028,68 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P28" s="9" t="n">
+      <c r="P28" s="11" t="n">
         <v>44.41</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="11" t="n">
         <v>46.52</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="11" t="n">
         <v>46.61</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" s="11" t="n">
         <v>43.24</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" s="11" t="n">
         <v>47.58</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="11" t="n">
         <v>47.44</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="11" t="n">
         <v>47.52</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="11" t="n">
         <v>47.36</v>
       </c>
-      <c r="X28" s="9" t="n">
+      <c r="X28" s="11" t="n">
         <v>46.7</v>
       </c>
-      <c r="Y28" s="9" t="n">
+      <c r="Y28" s="11" t="n">
         <v>43.12</v>
       </c>
-      <c r="Z28" s="9" t="n">
+      <c r="Z28" s="11" t="n">
         <v>43.08</v>
       </c>
-      <c r="AA28" s="9" t="n">
+      <c r="AA28" s="11" t="n">
         <v>46.76</v>
       </c>
-      <c r="AB28" s="9" t="n">
+      <c r="AB28" s="11" t="n">
         <v>46.58</v>
       </c>
-      <c r="AC28" s="9" t="n">
+      <c r="AC28" s="11" t="n">
         <v>44.84</v>
       </c>
-      <c r="AD28" s="9" t="n">
+      <c r="AD28" s="11" t="n">
         <v>46.04</v>
       </c>
-      <c r="AE28" s="9" t="n">
+      <c r="AE28" s="11" t="n">
         <v>44.46</v>
       </c>
-      <c r="AF28" s="9" t="n">
+      <c r="AF28" s="11" t="n">
         <v>46.29</v>
       </c>
-      <c r="AG28" s="9" t="n">
+      <c r="AG28" s="11" t="n">
         <v>47.22</v>
       </c>
       <c r="AH28" s="6" t="n">
         <v>45.26</v>
       </c>
-      <c r="AI28" s="6" t="n">
+      <c r="AI28" s="10" t="n">
         <v>499.61</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3180,133 +3201,133 @@
       <c r="AG29" s="7" t="n">
         <v>74.38</v>
       </c>
-      <c r="AH29" s="6" t="n">
+      <c r="AH29" s="8" t="n">
         <v>74.5</v>
       </c>
-      <c r="AI29" s="6" t="n">
+      <c r="AI29" s="10" t="n">
         <v>273.47</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>LA VOZ DE ARUTAM (NO AUTORIZADA)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="14" t="n">
         <v>107.3</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="15" t="n">
         <v>43.06</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="16" t="n">
         <v>41.51</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="15" t="n">
         <v>47.48</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="15" t="n">
         <v>48.84</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="n">
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="n">
         <v>49.17</v>
       </c>
-      <c r="J30" s="14" t="n">
+      <c r="J30" s="16" t="n">
         <v>40.76</v>
       </c>
-      <c r="K30" s="14" t="n">
+      <c r="K30" s="16" t="n">
         <v>41.36</v>
       </c>
-      <c r="L30" s="13" t="n">
+      <c r="L30" s="15" t="n">
         <v>46.16</v>
       </c>
-      <c r="M30" s="13" t="n">
+      <c r="M30" s="15" t="n">
         <v>43.89</v>
       </c>
-      <c r="N30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" s="13" t="n">
+      <c r="N30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="15" t="n">
         <v>53.46</v>
       </c>
-      <c r="Q30" s="15" t="n">
+      <c r="Q30" s="17" t="n">
         <v>54.55</v>
       </c>
-      <c r="R30" s="15" t="n">
+      <c r="R30" s="17" t="n">
         <v>56.15</v>
       </c>
-      <c r="S30" s="13" t="n">
+      <c r="S30" s="15" t="n">
         <v>49.19</v>
       </c>
-      <c r="T30" s="13" t="n">
+      <c r="T30" s="15" t="n">
         <v>47.4</v>
       </c>
-      <c r="U30" s="13" t="n">
+      <c r="U30" s="15" t="n">
         <v>46.51</v>
       </c>
-      <c r="V30" s="13" t="n">
+      <c r="V30" s="15" t="n">
         <v>50.82</v>
       </c>
-      <c r="W30" s="15" t="n">
+      <c r="W30" s="17" t="n">
         <v>55.1</v>
       </c>
-      <c r="X30" s="15" t="n">
+      <c r="X30" s="17" t="n">
         <v>54.54</v>
       </c>
-      <c r="Y30" s="13" t="n">
+      <c r="Y30" s="15" t="n">
         <v>49.52</v>
       </c>
-      <c r="Z30" s="13" t="n">
+      <c r="Z30" s="15" t="n">
         <v>47.54</v>
       </c>
-      <c r="AA30" s="15" t="n">
+      <c r="AA30" s="17" t="n">
         <v>54.18</v>
       </c>
-      <c r="AB30" s="15" t="n">
+      <c r="AB30" s="17" t="n">
         <v>55.12</v>
       </c>
-      <c r="AC30" s="13" t="n">
+      <c r="AC30" s="15" t="n">
         <v>48.65</v>
       </c>
-      <c r="AD30" s="13" t="n">
+      <c r="AD30" s="15" t="n">
         <v>53.31</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="15" t="n">
         <v>49.16</v>
       </c>
-      <c r="AF30" s="13" t="n">
+      <c r="AF30" s="15" t="n">
         <v>50.49</v>
       </c>
-      <c r="AG30" s="13" t="n">
+      <c r="AG30" s="15" t="n">
         <v>51.46</v>
       </c>
-      <c r="AH30" s="12" t="n">
+      <c r="AH30" s="14" t="n">
         <v>49.24</v>
       </c>
-      <c r="AI30" s="12" t="n">
+      <c r="AI30" s="18" t="n">
         <v>498.71</v>
       </c>
-      <c r="AJ30" s="12" t="inlineStr"/>
-      <c r="AK30" s="16" t="inlineStr"/>
+      <c r="AJ30" s="14" t="inlineStr"/>
+      <c r="AK30" s="19" t="inlineStr"/>
     </row>
     <row r="31"/>
     <row r="32"/>
@@ -3481,7 +3502,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK40" s="17" t="n"/>
+      <c r="AK40" s="20" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3593,12 +3614,12 @@
       <c r="AG41" s="7" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="AH41" s="6" t="n">
+      <c r="AH41" s="8" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="18" t="n"/>
+      <c r="AK41" s="21" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3710,12 +3731,12 @@
       <c r="AG42" s="7" t="n">
         <v>109.2</v>
       </c>
-      <c r="AH42" s="6" t="n">
+      <c r="AH42" s="8" t="n">
         <v>109.02</v>
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="18" t="n"/>
+      <c r="AK42" s="21" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3726,16 +3747,16 @@
       <c r="B43" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="12" t="n">
         <v>38.13</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="12" t="n">
         <v>41.13</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="12" t="n">
         <v>41.17</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -3748,19 +3769,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="12" t="n">
         <v>36.3</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" s="11" t="n">
         <v>49.5</v>
       </c>
-      <c r="K43" s="10" t="n">
+      <c r="K43" s="12" t="n">
         <v>37.1</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L43" s="12" t="n">
         <v>40.53</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="11" t="n">
         <v>50.5</v>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -3773,58 +3794,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P43" s="10" t="n">
+      <c r="P43" s="12" t="n">
         <v>39.87</v>
       </c>
-      <c r="Q43" s="10" t="n">
+      <c r="Q43" s="12" t="n">
         <v>38.13</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="12" t="n">
         <v>37.27</v>
       </c>
-      <c r="S43" s="9" t="n">
+      <c r="S43" s="11" t="n">
         <v>47.38</v>
       </c>
-      <c r="T43" s="9" t="n">
+      <c r="T43" s="11" t="n">
         <v>51.48</v>
       </c>
       <c r="U43" s="7" t="n">
         <v>56.65</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="11" t="n">
         <v>45.32</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="12" t="n">
         <v>41.1</v>
       </c>
-      <c r="X43" s="10" t="n">
+      <c r="X43" s="12" t="n">
         <v>39.07</v>
       </c>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="12" t="n">
         <v>41.78</v>
       </c>
-      <c r="Z43" s="9" t="n">
+      <c r="Z43" s="11" t="n">
         <v>44.7</v>
       </c>
-      <c r="AA43" s="10" t="n">
+      <c r="AA43" s="12" t="n">
         <v>42.47</v>
       </c>
-      <c r="AB43" s="10" t="n">
+      <c r="AB43" s="12" t="n">
         <v>37.5</v>
       </c>
-      <c r="AC43" s="10" t="n">
+      <c r="AC43" s="12" t="n">
         <v>39.95</v>
       </c>
-      <c r="AD43" s="10" t="n">
+      <c r="AD43" s="12" t="n">
         <v>38.4</v>
       </c>
-      <c r="AE43" s="10" t="n">
+      <c r="AE43" s="12" t="n">
         <v>39.77</v>
       </c>
-      <c r="AF43" s="10" t="n">
+      <c r="AF43" s="12" t="n">
         <v>41.9</v>
       </c>
-      <c r="AG43" s="10" t="n">
+      <c r="AG43" s="12" t="n">
         <v>39.3</v>
       </c>
       <c r="AH43" s="6" t="n">
@@ -3832,7 +3853,7 @@
       </c>
       <c r="AI43" s="6" t="inlineStr"/>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="18" t="n"/>
+      <c r="AK43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3843,16 +3864,16 @@
       <c r="B44" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="12" t="n">
         <v>36.4</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="12" t="n">
         <v>37.47</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="12" t="n">
         <v>39.78</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="12" t="n">
         <v>41.35</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3865,19 +3886,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="10" t="n">
+      <c r="I44" s="12" t="n">
         <v>36.1</v>
       </c>
-      <c r="J44" s="10" t="n">
+      <c r="J44" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="K44" s="10" t="n">
+      <c r="K44" s="12" t="n">
         <v>37.07</v>
       </c>
-      <c r="L44" s="10" t="n">
+      <c r="L44" s="12" t="n">
         <v>37.3</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="12" t="n">
         <v>39.17</v>
       </c>
       <c r="N44" s="6" t="inlineStr">
@@ -3890,58 +3911,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P44" s="10" t="n">
+      <c r="P44" s="12" t="n">
         <v>36.13</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="12" t="n">
         <v>36.55</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="12" t="n">
         <v>37.55</v>
       </c>
-      <c r="S44" s="10" t="n">
+      <c r="S44" s="12" t="n">
         <v>37.77</v>
       </c>
-      <c r="T44" s="10" t="n">
+      <c r="T44" s="12" t="n">
         <v>42.85</v>
       </c>
-      <c r="U44" s="9" t="n">
+      <c r="U44" s="11" t="n">
         <v>43.72</v>
       </c>
-      <c r="V44" s="10" t="n">
+      <c r="V44" s="12" t="n">
         <v>42.25</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="12" t="n">
         <v>39.5</v>
       </c>
-      <c r="X44" s="10" t="n">
+      <c r="X44" s="12" t="n">
         <v>37.32</v>
       </c>
-      <c r="Y44" s="10" t="n">
+      <c r="Y44" s="12" t="n">
         <v>38.07</v>
       </c>
-      <c r="Z44" s="10" t="n">
+      <c r="Z44" s="12" t="n">
         <v>37.63</v>
       </c>
-      <c r="AA44" s="10" t="n">
+      <c r="AA44" s="12" t="n">
         <v>40.42</v>
       </c>
-      <c r="AB44" s="10" t="n">
+      <c r="AB44" s="12" t="n">
         <v>38.12</v>
       </c>
-      <c r="AC44" s="10" t="n">
+      <c r="AC44" s="12" t="n">
         <v>36.5</v>
       </c>
-      <c r="AD44" s="10" t="n">
+      <c r="AD44" s="12" t="n">
         <v>36.72</v>
       </c>
-      <c r="AE44" s="10" t="n">
+      <c r="AE44" s="12" t="n">
         <v>36.95</v>
       </c>
-      <c r="AF44" s="10" t="n">
+      <c r="AF44" s="12" t="n">
         <v>39.42</v>
       </c>
-      <c r="AG44" s="10" t="n">
+      <c r="AG44" s="12" t="n">
         <v>37.27</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -3949,7 +3970,7 @@
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="18" t="n"/>
+      <c r="AK44" s="21" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4061,12 +4082,12 @@
       <c r="AG45" s="7" t="n">
         <v>93.43000000000001</v>
       </c>
-      <c r="AH45" s="6" t="n">
+      <c r="AH45" s="8" t="n">
         <v>93.8</v>
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="18" t="n"/>
+      <c r="AK45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4077,16 +4098,16 @@
       <c r="B46" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="12" t="n">
         <v>27.47</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="12" t="n">
         <v>26.83</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="12" t="n">
         <v>28.47</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="12" t="n">
         <v>27.65</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -4099,19 +4120,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="10" t="n">
+      <c r="I46" s="12" t="n">
         <v>26.77</v>
       </c>
-      <c r="J46" s="10" t="n">
+      <c r="J46" s="12" t="n">
         <v>27.47</v>
       </c>
-      <c r="K46" s="10" t="n">
+      <c r="K46" s="12" t="n">
         <v>26.73</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" s="12" t="n">
         <v>26.62</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="12" t="n">
         <v>26.77</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -4124,58 +4145,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="10" t="n">
+      <c r="P46" s="12" t="n">
         <v>27.73</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="12" t="n">
         <v>26.82</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="12" t="n">
         <v>26.38</v>
       </c>
-      <c r="S46" s="10" t="n">
+      <c r="S46" s="12" t="n">
         <v>27.02</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="T46" s="12" t="n">
         <v>26.75</v>
       </c>
-      <c r="U46" s="10" t="n">
+      <c r="U46" s="12" t="n">
         <v>27.97</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="12" t="n">
         <v>26.12</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="12" t="n">
         <v>26.88</v>
       </c>
-      <c r="X46" s="10" t="n">
+      <c r="X46" s="12" t="n">
         <v>26.98</v>
       </c>
-      <c r="Y46" s="10" t="n">
+      <c r="Y46" s="12" t="n">
         <v>26.9</v>
       </c>
-      <c r="Z46" s="10" t="n">
+      <c r="Z46" s="12" t="n">
         <v>35.83</v>
       </c>
-      <c r="AA46" s="10" t="n">
+      <c r="AA46" s="12" t="n">
         <v>27.43</v>
       </c>
-      <c r="AB46" s="10" t="n">
+      <c r="AB46" s="12" t="n">
         <v>26.72</v>
       </c>
-      <c r="AC46" s="10" t="n">
+      <c r="AC46" s="12" t="n">
         <v>26.77</v>
       </c>
-      <c r="AD46" s="10" t="n">
+      <c r="AD46" s="12" t="n">
         <v>26.87</v>
       </c>
-      <c r="AE46" s="10" t="n">
+      <c r="AE46" s="12" t="n">
         <v>28.92</v>
       </c>
-      <c r="AF46" s="10" t="n">
+      <c r="AF46" s="12" t="n">
         <v>27.12</v>
       </c>
-      <c r="AG46" s="10" t="n">
+      <c r="AG46" s="12" t="n">
         <v>26.6</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4183,7 +4204,7 @@
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="18" t="n"/>
+      <c r="AK46" s="21" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4194,16 +4215,16 @@
       <c r="B47" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="12" t="n">
         <v>28.37</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D47" s="12" t="n">
         <v>27.92</v>
       </c>
-      <c r="E47" s="10" t="n">
+      <c r="E47" s="12" t="n">
         <v>27.95</v>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F47" s="12" t="n">
         <v>27.78</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -4216,19 +4237,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="10" t="n">
+      <c r="I47" s="12" t="n">
         <v>27.37</v>
       </c>
-      <c r="J47" s="10" t="n">
+      <c r="J47" s="12" t="n">
         <v>27.83</v>
       </c>
-      <c r="K47" s="10" t="n">
+      <c r="K47" s="12" t="n">
         <v>27.77</v>
       </c>
-      <c r="L47" s="10" t="n">
+      <c r="L47" s="12" t="n">
         <v>28.52</v>
       </c>
-      <c r="M47" s="10" t="n">
+      <c r="M47" s="12" t="n">
         <v>28.13</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -4241,58 +4262,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="10" t="n">
+      <c r="P47" s="12" t="n">
         <v>27.4</v>
       </c>
-      <c r="Q47" s="10" t="n">
+      <c r="Q47" s="12" t="n">
         <v>27.75</v>
       </c>
-      <c r="R47" s="10" t="n">
+      <c r="R47" s="12" t="n">
         <v>27.68</v>
       </c>
-      <c r="S47" s="10" t="n">
+      <c r="S47" s="12" t="n">
         <v>27.72</v>
       </c>
-      <c r="T47" s="10" t="n">
+      <c r="T47" s="12" t="n">
         <v>28.08</v>
       </c>
-      <c r="U47" s="10" t="n">
+      <c r="U47" s="12" t="n">
         <v>27.73</v>
       </c>
-      <c r="V47" s="10" t="n">
+      <c r="V47" s="12" t="n">
         <v>28.07</v>
       </c>
-      <c r="W47" s="10" t="n">
+      <c r="W47" s="12" t="n">
         <v>28.58</v>
       </c>
-      <c r="X47" s="10" t="n">
+      <c r="X47" s="12" t="n">
         <v>28.65</v>
       </c>
-      <c r="Y47" s="10" t="n">
+      <c r="Y47" s="12" t="n">
         <v>27.85</v>
       </c>
-      <c r="Z47" s="10" t="n">
+      <c r="Z47" s="12" t="n">
         <v>28.33</v>
       </c>
-      <c r="AA47" s="10" t="n">
+      <c r="AA47" s="12" t="n">
         <v>28.08</v>
       </c>
-      <c r="AB47" s="10" t="n">
+      <c r="AB47" s="12" t="n">
         <v>29.27</v>
       </c>
-      <c r="AC47" s="10" t="n">
+      <c r="AC47" s="12" t="n">
         <v>28.18</v>
       </c>
-      <c r="AD47" s="10" t="n">
+      <c r="AD47" s="12" t="n">
         <v>28.13</v>
       </c>
-      <c r="AE47" s="10" t="n">
+      <c r="AE47" s="12" t="n">
         <v>27.93</v>
       </c>
-      <c r="AF47" s="10" t="n">
+      <c r="AF47" s="12" t="n">
         <v>28.4</v>
       </c>
-      <c r="AG47" s="10" t="n">
+      <c r="AG47" s="12" t="n">
         <v>27.67</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -4300,7 +4321,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="18" t="n"/>
+      <c r="AK47" s="21" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4311,16 +4332,16 @@
       <c r="B48" s="6" t="n">
         <v>555.25</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="12" t="n">
         <v>30.87</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="12" t="n">
         <v>35.67</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E48" s="12" t="n">
         <v>31.3</v>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="12" t="n">
         <v>30.95</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -4333,19 +4354,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="10" t="n">
+      <c r="I48" s="12" t="n">
         <v>29.83</v>
       </c>
-      <c r="J48" s="10" t="n">
+      <c r="J48" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="K48" s="10" t="n">
+      <c r="K48" s="12" t="n">
         <v>30.7</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L48" s="12" t="n">
         <v>32.82</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="12" t="n">
         <v>36.93</v>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -4358,58 +4379,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="10" t="n">
+      <c r="P48" s="12" t="n">
         <v>30.17</v>
       </c>
-      <c r="Q48" s="10" t="n">
+      <c r="Q48" s="12" t="n">
         <v>30.43</v>
       </c>
-      <c r="R48" s="10" t="n">
+      <c r="R48" s="12" t="n">
         <v>30.48</v>
       </c>
-      <c r="S48" s="10" t="n">
+      <c r="S48" s="12" t="n">
         <v>35.07</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="T48" s="12" t="n">
         <v>35.13</v>
       </c>
-      <c r="U48" s="10" t="n">
+      <c r="U48" s="12" t="n">
         <v>38.18</v>
       </c>
-      <c r="V48" s="10" t="n">
+      <c r="V48" s="12" t="n">
         <v>30.97</v>
       </c>
-      <c r="W48" s="10" t="n">
+      <c r="W48" s="12" t="n">
         <v>29.7</v>
       </c>
-      <c r="X48" s="10" t="n">
+      <c r="X48" s="12" t="n">
         <v>30.2</v>
       </c>
-      <c r="Y48" s="10" t="n">
+      <c r="Y48" s="12" t="n">
         <v>30.97</v>
       </c>
-      <c r="Z48" s="10" t="n">
+      <c r="Z48" s="12" t="n">
         <v>34.18</v>
       </c>
-      <c r="AA48" s="10" t="n">
+      <c r="AA48" s="12" t="n">
         <v>30.1</v>
       </c>
-      <c r="AB48" s="10" t="n">
+      <c r="AB48" s="12" t="n">
         <v>29.78</v>
       </c>
-      <c r="AC48" s="10" t="n">
+      <c r="AC48" s="12" t="n">
         <v>31.43</v>
       </c>
-      <c r="AD48" s="10" t="n">
+      <c r="AD48" s="12" t="n">
         <v>30.87</v>
       </c>
-      <c r="AE48" s="10" t="n">
+      <c r="AE48" s="12" t="n">
         <v>29.88</v>
       </c>
-      <c r="AF48" s="10" t="n">
+      <c r="AF48" s="12" t="n">
         <v>31.67</v>
       </c>
-      <c r="AG48" s="10" t="n">
+      <c r="AG48" s="12" t="n">
         <v>29.67</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -4417,7 +4438,7 @@
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="18" t="n"/>
+      <c r="AK48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4428,16 +4449,16 @@
       <c r="B49" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="12" t="n">
         <v>29.83</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D49" s="12" t="n">
         <v>34.67</v>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="E49" s="12" t="n">
         <v>30.1</v>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="F49" s="12" t="n">
         <v>30.13</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -4450,19 +4471,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="10" t="n">
+      <c r="I49" s="12" t="n">
         <v>30.27</v>
       </c>
-      <c r="J49" s="10" t="n">
+      <c r="J49" s="12" t="n">
         <v>31.17</v>
       </c>
-      <c r="K49" s="10" t="n">
+      <c r="K49" s="12" t="n">
         <v>29.83</v>
       </c>
-      <c r="L49" s="10" t="n">
+      <c r="L49" s="12" t="n">
         <v>30.28</v>
       </c>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="12" t="n">
         <v>33.5</v>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -4475,58 +4496,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P49" s="10" t="n">
+      <c r="P49" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="12" t="n">
         <v>32.07</v>
       </c>
-      <c r="R49" s="10" t="n">
+      <c r="R49" s="12" t="n">
         <v>32.5</v>
       </c>
-      <c r="S49" s="10" t="n">
+      <c r="S49" s="12" t="n">
         <v>32.17</v>
       </c>
-      <c r="T49" s="10" t="n">
+      <c r="T49" s="12" t="n">
         <v>29.88</v>
       </c>
-      <c r="U49" s="10" t="n">
+      <c r="U49" s="12" t="n">
         <v>32.85</v>
       </c>
-      <c r="V49" s="10" t="n">
+      <c r="V49" s="12" t="n">
         <v>29.97</v>
       </c>
-      <c r="W49" s="10" t="n">
+      <c r="W49" s="12" t="n">
         <v>30.85</v>
       </c>
-      <c r="X49" s="10" t="n">
+      <c r="X49" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="Y49" s="10" t="n">
+      <c r="Y49" s="12" t="n">
         <v>30.82</v>
       </c>
-      <c r="Z49" s="10" t="n">
+      <c r="Z49" s="12" t="n">
         <v>33.93</v>
       </c>
-      <c r="AA49" s="10" t="n">
+      <c r="AA49" s="12" t="n">
         <v>30.57</v>
       </c>
-      <c r="AB49" s="10" t="n">
+      <c r="AB49" s="12" t="n">
         <v>30.85</v>
       </c>
-      <c r="AC49" s="10" t="n">
+      <c r="AC49" s="12" t="n">
         <v>32.78</v>
       </c>
-      <c r="AD49" s="10" t="n">
+      <c r="AD49" s="12" t="n">
         <v>31.38</v>
       </c>
-      <c r="AE49" s="10" t="n">
+      <c r="AE49" s="12" t="n">
         <v>30.18</v>
       </c>
-      <c r="AF49" s="10" t="n">
+      <c r="AF49" s="12" t="n">
         <v>31.43</v>
       </c>
-      <c r="AG49" s="10" t="n">
+      <c r="AG49" s="12" t="n">
         <v>30.47</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -4534,7 +4555,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="18" t="n"/>
+      <c r="AK49" s="21" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4545,16 +4566,16 @@
       <c r="B50" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="12" t="n">
         <v>28.7</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="12" t="n">
         <v>33.23</v>
       </c>
-      <c r="E50" s="10" t="n">
+      <c r="E50" s="12" t="n">
         <v>29.02</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="12" t="n">
         <v>28.9</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -4567,19 +4588,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="10" t="n">
+      <c r="I50" s="12" t="n">
         <v>28.7</v>
       </c>
-      <c r="J50" s="10" t="n">
+      <c r="J50" s="12" t="n">
         <v>28.6</v>
       </c>
-      <c r="K50" s="10" t="n">
+      <c r="K50" s="12" t="n">
         <v>28.27</v>
       </c>
-      <c r="L50" s="10" t="n">
+      <c r="L50" s="12" t="n">
         <v>29.25</v>
       </c>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="12" t="n">
         <v>29.67</v>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -4592,58 +4613,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P50" s="10" t="n">
+      <c r="P50" s="12" t="n">
         <v>28.9</v>
       </c>
-      <c r="Q50" s="10" t="n">
+      <c r="Q50" s="12" t="n">
         <v>29.18</v>
       </c>
-      <c r="R50" s="10" t="n">
+      <c r="R50" s="12" t="n">
         <v>31.72</v>
       </c>
-      <c r="S50" s="10" t="n">
+      <c r="S50" s="12" t="n">
         <v>31.28</v>
       </c>
-      <c r="T50" s="10" t="n">
+      <c r="T50" s="12" t="n">
         <v>28.7</v>
       </c>
-      <c r="U50" s="10" t="n">
+      <c r="U50" s="12" t="n">
         <v>30.88</v>
       </c>
-      <c r="V50" s="10" t="n">
+      <c r="V50" s="12" t="n">
         <v>29.17</v>
       </c>
-      <c r="W50" s="10" t="n">
+      <c r="W50" s="12" t="n">
         <v>28.6</v>
       </c>
-      <c r="X50" s="10" t="n">
+      <c r="X50" s="12" t="n">
         <v>29.23</v>
       </c>
-      <c r="Y50" s="10" t="n">
+      <c r="Y50" s="12" t="n">
         <v>32.1</v>
       </c>
-      <c r="Z50" s="10" t="n">
+      <c r="Z50" s="12" t="n">
         <v>28.92</v>
       </c>
-      <c r="AA50" s="10" t="n">
+      <c r="AA50" s="12" t="n">
         <v>29.53</v>
       </c>
-      <c r="AB50" s="10" t="n">
+      <c r="AB50" s="12" t="n">
         <v>29.12</v>
       </c>
-      <c r="AC50" s="10" t="n">
+      <c r="AC50" s="12" t="n">
         <v>29.28</v>
       </c>
-      <c r="AD50" s="10" t="n">
+      <c r="AD50" s="12" t="n">
         <v>29.4</v>
       </c>
-      <c r="AE50" s="10" t="n">
+      <c r="AE50" s="12" t="n">
         <v>28.3</v>
       </c>
-      <c r="AF50" s="10" t="n">
+      <c r="AF50" s="12" t="n">
         <v>28.68</v>
       </c>
-      <c r="AG50" s="10" t="n">
+      <c r="AG50" s="12" t="n">
         <v>29.07</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -4651,124 +4672,124 @@
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="18" t="n"/>
+      <c r="AK50" s="21" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>EL CIUDADANO TV NO AUTORIZADA</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="14" t="n">
         <v>675.25</v>
       </c>
-      <c r="C51" s="14" t="n">
+      <c r="C51" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="16" t="n">
         <v>32.42</v>
       </c>
-      <c r="E51" s="14" t="n">
+      <c r="E51" s="16" t="n">
         <v>30.38</v>
       </c>
-      <c r="F51" s="14" t="n">
+      <c r="F51" s="16" t="n">
         <v>28.95</v>
       </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="n">
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="16" t="n">
         <v>28.37</v>
       </c>
-      <c r="J51" s="14" t="n">
+      <c r="J51" s="16" t="n">
         <v>31.97</v>
       </c>
-      <c r="K51" s="14" t="n">
+      <c r="K51" s="16" t="n">
         <v>30.47</v>
       </c>
-      <c r="L51" s="14" t="n">
+      <c r="L51" s="16" t="n">
         <v>30.97</v>
       </c>
-      <c r="M51" s="14" t="n">
+      <c r="M51" s="16" t="n">
         <v>32.63</v>
       </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="14" t="n">
+      <c r="N51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="16" t="n">
         <v>31.6</v>
       </c>
-      <c r="Q51" s="14" t="n">
+      <c r="Q51" s="16" t="n">
         <v>29.1</v>
       </c>
-      <c r="R51" s="14" t="n">
+      <c r="R51" s="16" t="n">
         <v>29.88</v>
       </c>
-      <c r="S51" s="14" t="n">
+      <c r="S51" s="16" t="n">
         <v>31.85</v>
       </c>
-      <c r="T51" s="14" t="n">
+      <c r="T51" s="16" t="n">
         <v>30.62</v>
       </c>
-      <c r="U51" s="14" t="n">
+      <c r="U51" s="16" t="n">
         <v>32.62</v>
       </c>
-      <c r="V51" s="14" t="n">
+      <c r="V51" s="16" t="n">
         <v>29.52</v>
       </c>
-      <c r="W51" s="14" t="n">
+      <c r="W51" s="16" t="n">
         <v>29.95</v>
       </c>
-      <c r="X51" s="14" t="n">
+      <c r="X51" s="16" t="n">
         <v>29.62</v>
       </c>
-      <c r="Y51" s="14" t="n">
+      <c r="Y51" s="16" t="n">
         <v>30.12</v>
       </c>
-      <c r="Z51" s="14" t="n">
+      <c r="Z51" s="16" t="n">
         <v>31.13</v>
       </c>
-      <c r="AA51" s="14" t="n">
+      <c r="AA51" s="16" t="n">
         <v>30.3</v>
       </c>
-      <c r="AB51" s="14" t="n">
+      <c r="AB51" s="16" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC51" s="14" t="n">
+      <c r="AC51" s="16" t="n">
         <v>29.95</v>
       </c>
-      <c r="AD51" s="14" t="n">
+      <c r="AD51" s="16" t="n">
         <v>28.9</v>
       </c>
-      <c r="AE51" s="14" t="n">
+      <c r="AE51" s="16" t="n">
         <v>29.73</v>
       </c>
-      <c r="AF51" s="14" t="n">
+      <c r="AF51" s="16" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG51" s="14" t="n">
+      <c r="AG51" s="16" t="n">
         <v>30.4</v>
       </c>
-      <c r="AH51" s="12" t="n">
+      <c r="AH51" s="14" t="n">
         <v>30.39</v>
       </c>
-      <c r="AI51" s="12" t="inlineStr"/>
-      <c r="AJ51" s="12" t="inlineStr"/>
-      <c r="AK51" s="19" t="n"/>
+      <c r="AI51" s="14" t="inlineStr"/>
+      <c r="AJ51" s="14" t="inlineStr"/>
+      <c r="AK51" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -306,7 +306,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -329,9 +329,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2476500" cy="1143000"/>
@@ -379,7 +379,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
       <row>34</row>
       <rowOff>0</rowOff>

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCDFECE"/>
         <bgColor rgb="FFCDFECE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
       </patternFill>
     </fill>
     <fill>
@@ -171,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,10 +203,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,13 +218,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -795,7 +807,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -1276,10 +1288,10 @@
       <c r="AG13" s="7" t="n">
         <v>69.26000000000001</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="11" t="n">
         <v>52.3</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="11" t="n">
         <v>237.33</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
@@ -1517,7 +1529,7 @@
       <c r="AH15" s="6" t="n">
         <v>73.55</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="11" t="n">
         <v>299.96</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
@@ -1990,10 +2002,10 @@
       <c r="AG19" s="9" t="n">
         <v>46.35</v>
       </c>
-      <c r="AH19" s="6" t="n">
+      <c r="AH19" s="11" t="n">
         <v>46.54</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="11" t="n">
         <v>499.13</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
@@ -2942,10 +2954,10 @@
       <c r="AG27" s="9" t="n">
         <v>46.65</v>
       </c>
-      <c r="AH27" s="6" t="n">
+      <c r="AH27" s="11" t="n">
         <v>44.34</v>
       </c>
-      <c r="AI27" s="6" t="n">
+      <c r="AI27" s="11" t="n">
         <v>499.69</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
@@ -3061,10 +3073,10 @@
       <c r="AG28" s="9" t="n">
         <v>47.22</v>
       </c>
-      <c r="AH28" s="6" t="n">
+      <c r="AH28" s="11" t="n">
         <v>45.26</v>
       </c>
-      <c r="AI28" s="6" t="n">
+      <c r="AI28" s="11" t="n">
         <v>499.61</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
@@ -3183,130 +3195,130 @@
       <c r="AH29" s="6" t="n">
         <v>74.5</v>
       </c>
-      <c r="AI29" s="6" t="n">
+      <c r="AI29" s="11" t="n">
         <v>273.47</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
       <c r="AK29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>LA VOZ DE ARUTAM (NO AUTORIZADA)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="13" t="n">
         <v>107.3</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="14" t="n">
         <v>43.06</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="15" t="n">
         <v>41.51</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="14" t="n">
         <v>47.48</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="14" t="n">
         <v>48.84</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="n">
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="n">
         <v>49.17</v>
       </c>
-      <c r="J30" s="14" t="n">
+      <c r="J30" s="15" t="n">
         <v>40.76</v>
       </c>
-      <c r="K30" s="14" t="n">
+      <c r="K30" s="15" t="n">
         <v>41.36</v>
       </c>
-      <c r="L30" s="13" t="n">
+      <c r="L30" s="14" t="n">
         <v>46.16</v>
       </c>
-      <c r="M30" s="13" t="n">
+      <c r="M30" s="14" t="n">
         <v>43.89</v>
       </c>
-      <c r="N30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" s="13" t="n">
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="14" t="n">
         <v>53.46</v>
       </c>
-      <c r="Q30" s="15" t="n">
+      <c r="Q30" s="16" t="n">
         <v>54.55</v>
       </c>
-      <c r="R30" s="15" t="n">
+      <c r="R30" s="16" t="n">
         <v>56.15</v>
       </c>
-      <c r="S30" s="13" t="n">
+      <c r="S30" s="14" t="n">
         <v>49.19</v>
       </c>
-      <c r="T30" s="13" t="n">
+      <c r="T30" s="14" t="n">
         <v>47.4</v>
       </c>
-      <c r="U30" s="13" t="n">
+      <c r="U30" s="14" t="n">
         <v>46.51</v>
       </c>
-      <c r="V30" s="13" t="n">
+      <c r="V30" s="14" t="n">
         <v>50.82</v>
       </c>
-      <c r="W30" s="15" t="n">
+      <c r="W30" s="16" t="n">
         <v>55.1</v>
       </c>
-      <c r="X30" s="15" t="n">
+      <c r="X30" s="16" t="n">
         <v>54.54</v>
       </c>
-      <c r="Y30" s="13" t="n">
+      <c r="Y30" s="14" t="n">
         <v>49.52</v>
       </c>
-      <c r="Z30" s="13" t="n">
+      <c r="Z30" s="14" t="n">
         <v>47.54</v>
       </c>
-      <c r="AA30" s="15" t="n">
+      <c r="AA30" s="16" t="n">
         <v>54.18</v>
       </c>
-      <c r="AB30" s="15" t="n">
+      <c r="AB30" s="16" t="n">
         <v>55.12</v>
       </c>
-      <c r="AC30" s="13" t="n">
+      <c r="AC30" s="14" t="n">
         <v>48.65</v>
       </c>
-      <c r="AD30" s="13" t="n">
+      <c r="AD30" s="14" t="n">
         <v>53.31</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="14" t="n">
         <v>49.16</v>
       </c>
-      <c r="AF30" s="13" t="n">
+      <c r="AF30" s="14" t="n">
         <v>50.49</v>
       </c>
-      <c r="AG30" s="13" t="n">
+      <c r="AG30" s="14" t="n">
         <v>51.46</v>
       </c>
-      <c r="AH30" s="12" t="n">
+      <c r="AH30" s="17" t="n">
         <v>49.24</v>
       </c>
-      <c r="AI30" s="12" t="n">
+      <c r="AI30" s="17" t="n">
         <v>498.71</v>
       </c>
-      <c r="AJ30" s="12" t="inlineStr"/>
-      <c r="AK30" s="16" t="inlineStr"/>
+      <c r="AJ30" s="13" t="inlineStr"/>
+      <c r="AK30" s="18" t="inlineStr"/>
     </row>
     <row r="31"/>
     <row r="32"/>
@@ -3355,7 +3367,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3493,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK40" s="17" t="n"/>
+      <c r="AK40" s="19" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3593,12 +3605,12 @@
       <c r="AG41" s="7" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="AH41" s="6" t="n">
+      <c r="AH41" s="7" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="18" t="n"/>
+      <c r="AK41" s="20" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3710,12 +3722,12 @@
       <c r="AG42" s="7" t="n">
         <v>109.2</v>
       </c>
-      <c r="AH42" s="6" t="n">
+      <c r="AH42" s="7" t="n">
         <v>109.02</v>
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="18" t="n"/>
+      <c r="AK42" s="20" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3751,7 +3763,7 @@
       <c r="I43" s="10" t="n">
         <v>36.3</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" s="10" t="n">
         <v>49.5</v>
       </c>
       <c r="K43" s="10" t="n">
@@ -3760,7 +3772,7 @@
       <c r="L43" s="10" t="n">
         <v>40.53</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="10" t="n">
         <v>50.5</v>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -3782,16 +3794,16 @@
       <c r="R43" s="10" t="n">
         <v>37.27</v>
       </c>
-      <c r="S43" s="9" t="n">
+      <c r="S43" s="10" t="n">
         <v>47.38</v>
       </c>
-      <c r="T43" s="9" t="n">
+      <c r="T43" s="10" t="n">
         <v>51.48</v>
       </c>
-      <c r="U43" s="7" t="n">
+      <c r="U43" s="9" t="n">
         <v>56.65</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="10" t="n">
         <v>45.32</v>
       </c>
       <c r="W43" s="10" t="n">
@@ -3803,7 +3815,7 @@
       <c r="Y43" s="10" t="n">
         <v>41.78</v>
       </c>
-      <c r="Z43" s="9" t="n">
+      <c r="Z43" s="10" t="n">
         <v>44.7</v>
       </c>
       <c r="AA43" s="10" t="n">
@@ -3827,12 +3839,12 @@
       <c r="AG43" s="10" t="n">
         <v>39.3</v>
       </c>
-      <c r="AH43" s="6" t="n">
+      <c r="AH43" s="11" t="n">
         <v>42.16</v>
       </c>
       <c r="AI43" s="6" t="inlineStr"/>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="18" t="n"/>
+      <c r="AK43" s="20" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3905,7 +3917,7 @@
       <c r="T44" s="10" t="n">
         <v>42.85</v>
       </c>
-      <c r="U44" s="9" t="n">
+      <c r="U44" s="10" t="n">
         <v>43.72</v>
       </c>
       <c r="V44" s="10" t="n">
@@ -3944,12 +3956,12 @@
       <c r="AG44" s="10" t="n">
         <v>37.27</v>
       </c>
-      <c r="AH44" s="6" t="n">
+      <c r="AH44" s="11" t="n">
         <v>38.46</v>
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="18" t="n"/>
+      <c r="AK44" s="20" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4061,12 +4073,12 @@
       <c r="AG45" s="7" t="n">
         <v>93.43000000000001</v>
       </c>
-      <c r="AH45" s="6" t="n">
+      <c r="AH45" s="7" t="n">
         <v>93.8</v>
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="18" t="n"/>
+      <c r="AK45" s="20" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4178,12 +4190,12 @@
       <c r="AG46" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="AH46" s="6" t="n">
+      <c r="AH46" s="11" t="n">
         <v>27.43</v>
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="18" t="n"/>
+      <c r="AK46" s="20" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4295,12 +4307,12 @@
       <c r="AG47" s="10" t="n">
         <v>27.67</v>
       </c>
-      <c r="AH47" s="6" t="n">
+      <c r="AH47" s="11" t="n">
         <v>28.04</v>
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="18" t="n"/>
+      <c r="AK47" s="20" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4412,12 +4424,12 @@
       <c r="AG48" s="10" t="n">
         <v>29.67</v>
       </c>
-      <c r="AH48" s="6" t="n">
+      <c r="AH48" s="11" t="n">
         <v>32.04</v>
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="18" t="n"/>
+      <c r="AK48" s="20" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4529,12 +4541,12 @@
       <c r="AG49" s="10" t="n">
         <v>30.47</v>
       </c>
-      <c r="AH49" s="6" t="n">
+      <c r="AH49" s="11" t="n">
         <v>31.29</v>
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="18" t="n"/>
+      <c r="AK49" s="20" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4646,129 +4658,129 @@
       <c r="AG50" s="10" t="n">
         <v>29.07</v>
       </c>
-      <c r="AH50" s="6" t="n">
+      <c r="AH50" s="11" t="n">
         <v>29.5</v>
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="18" t="n"/>
+      <c r="AK50" s="20" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>EL CIUDADANO TV NO AUTORIZADA</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="13" t="n">
         <v>675.25</v>
       </c>
-      <c r="C51" s="14" t="n">
+      <c r="C51" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="15" t="n">
         <v>32.42</v>
       </c>
-      <c r="E51" s="14" t="n">
+      <c r="E51" s="15" t="n">
         <v>30.38</v>
       </c>
-      <c r="F51" s="14" t="n">
+      <c r="F51" s="15" t="n">
         <v>28.95</v>
       </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="n">
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="n">
         <v>28.37</v>
       </c>
-      <c r="J51" s="14" t="n">
+      <c r="J51" s="15" t="n">
         <v>31.97</v>
       </c>
-      <c r="K51" s="14" t="n">
+      <c r="K51" s="15" t="n">
         <v>30.47</v>
       </c>
-      <c r="L51" s="14" t="n">
+      <c r="L51" s="15" t="n">
         <v>30.97</v>
       </c>
-      <c r="M51" s="14" t="n">
+      <c r="M51" s="15" t="n">
         <v>32.63</v>
       </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="14" t="n">
+      <c r="N51" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="15" t="n">
         <v>31.6</v>
       </c>
-      <c r="Q51" s="14" t="n">
+      <c r="Q51" s="15" t="n">
         <v>29.1</v>
       </c>
-      <c r="R51" s="14" t="n">
+      <c r="R51" s="15" t="n">
         <v>29.88</v>
       </c>
-      <c r="S51" s="14" t="n">
+      <c r="S51" s="15" t="n">
         <v>31.85</v>
       </c>
-      <c r="T51" s="14" t="n">
+      <c r="T51" s="15" t="n">
         <v>30.62</v>
       </c>
-      <c r="U51" s="14" t="n">
+      <c r="U51" s="15" t="n">
         <v>32.62</v>
       </c>
-      <c r="V51" s="14" t="n">
+      <c r="V51" s="15" t="n">
         <v>29.52</v>
       </c>
-      <c r="W51" s="14" t="n">
+      <c r="W51" s="15" t="n">
         <v>29.95</v>
       </c>
-      <c r="X51" s="14" t="n">
+      <c r="X51" s="15" t="n">
         <v>29.62</v>
       </c>
-      <c r="Y51" s="14" t="n">
+      <c r="Y51" s="15" t="n">
         <v>30.12</v>
       </c>
-      <c r="Z51" s="14" t="n">
+      <c r="Z51" s="15" t="n">
         <v>31.13</v>
       </c>
-      <c r="AA51" s="14" t="n">
+      <c r="AA51" s="15" t="n">
         <v>30.3</v>
       </c>
-      <c r="AB51" s="14" t="n">
+      <c r="AB51" s="15" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC51" s="14" t="n">
+      <c r="AC51" s="15" t="n">
         <v>29.95</v>
       </c>
-      <c r="AD51" s="14" t="n">
+      <c r="AD51" s="15" t="n">
         <v>28.9</v>
       </c>
-      <c r="AE51" s="14" t="n">
+      <c r="AE51" s="15" t="n">
         <v>29.73</v>
       </c>
-      <c r="AF51" s="14" t="n">
+      <c r="AF51" s="15" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG51" s="14" t="n">
+      <c r="AG51" s="15" t="n">
         <v>30.4</v>
       </c>
-      <c r="AH51" s="12" t="n">
+      <c r="AH51" s="17" t="n">
         <v>30.39</v>
       </c>
-      <c r="AI51" s="12" t="inlineStr"/>
-      <c r="AJ51" s="12" t="inlineStr"/>
-      <c r="AK51" s="19" t="n"/>
+      <c r="AI51" s="13" t="inlineStr"/>
+      <c r="AJ51" s="13" t="inlineStr"/>
+      <c r="AK51" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -45,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFC4A2C"/>
-        <bgColor rgb="FFFC4A2C"/>
+        <fgColor rgb="FFFFFE9F"/>
+        <bgColor rgb="FFFFFE9F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFE9F"/>
-        <bgColor rgb="FFFFFE9F"/>
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
       </patternFill>
     </fill>
     <fill>
@@ -203,13 +203,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,7 +218,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,7 +227,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>
@@ -1050,10 +1050,10 @@
       <c r="AG11" s="7" t="n">
         <v>79.95</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="7" t="n">
         <v>76.17</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="7" t="n">
         <v>172.46</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
@@ -1169,10 +1169,10 @@
       <c r="AG12" s="7" t="n">
         <v>77.42</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="7" t="n">
         <v>62.84</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="7" t="n">
         <v>205.41</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       <c r="AG13" s="7" t="n">
         <v>69.26000000000001</v>
       </c>
-      <c r="AH13" s="11" t="n">
+      <c r="AH13" s="9" t="n">
         <v>52.3</v>
       </c>
       <c r="AI13" s="11" t="n">
@@ -1407,10 +1407,10 @@
       <c r="AG14" s="7" t="n">
         <v>109.6</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="7" t="n">
         <v>108.19</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="7" t="n">
         <v>137.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
@@ -1526,7 +1526,7 @@
       <c r="AG15" s="7" t="n">
         <v>93.54000000000001</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="7" t="n">
         <v>73.55</v>
       </c>
       <c r="AI15" s="11" t="n">
@@ -1645,10 +1645,10 @@
       <c r="AG16" s="7" t="n">
         <v>104.34</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="7" t="n">
         <v>101.88</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="7" t="n">
         <v>149.91</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
@@ -1764,10 +1764,10 @@
       <c r="AG17" s="7" t="n">
         <v>104.2</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="7" t="n">
         <v>103.73</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="7" t="n">
         <v>187.17</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
       <c r="AG18" s="7" t="n">
         <v>64.59</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="7" t="n">
         <v>63.23</v>
       </c>
-      <c r="AI18" s="6" t="n">
+      <c r="AI18" s="7" t="n">
         <v>174.55</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       <c r="AG19" s="9" t="n">
         <v>46.35</v>
       </c>
-      <c r="AH19" s="11" t="n">
+      <c r="AH19" s="9" t="n">
         <v>46.54</v>
       </c>
       <c r="AI19" s="11" t="n">
@@ -2121,10 +2121,10 @@
       <c r="AG20" s="7" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="7" t="n">
         <v>86.86</v>
       </c>
-      <c r="AI20" s="6" t="n">
+      <c r="AI20" s="7" t="n">
         <v>112.27</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
       <c r="AG21" s="7" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="7" t="n">
         <v>101.82</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="7" t="n">
         <v>208.17</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
       <c r="AG22" s="7" t="n">
         <v>97.05</v>
       </c>
-      <c r="AH22" s="6" t="n">
+      <c r="AH22" s="7" t="n">
         <v>97.83</v>
       </c>
-      <c r="AI22" s="6" t="n">
+      <c r="AI22" s="7" t="n">
         <v>131.9</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
       <c r="AG23" s="7" t="n">
         <v>109.65</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH23" s="7" t="n">
         <v>92.2</v>
       </c>
-      <c r="AI23" s="6" t="n">
+      <c r="AI23" s="7" t="n">
         <v>217.44</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
       <c r="AG24" s="7" t="n">
         <v>107.92</v>
       </c>
-      <c r="AH24" s="6" t="n">
+      <c r="AH24" s="7" t="n">
         <v>107.96</v>
       </c>
-      <c r="AI24" s="6" t="n">
+      <c r="AI24" s="7" t="n">
         <v>179.35</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
       <c r="AG25" s="7" t="n">
         <v>99.05</v>
       </c>
-      <c r="AH25" s="6" t="n">
+      <c r="AH25" s="7" t="n">
         <v>99.06</v>
       </c>
-      <c r="AI25" s="6" t="n">
+      <c r="AI25" s="7" t="n">
         <v>37.91</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
       <c r="AG26" s="7" t="n">
         <v>90.84999999999999</v>
       </c>
-      <c r="AH26" s="6" t="n">
+      <c r="AH26" s="7" t="n">
         <v>89.51000000000001</v>
       </c>
-      <c r="AI26" s="6" t="n">
+      <c r="AI26" s="7" t="n">
         <v>162.72</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
@@ -2954,7 +2954,7 @@
       <c r="AG27" s="9" t="n">
         <v>46.65</v>
       </c>
-      <c r="AH27" s="11" t="n">
+      <c r="AH27" s="9" t="n">
         <v>44.34</v>
       </c>
       <c r="AI27" s="11" t="n">
@@ -3073,7 +3073,7 @@
       <c r="AG28" s="9" t="n">
         <v>47.22</v>
       </c>
-      <c r="AH28" s="11" t="n">
+      <c r="AH28" s="9" t="n">
         <v>45.26</v>
       </c>
       <c r="AI28" s="11" t="n">
@@ -3192,7 +3192,7 @@
       <c r="AG29" s="7" t="n">
         <v>74.38</v>
       </c>
-      <c r="AH29" s="6" t="n">
+      <c r="AH29" s="7" t="n">
         <v>74.5</v>
       </c>
       <c r="AI29" s="11" t="n">
@@ -3311,7 +3311,7 @@
       <c r="AG30" s="14" t="n">
         <v>51.46</v>
       </c>
-      <c r="AH30" s="17" t="n">
+      <c r="AH30" s="14" t="n">
         <v>49.24</v>
       </c>
       <c r="AI30" s="17" t="n">
@@ -3367,7 +3367,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -206,9 +206,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -219,9 +216,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -235,6 +229,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1190,7 +1190,7 @@
       <c r="C13" s="9" t="n">
         <v>45.5</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>41.8</v>
       </c>
       <c r="E13" s="9" t="n">
@@ -1215,7 +1215,7 @@
       <c r="J13" s="9" t="n">
         <v>43.55</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K13" s="9" t="n">
         <v>42.94</v>
       </c>
       <c r="L13" s="9" t="n">
@@ -1291,7 +1291,7 @@
       <c r="AH13" s="9" t="n">
         <v>52.3</v>
       </c>
-      <c r="AI13" s="11" t="n">
+      <c r="AI13" s="10" t="n">
         <v>237.33</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       <c r="C15" s="9" t="n">
         <v>45.29</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>42.04</v>
       </c>
       <c r="E15" s="9" t="n">
@@ -1450,7 +1450,7 @@
       <c r="I15" s="9" t="n">
         <v>50.55</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" s="9" t="n">
         <v>42.94</v>
       </c>
       <c r="K15" s="9" t="n">
@@ -1529,7 +1529,7 @@
       <c r="AH15" s="7" t="n">
         <v>73.55</v>
       </c>
-      <c r="AI15" s="11" t="n">
+      <c r="AI15" s="10" t="n">
         <v>299.96</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
       <c r="C19" s="9" t="n">
         <v>45.01</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>42.51</v>
       </c>
       <c r="E19" s="9" t="n">
@@ -1935,7 +1935,7 @@
       <c r="L19" s="9" t="n">
         <v>45.42</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="9" t="n">
         <v>42.99</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
@@ -1978,7 +1978,7 @@
       <c r="Y19" s="9" t="n">
         <v>44.94</v>
       </c>
-      <c r="Z19" s="10" t="n">
+      <c r="Z19" s="9" t="n">
         <v>42.99</v>
       </c>
       <c r="AA19" s="9" t="n">
@@ -2005,7 +2005,7 @@
       <c r="AH19" s="9" t="n">
         <v>46.54</v>
       </c>
-      <c r="AI19" s="11" t="n">
+      <c r="AI19" s="10" t="n">
         <v>499.13</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
       <c r="B27" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="9" t="n">
         <v>40.55</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="9" t="n">
         <v>40.37</v>
       </c>
       <c r="E27" s="9" t="n">
@@ -2881,10 +2881,10 @@
       <c r="J27" s="9" t="n">
         <v>44.02</v>
       </c>
-      <c r="K27" s="10" t="n">
+      <c r="K27" s="9" t="n">
         <v>39.78</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L27" s="9" t="n">
         <v>42.79</v>
       </c>
       <c r="M27" s="9" t="n">
@@ -2909,7 +2909,7 @@
       <c r="R27" s="9" t="n">
         <v>45.51</v>
       </c>
-      <c r="S27" s="10" t="n">
+      <c r="S27" s="9" t="n">
         <v>41.6</v>
       </c>
       <c r="T27" s="9" t="n">
@@ -2930,7 +2930,7 @@
       <c r="Y27" s="9" t="n">
         <v>43.96</v>
       </c>
-      <c r="Z27" s="10" t="n">
+      <c r="Z27" s="9" t="n">
         <v>42.04</v>
       </c>
       <c r="AA27" s="9" t="n">
@@ -2939,13 +2939,13 @@
       <c r="AB27" s="9" t="n">
         <v>44.94</v>
       </c>
-      <c r="AC27" s="10" t="n">
+      <c r="AC27" s="9" t="n">
         <v>42.45</v>
       </c>
       <c r="AD27" s="9" t="n">
         <v>45.12</v>
       </c>
-      <c r="AE27" s="10" t="n">
+      <c r="AE27" s="9" t="n">
         <v>42.72</v>
       </c>
       <c r="AF27" s="9" t="n">
@@ -2957,7 +2957,7 @@
       <c r="AH27" s="9" t="n">
         <v>44.34</v>
       </c>
-      <c r="AI27" s="11" t="n">
+      <c r="AI27" s="10" t="n">
         <v>499.69</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
       <c r="B28" s="6" t="n">
         <v>104.9</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="9" t="n">
         <v>42.55</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="9" t="n">
         <v>40.56</v>
       </c>
       <c r="E28" s="9" t="n">
@@ -3076,7 +3076,7 @@
       <c r="AH28" s="9" t="n">
         <v>45.26</v>
       </c>
-      <c r="AI28" s="11" t="n">
+      <c r="AI28" s="10" t="n">
         <v>499.61</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
@@ -3195,130 +3195,130 @@
       <c r="AH29" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="AI29" s="11" t="n">
+      <c r="AI29" s="10" t="n">
         <v>273.47</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
       <c r="AK29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>LA VOZ DE ARUTAM (NO AUTORIZADA)</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n">
+      <c r="B30" s="12" t="n">
         <v>107.3</v>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="13" t="n">
         <v>43.06</v>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="13" t="n">
         <v>41.51</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="13" t="n">
         <v>47.48</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="13" t="n">
         <v>48.84</v>
       </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="n">
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="n">
         <v>49.17</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="13" t="n">
         <v>40.76</v>
       </c>
-      <c r="K30" s="15" t="n">
+      <c r="K30" s="13" t="n">
         <v>41.36</v>
       </c>
-      <c r="L30" s="14" t="n">
+      <c r="L30" s="13" t="n">
         <v>46.16</v>
       </c>
-      <c r="M30" s="14" t="n">
+      <c r="M30" s="13" t="n">
         <v>43.89</v>
       </c>
-      <c r="N30" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" s="14" t="n">
+      <c r="N30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="13" t="n">
         <v>53.46</v>
       </c>
-      <c r="Q30" s="16" t="n">
+      <c r="Q30" s="14" t="n">
         <v>54.55</v>
       </c>
-      <c r="R30" s="16" t="n">
+      <c r="R30" s="14" t="n">
         <v>56.15</v>
       </c>
-      <c r="S30" s="14" t="n">
+      <c r="S30" s="13" t="n">
         <v>49.19</v>
       </c>
-      <c r="T30" s="14" t="n">
+      <c r="T30" s="13" t="n">
         <v>47.4</v>
       </c>
-      <c r="U30" s="14" t="n">
+      <c r="U30" s="13" t="n">
         <v>46.51</v>
       </c>
-      <c r="V30" s="14" t="n">
+      <c r="V30" s="13" t="n">
         <v>50.82</v>
       </c>
-      <c r="W30" s="16" t="n">
+      <c r="W30" s="14" t="n">
         <v>55.1</v>
       </c>
-      <c r="X30" s="16" t="n">
+      <c r="X30" s="14" t="n">
         <v>54.54</v>
       </c>
-      <c r="Y30" s="14" t="n">
+      <c r="Y30" s="13" t="n">
         <v>49.52</v>
       </c>
-      <c r="Z30" s="14" t="n">
+      <c r="Z30" s="13" t="n">
         <v>47.54</v>
       </c>
-      <c r="AA30" s="16" t="n">
+      <c r="AA30" s="14" t="n">
         <v>54.18</v>
       </c>
-      <c r="AB30" s="16" t="n">
+      <c r="AB30" s="14" t="n">
         <v>55.12</v>
       </c>
-      <c r="AC30" s="14" t="n">
+      <c r="AC30" s="13" t="n">
         <v>48.65</v>
       </c>
-      <c r="AD30" s="14" t="n">
+      <c r="AD30" s="13" t="n">
         <v>53.31</v>
       </c>
-      <c r="AE30" s="14" t="n">
+      <c r="AE30" s="13" t="n">
         <v>49.16</v>
       </c>
-      <c r="AF30" s="14" t="n">
+      <c r="AF30" s="13" t="n">
         <v>50.49</v>
       </c>
-      <c r="AG30" s="14" t="n">
+      <c r="AG30" s="13" t="n">
         <v>51.46</v>
       </c>
-      <c r="AH30" s="14" t="n">
+      <c r="AH30" s="13" t="n">
         <v>49.24</v>
       </c>
-      <c r="AI30" s="17" t="n">
+      <c r="AI30" s="15" t="n">
         <v>498.71</v>
       </c>
-      <c r="AJ30" s="13" t="inlineStr"/>
-      <c r="AK30" s="18" t="inlineStr"/>
+      <c r="AJ30" s="12" t="inlineStr"/>
+      <c r="AK30" s="16" t="inlineStr"/>
     </row>
     <row r="31"/>
     <row r="32"/>
@@ -3493,7 +3493,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK40" s="19" t="n"/>
+      <c r="AK40" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="20" t="n"/>
+      <c r="AK41" s="18" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="20" t="n"/>
+      <c r="AK42" s="18" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3738,16 +3738,16 @@
       <c r="B43" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="19" t="n">
         <v>38.13</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="19" t="n">
         <v>41.13</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="19" t="n">
         <v>41.17</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="19" t="n">
         <v>36.3</v>
       </c>
-      <c r="J43" s="10" t="n">
+      <c r="J43" s="19" t="n">
         <v>49.5</v>
       </c>
-      <c r="K43" s="10" t="n">
+      <c r="K43" s="19" t="n">
         <v>37.1</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L43" s="19" t="n">
         <v>40.53</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="M43" s="19" t="n">
         <v>50.5</v>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -3785,66 +3785,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P43" s="10" t="n">
+      <c r="P43" s="19" t="n">
         <v>39.87</v>
       </c>
-      <c r="Q43" s="10" t="n">
+      <c r="Q43" s="19" t="n">
         <v>38.13</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="19" t="n">
         <v>37.27</v>
       </c>
-      <c r="S43" s="10" t="n">
+      <c r="S43" s="19" t="n">
         <v>47.38</v>
       </c>
-      <c r="T43" s="10" t="n">
+      <c r="T43" s="19" t="n">
         <v>51.48</v>
       </c>
       <c r="U43" s="9" t="n">
         <v>56.65</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="V43" s="19" t="n">
         <v>45.32</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="19" t="n">
         <v>41.1</v>
       </c>
-      <c r="X43" s="10" t="n">
+      <c r="X43" s="19" t="n">
         <v>39.07</v>
       </c>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="19" t="n">
         <v>41.78</v>
       </c>
-      <c r="Z43" s="10" t="n">
+      <c r="Z43" s="19" t="n">
         <v>44.7</v>
       </c>
-      <c r="AA43" s="10" t="n">
+      <c r="AA43" s="19" t="n">
         <v>42.47</v>
       </c>
-      <c r="AB43" s="10" t="n">
+      <c r="AB43" s="19" t="n">
         <v>37.5</v>
       </c>
-      <c r="AC43" s="10" t="n">
+      <c r="AC43" s="19" t="n">
         <v>39.95</v>
       </c>
-      <c r="AD43" s="10" t="n">
+      <c r="AD43" s="19" t="n">
         <v>38.4</v>
       </c>
-      <c r="AE43" s="10" t="n">
+      <c r="AE43" s="19" t="n">
         <v>39.77</v>
       </c>
-      <c r="AF43" s="10" t="n">
+      <c r="AF43" s="19" t="n">
         <v>41.9</v>
       </c>
-      <c r="AG43" s="10" t="n">
+      <c r="AG43" s="19" t="n">
         <v>39.3</v>
       </c>
-      <c r="AH43" s="11" t="n">
+      <c r="AH43" s="19" t="n">
         <v>42.16</v>
       </c>
       <c r="AI43" s="6" t="inlineStr"/>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="20" t="n"/>
+      <c r="AK43" s="18" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3855,16 +3855,16 @@
       <c r="B44" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="19" t="n">
         <v>36.4</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="19" t="n">
         <v>37.47</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="19" t="n">
         <v>39.78</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="19" t="n">
         <v>41.35</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3877,19 +3877,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="10" t="n">
+      <c r="I44" s="19" t="n">
         <v>36.1</v>
       </c>
-      <c r="J44" s="10" t="n">
+      <c r="J44" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="K44" s="10" t="n">
+      <c r="K44" s="19" t="n">
         <v>37.07</v>
       </c>
-      <c r="L44" s="10" t="n">
+      <c r="L44" s="19" t="n">
         <v>37.3</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="19" t="n">
         <v>39.17</v>
       </c>
       <c r="N44" s="6" t="inlineStr">
@@ -3902,66 +3902,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P44" s="10" t="n">
+      <c r="P44" s="19" t="n">
         <v>36.13</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="19" t="n">
         <v>36.55</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="19" t="n">
         <v>37.55</v>
       </c>
-      <c r="S44" s="10" t="n">
+      <c r="S44" s="19" t="n">
         <v>37.77</v>
       </c>
-      <c r="T44" s="10" t="n">
+      <c r="T44" s="19" t="n">
         <v>42.85</v>
       </c>
-      <c r="U44" s="10" t="n">
+      <c r="U44" s="19" t="n">
         <v>43.72</v>
       </c>
-      <c r="V44" s="10" t="n">
+      <c r="V44" s="19" t="n">
         <v>42.25</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="19" t="n">
         <v>39.5</v>
       </c>
-      <c r="X44" s="10" t="n">
+      <c r="X44" s="19" t="n">
         <v>37.32</v>
       </c>
-      <c r="Y44" s="10" t="n">
+      <c r="Y44" s="19" t="n">
         <v>38.07</v>
       </c>
-      <c r="Z44" s="10" t="n">
+      <c r="Z44" s="19" t="n">
         <v>37.63</v>
       </c>
-      <c r="AA44" s="10" t="n">
+      <c r="AA44" s="19" t="n">
         <v>40.42</v>
       </c>
-      <c r="AB44" s="10" t="n">
+      <c r="AB44" s="19" t="n">
         <v>38.12</v>
       </c>
-      <c r="AC44" s="10" t="n">
+      <c r="AC44" s="19" t="n">
         <v>36.5</v>
       </c>
-      <c r="AD44" s="10" t="n">
+      <c r="AD44" s="19" t="n">
         <v>36.72</v>
       </c>
-      <c r="AE44" s="10" t="n">
+      <c r="AE44" s="19" t="n">
         <v>36.95</v>
       </c>
-      <c r="AF44" s="10" t="n">
+      <c r="AF44" s="19" t="n">
         <v>39.42</v>
       </c>
-      <c r="AG44" s="10" t="n">
+      <c r="AG44" s="19" t="n">
         <v>37.27</v>
       </c>
-      <c r="AH44" s="11" t="n">
+      <c r="AH44" s="19" t="n">
         <v>38.46</v>
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="20" t="n"/>
+      <c r="AK44" s="18" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="20" t="n"/>
+      <c r="AK45" s="18" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4089,16 +4089,16 @@
       <c r="B46" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="19" t="n">
         <v>27.47</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="19" t="n">
         <v>26.83</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="19" t="n">
         <v>28.47</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="19" t="n">
         <v>27.65</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -4111,19 +4111,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="10" t="n">
+      <c r="I46" s="19" t="n">
         <v>26.77</v>
       </c>
-      <c r="J46" s="10" t="n">
+      <c r="J46" s="19" t="n">
         <v>27.47</v>
       </c>
-      <c r="K46" s="10" t="n">
+      <c r="K46" s="19" t="n">
         <v>26.73</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" s="19" t="n">
         <v>26.62</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="19" t="n">
         <v>26.77</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -4136,66 +4136,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="10" t="n">
+      <c r="P46" s="19" t="n">
         <v>27.73</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="19" t="n">
         <v>26.82</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="19" t="n">
         <v>26.38</v>
       </c>
-      <c r="S46" s="10" t="n">
+      <c r="S46" s="19" t="n">
         <v>27.02</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="T46" s="19" t="n">
         <v>26.75</v>
       </c>
-      <c r="U46" s="10" t="n">
+      <c r="U46" s="19" t="n">
         <v>27.97</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="19" t="n">
         <v>26.12</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="19" t="n">
         <v>26.88</v>
       </c>
-      <c r="X46" s="10" t="n">
+      <c r="X46" s="19" t="n">
         <v>26.98</v>
       </c>
-      <c r="Y46" s="10" t="n">
+      <c r="Y46" s="19" t="n">
         <v>26.9</v>
       </c>
-      <c r="Z46" s="10" t="n">
+      <c r="Z46" s="19" t="n">
         <v>35.83</v>
       </c>
-      <c r="AA46" s="10" t="n">
+      <c r="AA46" s="19" t="n">
         <v>27.43</v>
       </c>
-      <c r="AB46" s="10" t="n">
+      <c r="AB46" s="19" t="n">
         <v>26.72</v>
       </c>
-      <c r="AC46" s="10" t="n">
+      <c r="AC46" s="19" t="n">
         <v>26.77</v>
       </c>
-      <c r="AD46" s="10" t="n">
+      <c r="AD46" s="19" t="n">
         <v>26.87</v>
       </c>
-      <c r="AE46" s="10" t="n">
+      <c r="AE46" s="19" t="n">
         <v>28.92</v>
       </c>
-      <c r="AF46" s="10" t="n">
+      <c r="AF46" s="19" t="n">
         <v>27.12</v>
       </c>
-      <c r="AG46" s="10" t="n">
+      <c r="AG46" s="19" t="n">
         <v>26.6</v>
       </c>
-      <c r="AH46" s="11" t="n">
+      <c r="AH46" s="19" t="n">
         <v>27.43</v>
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="20" t="n"/>
+      <c r="AK46" s="18" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4206,16 +4206,16 @@
       <c r="B47" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="19" t="n">
         <v>28.37</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D47" s="19" t="n">
         <v>27.92</v>
       </c>
-      <c r="E47" s="10" t="n">
+      <c r="E47" s="19" t="n">
         <v>27.95</v>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F47" s="19" t="n">
         <v>27.78</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -4228,19 +4228,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="10" t="n">
+      <c r="I47" s="19" t="n">
         <v>27.37</v>
       </c>
-      <c r="J47" s="10" t="n">
+      <c r="J47" s="19" t="n">
         <v>27.83</v>
       </c>
-      <c r="K47" s="10" t="n">
+      <c r="K47" s="19" t="n">
         <v>27.77</v>
       </c>
-      <c r="L47" s="10" t="n">
+      <c r="L47" s="19" t="n">
         <v>28.52</v>
       </c>
-      <c r="M47" s="10" t="n">
+      <c r="M47" s="19" t="n">
         <v>28.13</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -4253,66 +4253,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="10" t="n">
+      <c r="P47" s="19" t="n">
         <v>27.4</v>
       </c>
-      <c r="Q47" s="10" t="n">
+      <c r="Q47" s="19" t="n">
         <v>27.75</v>
       </c>
-      <c r="R47" s="10" t="n">
+      <c r="R47" s="19" t="n">
         <v>27.68</v>
       </c>
-      <c r="S47" s="10" t="n">
+      <c r="S47" s="19" t="n">
         <v>27.72</v>
       </c>
-      <c r="T47" s="10" t="n">
+      <c r="T47" s="19" t="n">
         <v>28.08</v>
       </c>
-      <c r="U47" s="10" t="n">
+      <c r="U47" s="19" t="n">
         <v>27.73</v>
       </c>
-      <c r="V47" s="10" t="n">
+      <c r="V47" s="19" t="n">
         <v>28.07</v>
       </c>
-      <c r="W47" s="10" t="n">
+      <c r="W47" s="19" t="n">
         <v>28.58</v>
       </c>
-      <c r="X47" s="10" t="n">
+      <c r="X47" s="19" t="n">
         <v>28.65</v>
       </c>
-      <c r="Y47" s="10" t="n">
+      <c r="Y47" s="19" t="n">
         <v>27.85</v>
       </c>
-      <c r="Z47" s="10" t="n">
+      <c r="Z47" s="19" t="n">
         <v>28.33</v>
       </c>
-      <c r="AA47" s="10" t="n">
+      <c r="AA47" s="19" t="n">
         <v>28.08</v>
       </c>
-      <c r="AB47" s="10" t="n">
+      <c r="AB47" s="19" t="n">
         <v>29.27</v>
       </c>
-      <c r="AC47" s="10" t="n">
+      <c r="AC47" s="19" t="n">
         <v>28.18</v>
       </c>
-      <c r="AD47" s="10" t="n">
+      <c r="AD47" s="19" t="n">
         <v>28.13</v>
       </c>
-      <c r="AE47" s="10" t="n">
+      <c r="AE47" s="19" t="n">
         <v>27.93</v>
       </c>
-      <c r="AF47" s="10" t="n">
+      <c r="AF47" s="19" t="n">
         <v>28.4</v>
       </c>
-      <c r="AG47" s="10" t="n">
+      <c r="AG47" s="19" t="n">
         <v>27.67</v>
       </c>
-      <c r="AH47" s="11" t="n">
+      <c r="AH47" s="19" t="n">
         <v>28.04</v>
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="20" t="n"/>
+      <c r="AK47" s="18" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4323,16 +4323,16 @@
       <c r="B48" s="6" t="n">
         <v>555.25</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="19" t="n">
         <v>30.87</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="19" t="n">
         <v>35.67</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E48" s="19" t="n">
         <v>31.3</v>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="19" t="n">
         <v>30.95</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -4345,19 +4345,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="10" t="n">
+      <c r="I48" s="19" t="n">
         <v>29.83</v>
       </c>
-      <c r="J48" s="10" t="n">
+      <c r="J48" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="K48" s="10" t="n">
+      <c r="K48" s="19" t="n">
         <v>30.7</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L48" s="19" t="n">
         <v>32.82</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="19" t="n">
         <v>36.93</v>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -4370,66 +4370,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="10" t="n">
+      <c r="P48" s="19" t="n">
         <v>30.17</v>
       </c>
-      <c r="Q48" s="10" t="n">
+      <c r="Q48" s="19" t="n">
         <v>30.43</v>
       </c>
-      <c r="R48" s="10" t="n">
+      <c r="R48" s="19" t="n">
         <v>30.48</v>
       </c>
-      <c r="S48" s="10" t="n">
+      <c r="S48" s="19" t="n">
         <v>35.07</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="T48" s="19" t="n">
         <v>35.13</v>
       </c>
-      <c r="U48" s="10" t="n">
+      <c r="U48" s="19" t="n">
         <v>38.18</v>
       </c>
-      <c r="V48" s="10" t="n">
+      <c r="V48" s="19" t="n">
         <v>30.97</v>
       </c>
-      <c r="W48" s="10" t="n">
+      <c r="W48" s="19" t="n">
         <v>29.7</v>
       </c>
-      <c r="X48" s="10" t="n">
+      <c r="X48" s="19" t="n">
         <v>30.2</v>
       </c>
-      <c r="Y48" s="10" t="n">
+      <c r="Y48" s="19" t="n">
         <v>30.97</v>
       </c>
-      <c r="Z48" s="10" t="n">
+      <c r="Z48" s="19" t="n">
         <v>34.18</v>
       </c>
-      <c r="AA48" s="10" t="n">
+      <c r="AA48" s="19" t="n">
         <v>30.1</v>
       </c>
-      <c r="AB48" s="10" t="n">
+      <c r="AB48" s="19" t="n">
         <v>29.78</v>
       </c>
-      <c r="AC48" s="10" t="n">
+      <c r="AC48" s="19" t="n">
         <v>31.43</v>
       </c>
-      <c r="AD48" s="10" t="n">
+      <c r="AD48" s="19" t="n">
         <v>30.87</v>
       </c>
-      <c r="AE48" s="10" t="n">
+      <c r="AE48" s="19" t="n">
         <v>29.88</v>
       </c>
-      <c r="AF48" s="10" t="n">
+      <c r="AF48" s="19" t="n">
         <v>31.67</v>
       </c>
-      <c r="AG48" s="10" t="n">
+      <c r="AG48" s="19" t="n">
         <v>29.67</v>
       </c>
-      <c r="AH48" s="11" t="n">
+      <c r="AH48" s="19" t="n">
         <v>32.04</v>
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="20" t="n"/>
+      <c r="AK48" s="18" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4440,16 +4440,16 @@
       <c r="B49" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="19" t="n">
         <v>29.83</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D49" s="19" t="n">
         <v>34.67</v>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="E49" s="19" t="n">
         <v>30.1</v>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="F49" s="19" t="n">
         <v>30.13</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -4462,19 +4462,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="10" t="n">
+      <c r="I49" s="19" t="n">
         <v>30.27</v>
       </c>
-      <c r="J49" s="10" t="n">
+      <c r="J49" s="19" t="n">
         <v>31.17</v>
       </c>
-      <c r="K49" s="10" t="n">
+      <c r="K49" s="19" t="n">
         <v>29.83</v>
       </c>
-      <c r="L49" s="10" t="n">
+      <c r="L49" s="19" t="n">
         <v>30.28</v>
       </c>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="19" t="n">
         <v>33.5</v>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -4487,66 +4487,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P49" s="10" t="n">
+      <c r="P49" s="19" t="n">
         <v>31.2</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="19" t="n">
         <v>32.07</v>
       </c>
-      <c r="R49" s="10" t="n">
+      <c r="R49" s="19" t="n">
         <v>32.5</v>
       </c>
-      <c r="S49" s="10" t="n">
+      <c r="S49" s="19" t="n">
         <v>32.17</v>
       </c>
-      <c r="T49" s="10" t="n">
+      <c r="T49" s="19" t="n">
         <v>29.88</v>
       </c>
-      <c r="U49" s="10" t="n">
+      <c r="U49" s="19" t="n">
         <v>32.85</v>
       </c>
-      <c r="V49" s="10" t="n">
+      <c r="V49" s="19" t="n">
         <v>29.97</v>
       </c>
-      <c r="W49" s="10" t="n">
+      <c r="W49" s="19" t="n">
         <v>30.85</v>
       </c>
-      <c r="X49" s="10" t="n">
+      <c r="X49" s="19" t="n">
         <v>31.2</v>
       </c>
-      <c r="Y49" s="10" t="n">
+      <c r="Y49" s="19" t="n">
         <v>30.82</v>
       </c>
-      <c r="Z49" s="10" t="n">
+      <c r="Z49" s="19" t="n">
         <v>33.93</v>
       </c>
-      <c r="AA49" s="10" t="n">
+      <c r="AA49" s="19" t="n">
         <v>30.57</v>
       </c>
-      <c r="AB49" s="10" t="n">
+      <c r="AB49" s="19" t="n">
         <v>30.85</v>
       </c>
-      <c r="AC49" s="10" t="n">
+      <c r="AC49" s="19" t="n">
         <v>32.78</v>
       </c>
-      <c r="AD49" s="10" t="n">
+      <c r="AD49" s="19" t="n">
         <v>31.38</v>
       </c>
-      <c r="AE49" s="10" t="n">
+      <c r="AE49" s="19" t="n">
         <v>30.18</v>
       </c>
-      <c r="AF49" s="10" t="n">
+      <c r="AF49" s="19" t="n">
         <v>31.43</v>
       </c>
-      <c r="AG49" s="10" t="n">
+      <c r="AG49" s="19" t="n">
         <v>30.47</v>
       </c>
-      <c r="AH49" s="11" t="n">
+      <c r="AH49" s="19" t="n">
         <v>31.29</v>
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="20" t="n"/>
+      <c r="AK49" s="18" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4557,16 +4557,16 @@
       <c r="B50" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="19" t="n">
         <v>28.7</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="19" t="n">
         <v>33.23</v>
       </c>
-      <c r="E50" s="10" t="n">
+      <c r="E50" s="19" t="n">
         <v>29.02</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="19" t="n">
         <v>28.9</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -4579,19 +4579,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="10" t="n">
+      <c r="I50" s="19" t="n">
         <v>28.7</v>
       </c>
-      <c r="J50" s="10" t="n">
+      <c r="J50" s="19" t="n">
         <v>28.6</v>
       </c>
-      <c r="K50" s="10" t="n">
+      <c r="K50" s="19" t="n">
         <v>28.27</v>
       </c>
-      <c r="L50" s="10" t="n">
+      <c r="L50" s="19" t="n">
         <v>29.25</v>
       </c>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="19" t="n">
         <v>29.67</v>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -4604,182 +4604,182 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P50" s="10" t="n">
+      <c r="P50" s="19" t="n">
         <v>28.9</v>
       </c>
-      <c r="Q50" s="10" t="n">
+      <c r="Q50" s="19" t="n">
         <v>29.18</v>
       </c>
-      <c r="R50" s="10" t="n">
+      <c r="R50" s="19" t="n">
         <v>31.72</v>
       </c>
-      <c r="S50" s="10" t="n">
+      <c r="S50" s="19" t="n">
         <v>31.28</v>
       </c>
-      <c r="T50" s="10" t="n">
+      <c r="T50" s="19" t="n">
         <v>28.7</v>
       </c>
-      <c r="U50" s="10" t="n">
+      <c r="U50" s="19" t="n">
         <v>30.88</v>
       </c>
-      <c r="V50" s="10" t="n">
+      <c r="V50" s="19" t="n">
         <v>29.17</v>
       </c>
-      <c r="W50" s="10" t="n">
+      <c r="W50" s="19" t="n">
         <v>28.6</v>
       </c>
-      <c r="X50" s="10" t="n">
+      <c r="X50" s="19" t="n">
         <v>29.23</v>
       </c>
-      <c r="Y50" s="10" t="n">
+      <c r="Y50" s="19" t="n">
         <v>32.1</v>
       </c>
-      <c r="Z50" s="10" t="n">
+      <c r="Z50" s="19" t="n">
         <v>28.92</v>
       </c>
-      <c r="AA50" s="10" t="n">
+      <c r="AA50" s="19" t="n">
         <v>29.53</v>
       </c>
-      <c r="AB50" s="10" t="n">
+      <c r="AB50" s="19" t="n">
         <v>29.12</v>
       </c>
-      <c r="AC50" s="10" t="n">
+      <c r="AC50" s="19" t="n">
         <v>29.28</v>
       </c>
-      <c r="AD50" s="10" t="n">
+      <c r="AD50" s="19" t="n">
         <v>29.4</v>
       </c>
-      <c r="AE50" s="10" t="n">
+      <c r="AE50" s="19" t="n">
         <v>28.3</v>
       </c>
-      <c r="AF50" s="10" t="n">
+      <c r="AF50" s="19" t="n">
         <v>28.68</v>
       </c>
-      <c r="AG50" s="10" t="n">
+      <c r="AG50" s="19" t="n">
         <v>29.07</v>
       </c>
-      <c r="AH50" s="11" t="n">
+      <c r="AH50" s="19" t="n">
         <v>29.5</v>
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="20" t="n"/>
+      <c r="AK50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>EL CIUDADANO TV NO AUTORIZADA</t>
         </is>
       </c>
-      <c r="B51" s="13" t="n">
+      <c r="B51" s="12" t="n">
         <v>675.25</v>
       </c>
-      <c r="C51" s="15" t="n">
+      <c r="C51" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="20" t="n">
         <v>32.42</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E51" s="20" t="n">
         <v>30.38</v>
       </c>
-      <c r="F51" s="15" t="n">
+      <c r="F51" s="20" t="n">
         <v>28.95</v>
       </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="15" t="n">
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="n">
         <v>28.37</v>
       </c>
-      <c r="J51" s="15" t="n">
+      <c r="J51" s="20" t="n">
         <v>31.97</v>
       </c>
-      <c r="K51" s="15" t="n">
+      <c r="K51" s="20" t="n">
         <v>30.47</v>
       </c>
-      <c r="L51" s="15" t="n">
+      <c r="L51" s="20" t="n">
         <v>30.97</v>
       </c>
-      <c r="M51" s="15" t="n">
+      <c r="M51" s="20" t="n">
         <v>32.63</v>
       </c>
-      <c r="N51" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="15" t="n">
+      <c r="N51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="20" t="n">
         <v>31.6</v>
       </c>
-      <c r="Q51" s="15" t="n">
+      <c r="Q51" s="20" t="n">
         <v>29.1</v>
       </c>
-      <c r="R51" s="15" t="n">
+      <c r="R51" s="20" t="n">
         <v>29.88</v>
       </c>
-      <c r="S51" s="15" t="n">
+      <c r="S51" s="20" t="n">
         <v>31.85</v>
       </c>
-      <c r="T51" s="15" t="n">
+      <c r="T51" s="20" t="n">
         <v>30.62</v>
       </c>
-      <c r="U51" s="15" t="n">
+      <c r="U51" s="20" t="n">
         <v>32.62</v>
       </c>
-      <c r="V51" s="15" t="n">
+      <c r="V51" s="20" t="n">
         <v>29.52</v>
       </c>
-      <c r="W51" s="15" t="n">
+      <c r="W51" s="20" t="n">
         <v>29.95</v>
       </c>
-      <c r="X51" s="15" t="n">
+      <c r="X51" s="20" t="n">
         <v>29.62</v>
       </c>
-      <c r="Y51" s="15" t="n">
+      <c r="Y51" s="20" t="n">
         <v>30.12</v>
       </c>
-      <c r="Z51" s="15" t="n">
+      <c r="Z51" s="20" t="n">
         <v>31.13</v>
       </c>
-      <c r="AA51" s="15" t="n">
+      <c r="AA51" s="20" t="n">
         <v>30.3</v>
       </c>
-      <c r="AB51" s="15" t="n">
+      <c r="AB51" s="20" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC51" s="15" t="n">
+      <c r="AC51" s="20" t="n">
         <v>29.95</v>
       </c>
-      <c r="AD51" s="15" t="n">
+      <c r="AD51" s="20" t="n">
         <v>28.9</v>
       </c>
-      <c r="AE51" s="15" t="n">
+      <c r="AE51" s="20" t="n">
         <v>29.73</v>
       </c>
-      <c r="AF51" s="15" t="n">
+      <c r="AF51" s="20" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG51" s="15" t="n">
+      <c r="AG51" s="20" t="n">
         <v>30.4</v>
       </c>
-      <c r="AH51" s="17" t="n">
+      <c r="AH51" s="20" t="n">
         <v>30.39</v>
       </c>
-      <c r="AI51" s="13" t="inlineStr"/>
-      <c r="AJ51" s="13" t="inlineStr"/>
+      <c r="AI51" s="12" t="inlineStr"/>
+      <c r="AJ51" s="12" t="inlineStr"/>
       <c r="AK51" s="21" t="n"/>
     </row>
   </sheetData>

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -209,6 +209,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -225,15 +228,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1295,7 +1304,12 @@
         <v>237.33</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="11" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1533,7 +1547,12 @@
         <v>299.96</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="11" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2009,7 +2028,12 @@
         <v>499.13</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="11" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2961,7 +2985,12 @@
         <v>499.69</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="11" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -3080,7 +3109,12 @@
         <v>499.61</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="11" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3199,126 +3233,136 @@
         <v>273.47</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="11" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>LA VOZ DE ARUTAM (NO AUTORIZADA)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="13" t="n">
         <v>107.3</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="14" t="n">
         <v>43.06</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="14" t="n">
         <v>41.51</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="14" t="n">
         <v>47.48</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="14" t="n">
         <v>48.84</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="n">
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="n">
         <v>49.17</v>
       </c>
-      <c r="J30" s="13" t="n">
+      <c r="J30" s="14" t="n">
         <v>40.76</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="14" t="n">
         <v>41.36</v>
       </c>
-      <c r="L30" s="13" t="n">
+      <c r="L30" s="14" t="n">
         <v>46.16</v>
       </c>
-      <c r="M30" s="13" t="n">
+      <c r="M30" s="14" t="n">
         <v>43.89</v>
       </c>
-      <c r="N30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" s="13" t="n">
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="14" t="n">
         <v>53.46</v>
       </c>
-      <c r="Q30" s="14" t="n">
+      <c r="Q30" s="15" t="n">
         <v>54.55</v>
       </c>
-      <c r="R30" s="14" t="n">
+      <c r="R30" s="15" t="n">
         <v>56.15</v>
       </c>
-      <c r="S30" s="13" t="n">
+      <c r="S30" s="14" t="n">
         <v>49.19</v>
       </c>
-      <c r="T30" s="13" t="n">
+      <c r="T30" s="14" t="n">
         <v>47.4</v>
       </c>
-      <c r="U30" s="13" t="n">
+      <c r="U30" s="14" t="n">
         <v>46.51</v>
       </c>
-      <c r="V30" s="13" t="n">
+      <c r="V30" s="14" t="n">
         <v>50.82</v>
       </c>
-      <c r="W30" s="14" t="n">
+      <c r="W30" s="15" t="n">
         <v>55.1</v>
       </c>
-      <c r="X30" s="14" t="n">
+      <c r="X30" s="15" t="n">
         <v>54.54</v>
       </c>
-      <c r="Y30" s="13" t="n">
+      <c r="Y30" s="14" t="n">
         <v>49.52</v>
       </c>
-      <c r="Z30" s="13" t="n">
+      <c r="Z30" s="14" t="n">
         <v>47.54</v>
       </c>
-      <c r="AA30" s="14" t="n">
+      <c r="AA30" s="15" t="n">
         <v>54.18</v>
       </c>
-      <c r="AB30" s="14" t="n">
+      <c r="AB30" s="15" t="n">
         <v>55.12</v>
       </c>
-      <c r="AC30" s="13" t="n">
+      <c r="AC30" s="14" t="n">
         <v>48.65</v>
       </c>
-      <c r="AD30" s="13" t="n">
+      <c r="AD30" s="14" t="n">
         <v>53.31</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="14" t="n">
         <v>49.16</v>
       </c>
-      <c r="AF30" s="13" t="n">
+      <c r="AF30" s="14" t="n">
         <v>50.49</v>
       </c>
-      <c r="AG30" s="13" t="n">
+      <c r="AG30" s="14" t="n">
         <v>51.46</v>
       </c>
-      <c r="AH30" s="13" t="n">
+      <c r="AH30" s="14" t="n">
         <v>49.24</v>
       </c>
-      <c r="AI30" s="15" t="n">
+      <c r="AI30" s="16" t="n">
         <v>498.71</v>
       </c>
-      <c r="AJ30" s="12" t="inlineStr"/>
-      <c r="AK30" s="16" t="inlineStr"/>
+      <c r="AJ30" s="13" t="inlineStr"/>
+      <c r="AK30" s="17" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="31"/>
     <row r="32"/>
@@ -3493,7 +3537,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK40" s="17" t="n"/>
+      <c r="AK40" s="18" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3610,7 +3654,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="18" t="n"/>
+      <c r="AK41" s="19" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3727,9 +3771,9 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="18" t="n"/>
+      <c r="AK42" s="19" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>CADENA ECUATORIANA DE TELEVISIO</t>
@@ -3738,16 +3782,16 @@
       <c r="B43" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C43" s="19" t="n">
+      <c r="C43" s="20" t="n">
         <v>38.13</v>
       </c>
-      <c r="D43" s="19" t="n">
+      <c r="D43" s="20" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="19" t="n">
+      <c r="E43" s="20" t="n">
         <v>41.13</v>
       </c>
-      <c r="F43" s="19" t="n">
+      <c r="F43" s="20" t="n">
         <v>41.17</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -3760,19 +3804,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="19" t="n">
+      <c r="I43" s="20" t="n">
         <v>36.3</v>
       </c>
-      <c r="J43" s="19" t="n">
+      <c r="J43" s="20" t="n">
         <v>49.5</v>
       </c>
-      <c r="K43" s="19" t="n">
+      <c r="K43" s="20" t="n">
         <v>37.1</v>
       </c>
-      <c r="L43" s="19" t="n">
+      <c r="L43" s="20" t="n">
         <v>40.53</v>
       </c>
-      <c r="M43" s="19" t="n">
+      <c r="M43" s="20" t="n">
         <v>50.5</v>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -3785,68 +3829,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P43" s="19" t="n">
+      <c r="P43" s="20" t="n">
         <v>39.87</v>
       </c>
-      <c r="Q43" s="19" t="n">
+      <c r="Q43" s="20" t="n">
         <v>38.13</v>
       </c>
-      <c r="R43" s="19" t="n">
+      <c r="R43" s="20" t="n">
         <v>37.27</v>
       </c>
-      <c r="S43" s="19" t="n">
+      <c r="S43" s="20" t="n">
         <v>47.38</v>
       </c>
-      <c r="T43" s="19" t="n">
+      <c r="T43" s="20" t="n">
         <v>51.48</v>
       </c>
       <c r="U43" s="9" t="n">
         <v>56.65</v>
       </c>
-      <c r="V43" s="19" t="n">
+      <c r="V43" s="20" t="n">
         <v>45.32</v>
       </c>
-      <c r="W43" s="19" t="n">
+      <c r="W43" s="20" t="n">
         <v>41.1</v>
       </c>
-      <c r="X43" s="19" t="n">
+      <c r="X43" s="20" t="n">
         <v>39.07</v>
       </c>
-      <c r="Y43" s="19" t="n">
+      <c r="Y43" s="20" t="n">
         <v>41.78</v>
       </c>
-      <c r="Z43" s="19" t="n">
+      <c r="Z43" s="20" t="n">
         <v>44.7</v>
       </c>
-      <c r="AA43" s="19" t="n">
+      <c r="AA43" s="20" t="n">
         <v>42.47</v>
       </c>
-      <c r="AB43" s="19" t="n">
+      <c r="AB43" s="20" t="n">
         <v>37.5</v>
       </c>
-      <c r="AC43" s="19" t="n">
+      <c r="AC43" s="20" t="n">
         <v>39.95</v>
       </c>
-      <c r="AD43" s="19" t="n">
+      <c r="AD43" s="20" t="n">
         <v>38.4</v>
       </c>
-      <c r="AE43" s="19" t="n">
+      <c r="AE43" s="20" t="n">
         <v>39.77</v>
       </c>
-      <c r="AF43" s="19" t="n">
+      <c r="AF43" s="20" t="n">
         <v>41.9</v>
       </c>
-      <c r="AG43" s="19" t="n">
+      <c r="AG43" s="20" t="n">
         <v>39.3</v>
       </c>
-      <c r="AH43" s="19" t="n">
+      <c r="AH43" s="20" t="n">
         <v>42.16</v>
       </c>
       <c r="AI43" s="6" t="inlineStr"/>
-      <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="18" t="n"/>
+      <c r="AJ43" s="21" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK43" s="19" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>TELEVISION DEL PACIFICO</t>
@@ -3855,16 +3903,16 @@
       <c r="B44" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C44" s="19" t="n">
+      <c r="C44" s="20" t="n">
         <v>36.4</v>
       </c>
-      <c r="D44" s="19" t="n">
+      <c r="D44" s="20" t="n">
         <v>37.47</v>
       </c>
-      <c r="E44" s="19" t="n">
+      <c r="E44" s="20" t="n">
         <v>39.78</v>
       </c>
-      <c r="F44" s="19" t="n">
+      <c r="F44" s="20" t="n">
         <v>41.35</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3877,19 +3925,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="19" t="n">
+      <c r="I44" s="20" t="n">
         <v>36.1</v>
       </c>
-      <c r="J44" s="19" t="n">
+      <c r="J44" s="20" t="n">
         <v>39</v>
       </c>
-      <c r="K44" s="19" t="n">
+      <c r="K44" s="20" t="n">
         <v>37.07</v>
       </c>
-      <c r="L44" s="19" t="n">
+      <c r="L44" s="20" t="n">
         <v>37.3</v>
       </c>
-      <c r="M44" s="19" t="n">
+      <c r="M44" s="20" t="n">
         <v>39.17</v>
       </c>
       <c r="N44" s="6" t="inlineStr">
@@ -3902,66 +3950,70 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P44" s="19" t="n">
+      <c r="P44" s="20" t="n">
         <v>36.13</v>
       </c>
-      <c r="Q44" s="19" t="n">
+      <c r="Q44" s="20" t="n">
         <v>36.55</v>
       </c>
-      <c r="R44" s="19" t="n">
+      <c r="R44" s="20" t="n">
         <v>37.55</v>
       </c>
-      <c r="S44" s="19" t="n">
+      <c r="S44" s="20" t="n">
         <v>37.77</v>
       </c>
-      <c r="T44" s="19" t="n">
+      <c r="T44" s="20" t="n">
         <v>42.85</v>
       </c>
-      <c r="U44" s="19" t="n">
+      <c r="U44" s="20" t="n">
         <v>43.72</v>
       </c>
-      <c r="V44" s="19" t="n">
+      <c r="V44" s="20" t="n">
         <v>42.25</v>
       </c>
-      <c r="W44" s="19" t="n">
+      <c r="W44" s="20" t="n">
         <v>39.5</v>
       </c>
-      <c r="X44" s="19" t="n">
+      <c r="X44" s="20" t="n">
         <v>37.32</v>
       </c>
-      <c r="Y44" s="19" t="n">
+      <c r="Y44" s="20" t="n">
         <v>38.07</v>
       </c>
-      <c r="Z44" s="19" t="n">
+      <c r="Z44" s="20" t="n">
         <v>37.63</v>
       </c>
-      <c r="AA44" s="19" t="n">
+      <c r="AA44" s="20" t="n">
         <v>40.42</v>
       </c>
-      <c r="AB44" s="19" t="n">
+      <c r="AB44" s="20" t="n">
         <v>38.12</v>
       </c>
-      <c r="AC44" s="19" t="n">
+      <c r="AC44" s="20" t="n">
         <v>36.5</v>
       </c>
-      <c r="AD44" s="19" t="n">
+      <c r="AD44" s="20" t="n">
         <v>36.72</v>
       </c>
-      <c r="AE44" s="19" t="n">
+      <c r="AE44" s="20" t="n">
         <v>36.95</v>
       </c>
-      <c r="AF44" s="19" t="n">
+      <c r="AF44" s="20" t="n">
         <v>39.42</v>
       </c>
-      <c r="AG44" s="19" t="n">
+      <c r="AG44" s="20" t="n">
         <v>37.27</v>
       </c>
-      <c r="AH44" s="19" t="n">
+      <c r="AH44" s="20" t="n">
         <v>38.46</v>
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
-      <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="18" t="n"/>
+      <c r="AJ44" s="21" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK44" s="19" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4078,9 +4130,9 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="18" t="n"/>
+      <c r="AK45" s="19" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>UCSG TELEVISION</t>
@@ -4089,16 +4141,16 @@
       <c r="B46" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C46" s="19" t="n">
+      <c r="C46" s="20" t="n">
         <v>27.47</v>
       </c>
-      <c r="D46" s="19" t="n">
+      <c r="D46" s="20" t="n">
         <v>26.83</v>
       </c>
-      <c r="E46" s="19" t="n">
+      <c r="E46" s="20" t="n">
         <v>28.47</v>
       </c>
-      <c r="F46" s="19" t="n">
+      <c r="F46" s="20" t="n">
         <v>27.65</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -4111,19 +4163,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="19" t="n">
+      <c r="I46" s="20" t="n">
         <v>26.77</v>
       </c>
-      <c r="J46" s="19" t="n">
+      <c r="J46" s="20" t="n">
         <v>27.47</v>
       </c>
-      <c r="K46" s="19" t="n">
+      <c r="K46" s="20" t="n">
         <v>26.73</v>
       </c>
-      <c r="L46" s="19" t="n">
+      <c r="L46" s="20" t="n">
         <v>26.62</v>
       </c>
-      <c r="M46" s="19" t="n">
+      <c r="M46" s="20" t="n">
         <v>26.77</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -4136,68 +4188,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="19" t="n">
+      <c r="P46" s="20" t="n">
         <v>27.73</v>
       </c>
-      <c r="Q46" s="19" t="n">
+      <c r="Q46" s="20" t="n">
         <v>26.82</v>
       </c>
-      <c r="R46" s="19" t="n">
+      <c r="R46" s="20" t="n">
         <v>26.38</v>
       </c>
-      <c r="S46" s="19" t="n">
+      <c r="S46" s="20" t="n">
         <v>27.02</v>
       </c>
-      <c r="T46" s="19" t="n">
+      <c r="T46" s="20" t="n">
         <v>26.75</v>
       </c>
-      <c r="U46" s="19" t="n">
+      <c r="U46" s="20" t="n">
         <v>27.97</v>
       </c>
-      <c r="V46" s="19" t="n">
+      <c r="V46" s="20" t="n">
         <v>26.12</v>
       </c>
-      <c r="W46" s="19" t="n">
+      <c r="W46" s="20" t="n">
         <v>26.88</v>
       </c>
-      <c r="X46" s="19" t="n">
+      <c r="X46" s="20" t="n">
         <v>26.98</v>
       </c>
-      <c r="Y46" s="19" t="n">
+      <c r="Y46" s="20" t="n">
         <v>26.9</v>
       </c>
-      <c r="Z46" s="19" t="n">
+      <c r="Z46" s="20" t="n">
         <v>35.83</v>
       </c>
-      <c r="AA46" s="19" t="n">
+      <c r="AA46" s="20" t="n">
         <v>27.43</v>
       </c>
-      <c r="AB46" s="19" t="n">
+      <c r="AB46" s="20" t="n">
         <v>26.72</v>
       </c>
-      <c r="AC46" s="19" t="n">
+      <c r="AC46" s="20" t="n">
         <v>26.77</v>
       </c>
-      <c r="AD46" s="19" t="n">
+      <c r="AD46" s="20" t="n">
         <v>26.87</v>
       </c>
-      <c r="AE46" s="19" t="n">
+      <c r="AE46" s="20" t="n">
         <v>28.92</v>
       </c>
-      <c r="AF46" s="19" t="n">
+      <c r="AF46" s="20" t="n">
         <v>27.12</v>
       </c>
-      <c r="AG46" s="19" t="n">
+      <c r="AG46" s="20" t="n">
         <v>26.6</v>
       </c>
-      <c r="AH46" s="19" t="n">
+      <c r="AH46" s="20" t="n">
         <v>27.43</v>
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
-      <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="18" t="n"/>
+      <c r="AJ46" s="21" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK46" s="19" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>SONOVISIÓN TV</t>
@@ -4206,16 +4262,16 @@
       <c r="B47" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C47" s="19" t="n">
+      <c r="C47" s="20" t="n">
         <v>28.37</v>
       </c>
-      <c r="D47" s="19" t="n">
+      <c r="D47" s="20" t="n">
         <v>27.92</v>
       </c>
-      <c r="E47" s="19" t="n">
+      <c r="E47" s="20" t="n">
         <v>27.95</v>
       </c>
-      <c r="F47" s="19" t="n">
+      <c r="F47" s="20" t="n">
         <v>27.78</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -4228,19 +4284,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="19" t="n">
+      <c r="I47" s="20" t="n">
         <v>27.37</v>
       </c>
-      <c r="J47" s="19" t="n">
+      <c r="J47" s="20" t="n">
         <v>27.83</v>
       </c>
-      <c r="K47" s="19" t="n">
+      <c r="K47" s="20" t="n">
         <v>27.77</v>
       </c>
-      <c r="L47" s="19" t="n">
+      <c r="L47" s="20" t="n">
         <v>28.52</v>
       </c>
-      <c r="M47" s="19" t="n">
+      <c r="M47" s="20" t="n">
         <v>28.13</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -4253,68 +4309,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="19" t="n">
+      <c r="P47" s="20" t="n">
         <v>27.4</v>
       </c>
-      <c r="Q47" s="19" t="n">
+      <c r="Q47" s="20" t="n">
         <v>27.75</v>
       </c>
-      <c r="R47" s="19" t="n">
+      <c r="R47" s="20" t="n">
         <v>27.68</v>
       </c>
-      <c r="S47" s="19" t="n">
+      <c r="S47" s="20" t="n">
         <v>27.72</v>
       </c>
-      <c r="T47" s="19" t="n">
+      <c r="T47" s="20" t="n">
         <v>28.08</v>
       </c>
-      <c r="U47" s="19" t="n">
+      <c r="U47" s="20" t="n">
         <v>27.73</v>
       </c>
-      <c r="V47" s="19" t="n">
+      <c r="V47" s="20" t="n">
         <v>28.07</v>
       </c>
-      <c r="W47" s="19" t="n">
+      <c r="W47" s="20" t="n">
         <v>28.58</v>
       </c>
-      <c r="X47" s="19" t="n">
+      <c r="X47" s="20" t="n">
         <v>28.65</v>
       </c>
-      <c r="Y47" s="19" t="n">
+      <c r="Y47" s="20" t="n">
         <v>27.85</v>
       </c>
-      <c r="Z47" s="19" t="n">
+      <c r="Z47" s="20" t="n">
         <v>28.33</v>
       </c>
-      <c r="AA47" s="19" t="n">
+      <c r="AA47" s="20" t="n">
         <v>28.08</v>
       </c>
-      <c r="AB47" s="19" t="n">
+      <c r="AB47" s="20" t="n">
         <v>29.27</v>
       </c>
-      <c r="AC47" s="19" t="n">
+      <c r="AC47" s="20" t="n">
         <v>28.18</v>
       </c>
-      <c r="AD47" s="19" t="n">
+      <c r="AD47" s="20" t="n">
         <v>28.13</v>
       </c>
-      <c r="AE47" s="19" t="n">
+      <c r="AE47" s="20" t="n">
         <v>27.93</v>
       </c>
-      <c r="AF47" s="19" t="n">
+      <c r="AF47" s="20" t="n">
         <v>28.4</v>
       </c>
-      <c r="AG47" s="19" t="n">
+      <c r="AG47" s="20" t="n">
         <v>27.67</v>
       </c>
-      <c r="AH47" s="19" t="n">
+      <c r="AH47" s="20" t="n">
         <v>28.04</v>
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
-      <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="18" t="n"/>
+      <c r="AJ47" s="21" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK47" s="19" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
           <t>DIGITAL TV</t>
@@ -4323,16 +4383,16 @@
       <c r="B48" s="6" t="n">
         <v>555.25</v>
       </c>
-      <c r="C48" s="19" t="n">
+      <c r="C48" s="20" t="n">
         <v>30.87</v>
       </c>
-      <c r="D48" s="19" t="n">
+      <c r="D48" s="20" t="n">
         <v>35.67</v>
       </c>
-      <c r="E48" s="19" t="n">
+      <c r="E48" s="20" t="n">
         <v>31.3</v>
       </c>
-      <c r="F48" s="19" t="n">
+      <c r="F48" s="20" t="n">
         <v>30.95</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -4345,19 +4405,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="19" t="n">
+      <c r="I48" s="20" t="n">
         <v>29.83</v>
       </c>
-      <c r="J48" s="19" t="n">
+      <c r="J48" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="K48" s="19" t="n">
+      <c r="K48" s="20" t="n">
         <v>30.7</v>
       </c>
-      <c r="L48" s="19" t="n">
+      <c r="L48" s="20" t="n">
         <v>32.82</v>
       </c>
-      <c r="M48" s="19" t="n">
+      <c r="M48" s="20" t="n">
         <v>36.93</v>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -4370,68 +4430,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="19" t="n">
+      <c r="P48" s="20" t="n">
         <v>30.17</v>
       </c>
-      <c r="Q48" s="19" t="n">
+      <c r="Q48" s="20" t="n">
         <v>30.43</v>
       </c>
-      <c r="R48" s="19" t="n">
+      <c r="R48" s="20" t="n">
         <v>30.48</v>
       </c>
-      <c r="S48" s="19" t="n">
+      <c r="S48" s="20" t="n">
         <v>35.07</v>
       </c>
-      <c r="T48" s="19" t="n">
+      <c r="T48" s="20" t="n">
         <v>35.13</v>
       </c>
-      <c r="U48" s="19" t="n">
+      <c r="U48" s="20" t="n">
         <v>38.18</v>
       </c>
-      <c r="V48" s="19" t="n">
+      <c r="V48" s="20" t="n">
         <v>30.97</v>
       </c>
-      <c r="W48" s="19" t="n">
+      <c r="W48" s="20" t="n">
         <v>29.7</v>
       </c>
-      <c r="X48" s="19" t="n">
+      <c r="X48" s="20" t="n">
         <v>30.2</v>
       </c>
-      <c r="Y48" s="19" t="n">
+      <c r="Y48" s="20" t="n">
         <v>30.97</v>
       </c>
-      <c r="Z48" s="19" t="n">
+      <c r="Z48" s="20" t="n">
         <v>34.18</v>
       </c>
-      <c r="AA48" s="19" t="n">
+      <c r="AA48" s="20" t="n">
         <v>30.1</v>
       </c>
-      <c r="AB48" s="19" t="n">
+      <c r="AB48" s="20" t="n">
         <v>29.78</v>
       </c>
-      <c r="AC48" s="19" t="n">
+      <c r="AC48" s="20" t="n">
         <v>31.43</v>
       </c>
-      <c r="AD48" s="19" t="n">
+      <c r="AD48" s="20" t="n">
         <v>30.87</v>
       </c>
-      <c r="AE48" s="19" t="n">
+      <c r="AE48" s="20" t="n">
         <v>29.88</v>
       </c>
-      <c r="AF48" s="19" t="n">
+      <c r="AF48" s="20" t="n">
         <v>31.67</v>
       </c>
-      <c r="AG48" s="19" t="n">
+      <c r="AG48" s="20" t="n">
         <v>29.67</v>
       </c>
-      <c r="AH48" s="19" t="n">
+      <c r="AH48" s="20" t="n">
         <v>32.04</v>
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
-      <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="18" t="n"/>
+      <c r="AJ48" s="21" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK48" s="19" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>TV LEGISLATIVA NO AUTORIZADA</t>
@@ -4440,16 +4504,16 @@
       <c r="B49" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C49" s="19" t="n">
+      <c r="C49" s="20" t="n">
         <v>29.83</v>
       </c>
-      <c r="D49" s="19" t="n">
+      <c r="D49" s="20" t="n">
         <v>34.67</v>
       </c>
-      <c r="E49" s="19" t="n">
+      <c r="E49" s="20" t="n">
         <v>30.1</v>
       </c>
-      <c r="F49" s="19" t="n">
+      <c r="F49" s="20" t="n">
         <v>30.13</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -4462,19 +4526,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="19" t="n">
+      <c r="I49" s="20" t="n">
         <v>30.27</v>
       </c>
-      <c r="J49" s="19" t="n">
+      <c r="J49" s="20" t="n">
         <v>31.17</v>
       </c>
-      <c r="K49" s="19" t="n">
+      <c r="K49" s="20" t="n">
         <v>29.83</v>
       </c>
-      <c r="L49" s="19" t="n">
+      <c r="L49" s="20" t="n">
         <v>30.28</v>
       </c>
-      <c r="M49" s="19" t="n">
+      <c r="M49" s="20" t="n">
         <v>33.5</v>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -4487,68 +4551,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P49" s="19" t="n">
+      <c r="P49" s="20" t="n">
         <v>31.2</v>
       </c>
-      <c r="Q49" s="19" t="n">
+      <c r="Q49" s="20" t="n">
         <v>32.07</v>
       </c>
-      <c r="R49" s="19" t="n">
+      <c r="R49" s="20" t="n">
         <v>32.5</v>
       </c>
-      <c r="S49" s="19" t="n">
+      <c r="S49" s="20" t="n">
         <v>32.17</v>
       </c>
-      <c r="T49" s="19" t="n">
+      <c r="T49" s="20" t="n">
         <v>29.88</v>
       </c>
-      <c r="U49" s="19" t="n">
+      <c r="U49" s="20" t="n">
         <v>32.85</v>
       </c>
-      <c r="V49" s="19" t="n">
+      <c r="V49" s="20" t="n">
         <v>29.97</v>
       </c>
-      <c r="W49" s="19" t="n">
+      <c r="W49" s="20" t="n">
         <v>30.85</v>
       </c>
-      <c r="X49" s="19" t="n">
+      <c r="X49" s="20" t="n">
         <v>31.2</v>
       </c>
-      <c r="Y49" s="19" t="n">
+      <c r="Y49" s="20" t="n">
         <v>30.82</v>
       </c>
-      <c r="Z49" s="19" t="n">
+      <c r="Z49" s="20" t="n">
         <v>33.93</v>
       </c>
-      <c r="AA49" s="19" t="n">
+      <c r="AA49" s="20" t="n">
         <v>30.57</v>
       </c>
-      <c r="AB49" s="19" t="n">
+      <c r="AB49" s="20" t="n">
         <v>30.85</v>
       </c>
-      <c r="AC49" s="19" t="n">
+      <c r="AC49" s="20" t="n">
         <v>32.78</v>
       </c>
-      <c r="AD49" s="19" t="n">
+      <c r="AD49" s="20" t="n">
         <v>31.38</v>
       </c>
-      <c r="AE49" s="19" t="n">
+      <c r="AE49" s="20" t="n">
         <v>30.18</v>
       </c>
-      <c r="AF49" s="19" t="n">
+      <c r="AF49" s="20" t="n">
         <v>31.43</v>
       </c>
-      <c r="AG49" s="19" t="n">
+      <c r="AG49" s="20" t="n">
         <v>30.47</v>
       </c>
-      <c r="AH49" s="19" t="n">
+      <c r="AH49" s="20" t="n">
         <v>31.29</v>
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
-      <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="18" t="n"/>
+      <c r="AJ49" s="21" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK49" s="19" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>TELEATAHUALPA (RTU)</t>
@@ -4557,16 +4625,16 @@
       <c r="B50" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C50" s="19" t="n">
+      <c r="C50" s="20" t="n">
         <v>28.7</v>
       </c>
-      <c r="D50" s="19" t="n">
+      <c r="D50" s="20" t="n">
         <v>33.23</v>
       </c>
-      <c r="E50" s="19" t="n">
+      <c r="E50" s="20" t="n">
         <v>29.02</v>
       </c>
-      <c r="F50" s="19" t="n">
+      <c r="F50" s="20" t="n">
         <v>28.9</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -4579,19 +4647,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="19" t="n">
+      <c r="I50" s="20" t="n">
         <v>28.7</v>
       </c>
-      <c r="J50" s="19" t="n">
+      <c r="J50" s="20" t="n">
         <v>28.6</v>
       </c>
-      <c r="K50" s="19" t="n">
+      <c r="K50" s="20" t="n">
         <v>28.27</v>
       </c>
-      <c r="L50" s="19" t="n">
+      <c r="L50" s="20" t="n">
         <v>29.25</v>
       </c>
-      <c r="M50" s="19" t="n">
+      <c r="M50" s="20" t="n">
         <v>29.67</v>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -4604,183 +4672,191 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P50" s="19" t="n">
+      <c r="P50" s="20" t="n">
         <v>28.9</v>
       </c>
-      <c r="Q50" s="19" t="n">
+      <c r="Q50" s="20" t="n">
         <v>29.18</v>
       </c>
-      <c r="R50" s="19" t="n">
+      <c r="R50" s="20" t="n">
         <v>31.72</v>
       </c>
-      <c r="S50" s="19" t="n">
+      <c r="S50" s="20" t="n">
         <v>31.28</v>
       </c>
-      <c r="T50" s="19" t="n">
+      <c r="T50" s="20" t="n">
         <v>28.7</v>
       </c>
-      <c r="U50" s="19" t="n">
+      <c r="U50" s="20" t="n">
         <v>30.88</v>
       </c>
-      <c r="V50" s="19" t="n">
+      <c r="V50" s="20" t="n">
         <v>29.17</v>
       </c>
-      <c r="W50" s="19" t="n">
+      <c r="W50" s="20" t="n">
         <v>28.6</v>
       </c>
-      <c r="X50" s="19" t="n">
+      <c r="X50" s="20" t="n">
         <v>29.23</v>
       </c>
-      <c r="Y50" s="19" t="n">
+      <c r="Y50" s="20" t="n">
         <v>32.1</v>
       </c>
-      <c r="Z50" s="19" t="n">
+      <c r="Z50" s="20" t="n">
         <v>28.92</v>
       </c>
-      <c r="AA50" s="19" t="n">
+      <c r="AA50" s="20" t="n">
         <v>29.53</v>
       </c>
-      <c r="AB50" s="19" t="n">
+      <c r="AB50" s="20" t="n">
         <v>29.12</v>
       </c>
-      <c r="AC50" s="19" t="n">
+      <c r="AC50" s="20" t="n">
         <v>29.28</v>
       </c>
-      <c r="AD50" s="19" t="n">
+      <c r="AD50" s="20" t="n">
         <v>29.4</v>
       </c>
-      <c r="AE50" s="19" t="n">
+      <c r="AE50" s="20" t="n">
         <v>28.3</v>
       </c>
-      <c r="AF50" s="19" t="n">
+      <c r="AF50" s="20" t="n">
         <v>28.68</v>
       </c>
-      <c r="AG50" s="19" t="n">
+      <c r="AG50" s="20" t="n">
         <v>29.07</v>
       </c>
-      <c r="AH50" s="19" t="n">
+      <c r="AH50" s="20" t="n">
         <v>29.5</v>
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
-      <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="18" t="n"/>
+      <c r="AJ50" s="21" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK50" s="19" t="n"/>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>EL CIUDADANO TV NO AUTORIZADA</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="13" t="n">
         <v>675.25</v>
       </c>
-      <c r="C51" s="20" t="n">
+      <c r="C51" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="D51" s="20" t="n">
+      <c r="D51" s="22" t="n">
         <v>32.42</v>
       </c>
-      <c r="E51" s="20" t="n">
+      <c r="E51" s="22" t="n">
         <v>30.38</v>
       </c>
-      <c r="F51" s="20" t="n">
+      <c r="F51" s="22" t="n">
         <v>28.95</v>
       </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="20" t="n">
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="22" t="n">
         <v>28.37</v>
       </c>
-      <c r="J51" s="20" t="n">
+      <c r="J51" s="22" t="n">
         <v>31.97</v>
       </c>
-      <c r="K51" s="20" t="n">
+      <c r="K51" s="22" t="n">
         <v>30.47</v>
       </c>
-      <c r="L51" s="20" t="n">
+      <c r="L51" s="22" t="n">
         <v>30.97</v>
       </c>
-      <c r="M51" s="20" t="n">
+      <c r="M51" s="22" t="n">
         <v>32.63</v>
       </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="20" t="n">
+      <c r="N51" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="22" t="n">
         <v>31.6</v>
       </c>
-      <c r="Q51" s="20" t="n">
+      <c r="Q51" s="22" t="n">
         <v>29.1</v>
       </c>
-      <c r="R51" s="20" t="n">
+      <c r="R51" s="22" t="n">
         <v>29.88</v>
       </c>
-      <c r="S51" s="20" t="n">
+      <c r="S51" s="22" t="n">
         <v>31.85</v>
       </c>
-      <c r="T51" s="20" t="n">
+      <c r="T51" s="22" t="n">
         <v>30.62</v>
       </c>
-      <c r="U51" s="20" t="n">
+      <c r="U51" s="22" t="n">
         <v>32.62</v>
       </c>
-      <c r="V51" s="20" t="n">
+      <c r="V51" s="22" t="n">
         <v>29.52</v>
       </c>
-      <c r="W51" s="20" t="n">
+      <c r="W51" s="22" t="n">
         <v>29.95</v>
       </c>
-      <c r="X51" s="20" t="n">
+      <c r="X51" s="22" t="n">
         <v>29.62</v>
       </c>
-      <c r="Y51" s="20" t="n">
+      <c r="Y51" s="22" t="n">
         <v>30.12</v>
       </c>
-      <c r="Z51" s="20" t="n">
+      <c r="Z51" s="22" t="n">
         <v>31.13</v>
       </c>
-      <c r="AA51" s="20" t="n">
+      <c r="AA51" s="22" t="n">
         <v>30.3</v>
       </c>
-      <c r="AB51" s="20" t="n">
+      <c r="AB51" s="22" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC51" s="20" t="n">
+      <c r="AC51" s="22" t="n">
         <v>29.95</v>
       </c>
-      <c r="AD51" s="20" t="n">
+      <c r="AD51" s="22" t="n">
         <v>28.9</v>
       </c>
-      <c r="AE51" s="20" t="n">
+      <c r="AE51" s="22" t="n">
         <v>29.73</v>
       </c>
-      <c r="AF51" s="20" t="n">
+      <c r="AF51" s="22" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG51" s="20" t="n">
+      <c r="AG51" s="22" t="n">
         <v>30.4</v>
       </c>
-      <c r="AH51" s="20" t="n">
+      <c r="AH51" s="22" t="n">
         <v>30.39</v>
       </c>
-      <c r="AI51" s="12" t="inlineStr"/>
-      <c r="AJ51" s="12" t="inlineStr"/>
-      <c r="AK51" s="21" t="n"/>
+      <c r="AI51" s="13" t="inlineStr"/>
+      <c r="AJ51" s="23" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK51" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/macas_ReporteUnificado.xlsx
+++ b/ReportesUnificados/macas_ReporteUnificado.xlsx
@@ -816,7 +816,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
